--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -15,12 +15,12 @@
     <sheet name="PAPER_TRADE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$6:$K$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$6:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$6:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$6:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$1:$K$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PIYASA_REJIMI'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PAPER_TRADE'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PAPER_TRADE'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -64,27 +64,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -129,55 +129,64 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -545,13 +554,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -668,16 +677,16 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2183113574232514</v>
+        <v>0.1077292740640564</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>21831.13574232514</v>
+        <v>10772.92740640564</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.0573311795813907</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1251.60476370896</v>
+        <v>617.6246357539271</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>48.10856867095328</v>
@@ -688,7 +697,7 @@
       <c r="J7" s="4" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -709,16 +718,16 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.1869848989934444</v>
+        <v>0.09227072593594365</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>18698.48989934444</v>
+        <v>9227.072593594365</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.1135370331433445</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2122.971067432362</v>
+        <v>1047.614446874969</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>94.87335182556761</v>
@@ -729,178 +738,49 @@
       <c r="J8" s="4" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0.1725900803339808</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>17259.00803339808</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.0150053319741709</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>258.9771450860207</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>376.820729495411</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>352.6875</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0.3001066394834209</v>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0.1648309264671155</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>16483.09264671155</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.035964069170425</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>592.7990840888577</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>306.6453644744458</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>277.2324952194509</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0.5672232190119821</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0.1348305474093958</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>13483.05474093958</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.0318627708566734</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>429.6074836585416</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>107.313728169094</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.6372554171334678</v>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0.1224521893728121</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>12245.21893728121</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.0149130710450822</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>182.6138199742606</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>389.7266192813116</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>359.9101054961429</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.2377187363935803</v>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:K12"/>
+  <autoFilter ref="A6:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -911,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -941,7 +821,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
     </row>
@@ -1092,55 +972,55 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="6" t="n">
         <v>45.5</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="6" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="6" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="6" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="6" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="4" t="n">
         <v>0.7970588235294117</v>
       </c>
-      <c r="M8" s="13" t="n">
+      <c r="M8" s="4" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
@@ -1157,7 +1037,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
@@ -1212,7 +1092,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
@@ -1377,7 +1257,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
@@ -1422,55 +1302,55 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="6" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="5" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="5" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="5" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="6" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="6" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="6" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="6" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L14" s="13" t="n">
+      <c r="L14" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="M14" s="13" t="n">
+      <c r="M14" s="4" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="13" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
@@ -1487,7 +1367,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
@@ -1643,11 +1523,11 @@
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1656,48 +1536,103 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>33.41999816894531</v>
+        <v>63.70000076293945</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>-0.0659425781939114</v>
+        <v>-0.0615218226622063</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>-0.0310153372448183</v>
+        <v>-0.004687488079071</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.1010665940075984</v>
+        <v>0.1090908628521543</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>31.21619732644926</v>
+        <v>59.78106061241949</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>32.38346565501426</v>
+        <v>63.40140776872636</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>36.79764355562079</v>
+        <v>70.64908880985141</v>
       </c>
       <c r="K18" s="17" t="n">
-        <v>31.21619732644926</v>
+        <v>59.66295737853054</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>0.3764705882352941</v>
+        <v>0.4176470588235293</v>
       </c>
       <c r="M18" s="16" t="n">
         <v>64.34999999999999</v>
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
+          <t>6A momentum pozitif; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>33.41999816894531</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>-0.0659425781939114</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>-0.0310153372448183</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>0.1010665940075984</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>31.21619732644926</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>32.38346565501426</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>36.79764355562079</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>31.21619732644926</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>0.3764705882352941</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:O18"/>
+  <autoFilter ref="A6:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1823,43 +1758,43 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="4" t="n">
         <v>0.7970588235294117</v>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="5" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H3" s="15" t="n">
+      <c r="H3" s="5" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J3" s="15" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K3" s="15" t="n">
+      <c r="K3" s="5" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
@@ -1877,7 +1812,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
@@ -1918,7 +1853,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E5" s="15" t="n">
@@ -2041,7 +1976,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E8" s="15" t="n">
@@ -2069,43 +2004,43 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="5" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="5" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="5" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="5" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="5" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="K9" s="5" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
@@ -2123,7 +2058,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E10" s="15" t="n">
@@ -2356,43 +2291,43 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="16" t="n">
         <v>0.4176470588235293</v>
       </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="18" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="18" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="20" t="n">
+      <c r="J16" s="18" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K16" s="20" t="n">
+      <c r="K16" s="18" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
@@ -2490,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2510,55 +2445,67 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>SISE.IS, BIMAS.IS, TOASO.IS, ASELS.IS, FROTO.IS, ARCLK.IS</t>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>SISE.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>BIMAS.IS, TOASO.IS, ASELS.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, YKBNK.IS</t>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>KCHOL.IS, GARAN.IS, TUPRS.IS, AKBNK.IS, PGSUS.IS</t>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Nakit kuralı</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Beklenen getiri %5 altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2589,66 +2536,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="21" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="21" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="21" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -2666,7 +2613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2722,307 +2669,277 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="22" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="22" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H2" s="5" t="n">
+      <c r="G2" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H2" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
-        <v>63.70000076293945</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>63.70000076293945</v>
-      </c>
-      <c r="E3" s="5" t="n">
+      <c r="C3" s="22" t="n">
+        <v>244.8999938964844</v>
+      </c>
+      <c r="D3" s="22" t="n">
+        <v>244.8999938964844</v>
+      </c>
+      <c r="E3" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H3" s="5" t="n">
+      <c r="G3" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H3" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>244.8999938964844</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>244.8999938964844</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="C4" s="22" t="n">
+        <v>123.0999984741211</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>123.0999984741211</v>
+      </c>
+      <c r="E4" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="G4" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H4" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>123.0999984741211</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>123.0999984741211</v>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="C5" s="22" t="n">
+        <v>104</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>104</v>
+      </c>
+      <c r="E5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H5" s="5" t="n">
+      <c r="G5" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H5" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>104</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>104</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="C6" s="22" t="n">
+        <v>85.19999694824219</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>85.19999694824219</v>
+      </c>
+      <c r="E6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H6" s="5" t="n">
+      <c r="G6" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H6" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="C7" s="22" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="G7" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H7" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="C8" s="22" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="E8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="22" t="n">
+        <v>-3.637978807091713e-12</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H8" s="5" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>296</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>296</v>
+      </c>
+      <c r="E9" s="23" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="F9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="C10" s="22" t="n">
+        <v>384</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>384</v>
+      </c>
+      <c r="E10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="F10" s="22" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>296</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>296</v>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="G10" s="22" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>384</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>384</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -39,15 +39,15 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -88,19 +88,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -120,73 +114,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -571,7 +562,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>100.000 TL Bugün Nasıl Dağıtılır?</t>
         </is>
@@ -606,174 +597,174 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.1077292740640564</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>10772.92740640564</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="5" t="n">
         <v>617.6246357539271</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="5" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="5" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.09227072593594365</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>9227.072593594365</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="5" t="n">
         <v>1047.614446874969</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="5" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="3" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>80000</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -812,7 +803,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
@@ -840,792 +831,792 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Skor</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="10" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="10" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="10" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="L7" s="9" t="n">
         <v>0.8735294117647058</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="9" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N7" s="10" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="5" t="n">
         <v>45.5</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="5" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="5" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="5" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="3" t="n">
         <v>0.7970588235294117</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="3" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="13" t="n">
         <v>371.25</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="14" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="14" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="14" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="13" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="13" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="13" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="13" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="12" t="n">
         <v>0.6970588235294117</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="M9" s="12" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="13" t="n">
         <v>296</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="14" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="14" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="14" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="13" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="13" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="13" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="13" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="12" t="n">
         <v>0.6264705882352941</v>
       </c>
-      <c r="M10" s="13" t="n">
+      <c r="M10" s="12" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="10" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="10" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="10" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="10" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="9" t="n">
         <v>0.5411764705882353</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="9" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="10" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="10" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="10" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="10" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="9" t="n">
         <v>0.538235294117647</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="9" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="10" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="10" t="inlineStr">
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="13" t="n">
         <v>384</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="14" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="13" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="13" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="13" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="13" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L13" s="13" t="n">
+      <c r="L13" s="12" t="n">
         <v>0.5029411764705883</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="12" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="13" t="inlineStr">
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="13" t="inlineStr">
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="5" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="4" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="4" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="5" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="5" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="5" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="5" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="3" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="13" t="n">
         <v>104</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="14" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="14" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="14" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="13" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="13" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="13" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="13" t="n">
         <v>98.8</v>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L15" s="12" t="n">
         <v>0.4941176470588235</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="M15" s="12" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="13" t="inlineStr">
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="13" t="inlineStr">
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>291.5</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="11" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="11" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="11" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="10" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="10" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="10" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="10" t="n">
         <v>276.925</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="9" t="n">
         <v>0.4882352941176471</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="9" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="10" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="10" t="inlineStr">
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="17" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="17" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="17" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="16" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="16" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="16" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="16" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="15" t="n">
         <v>0.4235294117647059</v>
       </c>
-      <c r="M17" s="16" t="n">
+      <c r="M17" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="16" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="17" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="17" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="17" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H18" s="16" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I18" s="16" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="16" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="K18" s="16" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L18" s="16" t="n">
+      <c r="L18" s="15" t="n">
         <v>0.4176470588235293</v>
       </c>
-      <c r="M18" s="16" t="n">
+      <c r="M18" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="O18" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="16" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="17" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="17" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="17" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="16" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="16" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="16" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="K19" s="16" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L19" s="16" t="n">
+      <c r="L19" s="15" t="n">
         <v>0.3764705882352941</v>
       </c>
-      <c r="M19" s="16" t="n">
+      <c r="M19" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="N19" s="15" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O19" s="16" t="inlineStr">
+      <c r="O19" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -1660,756 +1651,756 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Skor</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="9" t="n">
         <v>0.8735294117647058</v>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="11" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="11" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="11" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="11" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="11" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="11" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>0.7970588235294117</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="4" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="4" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="4" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="12" t="n">
         <v>0.6970588235294117</v>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="14" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="14" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="14" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="14" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
+      <c r="J4" s="14" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K4" s="15" t="n">
+      <c r="K4" s="14" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.6264705882352941</v>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="14" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="14" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="14" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="14" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="15" t="n">
+      <c r="J5" s="14" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K5" s="15" t="n">
+      <c r="K5" s="14" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>0.5411764705882353</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="11" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="11" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="11" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="11" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.538235294117647</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="11" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="11" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="11" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="12" t="n">
         <v>0.5029411764705883</v>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="14" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="14" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="14" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="14" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="14" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K8" s="15" t="n">
+      <c r="K8" s="14" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="4" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="4" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="4" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <v>0.4941176470588235</v>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="14" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="14" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="14" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="14" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="14" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K10" s="15" t="n">
+      <c r="K10" s="14" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>0.4882352941176471</v>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="11" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="11" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="11" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="18" t="n">
         <v>0.4882352941176471</v>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="19" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="19" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="19" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="18" t="n">
         <v>0.4588235294117647</v>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="19" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="19" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="19" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="19" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="19" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K13" s="20" t="n">
+      <c r="K13" s="19" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="18" t="n">
         <v>0.4382352941176471</v>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="19" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="19" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="19" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="19" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="J14" s="19" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="K14" s="19" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="15" t="n">
         <v>0.4235294117647059</v>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="17" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="17" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="17" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="17" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="17" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="17" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="15" t="n">
         <v>0.4176470588235293</v>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="17" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="17" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="17" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="17" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="17" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="17" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="15" t="n">
         <v>0.3764705882352941</v>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="17" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="17" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="17" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="H17" s="17" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="17" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="K17" s="17" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="18" t="n">
         <v>0.3382352941176471</v>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="19" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="19" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="19" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="19" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="20" t="n">
+      <c r="J18" s="19" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K18" s="20" t="n">
+      <c r="K18" s="19" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -2433,72 +2424,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>SISE.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>BIMAS.IS, TOASO.IS, ASELS.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Beklenen getiri %5 altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
@@ -2524,78 +2515,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n">
+      <c r="B2" s="20" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B3" s="21" t="n">
+      <c r="B3" s="20" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="20" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -2627,314 +2618,314 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C2" s="22" t="n">
+      <c r="C2" s="21" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D2" s="22" t="n">
+      <c r="D2" s="21" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E2" s="23" t="n">
+      <c r="E2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="22" t="n">
+      <c r="F2" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H2" s="23" t="n">
+      <c r="G2" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H2" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="21" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="21" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E3" s="23" t="n">
+      <c r="E3" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="22" t="n">
+      <c r="F3" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H3" s="23" t="n">
+      <c r="G3" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H3" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="21" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D4" s="22" t="n">
+      <c r="D4" s="21" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E4" s="23" t="n">
+      <c r="E4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="F4" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H4" s="23" t="n">
+      <c r="G4" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H4" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="21" t="n">
         <v>104</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="21" t="n">
         <v>104</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H5" s="23" t="n">
+      <c r="G5" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="21" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="21" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H6" s="23" t="n">
+      <c r="G6" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="21" t="n">
         <v>45.5</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="21" t="n">
         <v>45.5</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H7" s="23" t="n">
+      <c r="G7" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H7" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <v>371.25</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="21" t="n">
         <v>371.25</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="21" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G8" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H8" s="23" t="n">
+      <c r="G8" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H8" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="21" t="n">
         <v>296</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="21" t="n">
         <v>296</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H9" s="23" t="n">
+      <c r="G9" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H9" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="21" t="n">
         <v>384</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="21" t="n">
         <v>384</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="22" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H10" s="23" t="n">
+      <c r="G10" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H10" s="22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H2" s="22" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H3" s="22" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H4" s="22" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H5" s="22" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H6" s="22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H7" s="22" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H9" s="22" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>450000</v>
+        <v>520000</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -41,9 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
@@ -60,6 +57,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -105,19 +105,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -137,96 +131,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,595 +602,595 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BIST RankingBot Yatırımcı Raporu</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı: 64.35/100</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BU AY YAPILACAKLAR</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>AZALT: ASELS.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NAKIT: %50</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Neden Nakit Tutuluyor?</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>- Yeterli sayıda yüksek kaliteli fırsat bulunamadı.</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>- Opportunity filter aktif.</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Tablo çekiciliğe göre sıralıdır; yüksek conviction daha güçlü adayları gösterir.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Qualified opportunities count: 5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Rejected opportunities count: 5</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.1243871586137416</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>12438.71586137416</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>713.1262528103351</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="8" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="8" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Cash allocation %: %50</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="7" t="n">
         <v>0.1065382972466226</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>10653.82972466226</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>1209.604218552528</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="8" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="8" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="7" t="n">
         <v>0.09833656824386003</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>9833.656824386002</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>147.5572851699831</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="8" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="8" t="n">
         <v>352.6875</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>0.3001066394834209</v>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="7" t="n">
         <v>0.09391563882388926</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>9391.563882388926</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>337.7588530847005</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="8" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="8" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>0.5672232190119821</v>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="7" t="n">
         <v>0.07682233707188654</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>7682.233707188654</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>244.7772522795647</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="8" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>0.6372554171334678</v>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1238,944 +1229,944 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Renkler: AL yeşil, TUT sarı, SAT kırmızı.</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bu rapor araştırma amaçlıdır; otomatik emir veya yatırım tavsiyesi değildir.</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="15" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="15" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="15" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="15" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="15" t="n">
+      <c r="M8" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="15" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="M9" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="19" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="18" t="n">
+      <c r="M11" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="15" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="15" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="15" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="15" t="n">
+      <c r="M12" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="15" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="15" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="15" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="15" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="15" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="15" t="n">
+      <c r="M13" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="21" t="n">
         <v>384</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="22" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="22" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="21" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="21" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="21" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="21" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="21" t="n">
+      <c r="M14" s="20" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="19" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="19" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>98.8</v>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="N16" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="O16" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="15" t="n">
         <v>291.5</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="16" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="15" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="15" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="15" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="15" t="n">
         <v>276.925</v>
       </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="24" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="24" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="24" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="24" t="inlineStr">
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="24" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="24" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="24" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="24" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n">
+      <c r="M19" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="N19" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="O19" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="24" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="25" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="25" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="24" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J20" s="25" t="n">
+      <c r="J20" s="24" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K20" s="25" t="n">
+      <c r="K20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M20" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="N20" s="23" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -2210,824 +2201,824 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="16" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="16" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="16" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="16" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="16" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J5" s="19" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="K5" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="19" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="19" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="19" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="16" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="16" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="16" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="16" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="22" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="22" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="22" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="22" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="19" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="19" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="19" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="16" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="16" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="27" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="27" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="27" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="27" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="27" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="27" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="27" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="27" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="27" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="27" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="27" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="27" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="27" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="27" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="27" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="27" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="27" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="27" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="25" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="25" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="25" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="25" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="25" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="25" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="25" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="25" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="27" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="27" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="27" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="27" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="27" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K20" s="28" t="n">
+      <c r="K20" s="27" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -3051,100 +3042,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nitelikli fırsat sayısı</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3170,232 +3161,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
@@ -3421,94 +3412,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -3540,342 +3531,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-06 05:45</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H4" s="30" t="n">
+      <c r="G4" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H5" s="30" t="n">
+      <c r="G5" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H6" s="30" t="n">
+      <c r="G6" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H7" s="30" t="n">
+      <c r="G7" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H8" s="30" t="n">
+      <c r="G8" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H9" s="30" t="n">
+      <c r="G9" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="28" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G10" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H10" s="30" t="n">
+      <c r="G10" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H11" s="30" t="n">
+      <c r="G11" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H11" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="29" t="n">
-        <v>940000</v>
-      </c>
-      <c r="H12" s="30" t="n">
+      <c r="G12" s="28" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="H12" s="29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-06 05:45</t>
+          <t>Son Güncelleme: 2026-06-07 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1010000</v>
+        <v>1080000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-07 06:11</t>
+          <t>Son Güncelleme: 2026-06-08 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1080000</v>
+        <v>1150000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-08 06:26</t>
+          <t>Son Güncelleme: 2026-06-09 05:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1150000</v>
+        <v>1220000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-09 05:58</t>
+          <t>Son Güncelleme: 2026-06-10 06:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1220000</v>
+        <v>1290000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -41,6 +41,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
@@ -57,9 +60,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -105,13 +105,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -131,93 +137,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,595 +611,595 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>BIST RankingBot Yatırımcı Raporu</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Güven Puanı: 64.35/100</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>BU AY YAPILACAKLAR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>AZALT: ASELS.IS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>NAKIT: %50</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Neden Nakit Tutuluyor?</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>- Yeterli sayıda yüksek kaliteli fırsat bulunamadı.</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>- Opportunity filter aktif.</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tablo çekiciliğe göre sıralıdır; yüksek conviction daha güçlü adayları gösterir.</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Qualified opportunities count: 5</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Rejected opportunities count: 5</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="8" t="n">
         <v>0.1243871586137416</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <v>12438.71586137416</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>713.1262528103351</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="9" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Cash allocation %: %50</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="8" t="n">
         <v>0.1065382972466226</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>10653.82972466226</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>1209.604218552528</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K21" s="6" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="8" t="n">
         <v>0.09833656824386003</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <v>9833.656824386002</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="9" t="n">
         <v>147.5572851699831</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="9" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="9" t="n">
         <v>352.6875</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>0.3001066394834209</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="8" t="n">
         <v>0.09391563882388926</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="9" t="n">
         <v>9391.563882388926</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>337.7588530847005</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="7" t="n">
         <v>0.5672232190119821</v>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="8" t="n">
         <v>0.07682233707188654</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="9" t="n">
         <v>7682.233707188654</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>244.7772522795647</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="9" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="9" t="n">
         <v>98.8</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="7" t="n">
         <v>0.6372554171334678</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1229,944 +1238,944 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Renkler: AL yeşil, TUT sarı, SAT kırmızı.</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Bu rapor araştırma amaçlıdır; otomatik emir veya yatırım tavsiyesi değildir.</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="16" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="16" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="16" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K8" s="15" t="n">
+      <c r="K8" s="16" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="N8" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="19" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="K10" s="19" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="18" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="19" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="K11" s="19" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="16" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="16" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K12" s="15" t="n">
+      <c r="K12" s="16" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="16" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="16" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="16" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="16" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="14" t="inlineStr">
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>384</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="23" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="20" t="n">
+      <c r="M14" s="21" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="20" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="O14" s="21" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="20" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="19" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="19" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="18" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O15" s="18" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>104</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="20" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="20" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="19" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="19" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="19" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="19" t="n">
         <v>98.8</v>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="18" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="O16" s="18" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>291.5</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="16" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="16" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="16" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K17" s="15" t="n">
+      <c r="K17" s="16" t="n">
         <v>276.925</v>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="15" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="25" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H18" s="24" t="n">
+      <c r="H18" s="25" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I18" s="24" t="n">
+      <c r="I18" s="25" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J18" s="24" t="n">
+      <c r="J18" s="25" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K18" s="24" t="n">
+      <c r="K18" s="25" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L18" s="23" t="inlineStr">
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M18" s="23" t="n">
+      <c r="M18" s="24" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="23" t="inlineStr">
+      <c r="N18" s="24" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H19" s="24" t="n">
+      <c r="H19" s="25" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="I19" s="25" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J19" s="24" t="n">
+      <c r="J19" s="25" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K19" s="24" t="n">
+      <c r="K19" s="25" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L19" s="23" t="inlineStr">
+      <c r="L19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M19" s="23" t="n">
+      <c r="M19" s="24" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="23" t="inlineStr">
+      <c r="N19" s="24" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O19" s="23" t="inlineStr">
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="26" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H20" s="25" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I20" s="25" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J20" s="24" t="n">
+      <c r="J20" s="25" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K20" s="24" t="n">
+      <c r="K20" s="25" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="24" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N20" s="23" t="inlineStr">
+      <c r="N20" s="24" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O20" s="23" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -2201,824 +2210,824 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="17" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H4" s="16" t="n">
+      <c r="H4" s="17" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
+      <c r="J4" s="17" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="17" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="20" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="20" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="20" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="20" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="20" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="20" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="20" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="20" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="20" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="20" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="20" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="17" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="17" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="17" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="23" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="23" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K10" s="22" t="n">
+      <c r="K10" s="23" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="20" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="20" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="20" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="20" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="20" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="20" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="17" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="17" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="28" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="28" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="28" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="28" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="28" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K14" s="27" t="n">
+      <c r="K14" s="28" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="28" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="28" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="28" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="28" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
+      <c r="J15" s="28" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K15" s="27" t="n">
+      <c r="K15" s="28" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="28" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="28" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="28" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="28" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
+      <c r="J16" s="28" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K16" s="27" t="n">
+      <c r="K16" s="28" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="26" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="26" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
+      <c r="J17" s="26" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K17" s="25" t="n">
+      <c r="K17" s="26" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="26" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="26" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="26" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="26" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="26" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="26" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="28" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="27" t="n">
+      <c r="J20" s="28" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K20" s="27" t="n">
+      <c r="K20" s="28" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -3042,100 +3051,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Nitelikli fırsat sayısı</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3161,232 +3170,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
@@ -3412,94 +3421,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -3531,342 +3540,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 06:11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="29" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H4" s="29" t="n">
+      <c r="G4" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H4" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="29" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H5" s="29" t="n">
+      <c r="G5" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H5" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H6" s="29" t="n">
+      <c r="G6" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H6" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="29" t="n">
         <v>104</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H7" s="29" t="n">
+      <c r="G7" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H7" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H8" s="29" t="n">
+      <c r="G8" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H8" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="29" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="29" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H9" s="29" t="n">
+      <c r="G9" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H9" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="29" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="29" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G10" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H10" s="29" t="n">
+      <c r="G10" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H10" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>296</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="29" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H11" s="29" t="n">
+      <c r="G11" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H11" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="29" t="n">
         <v>384</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="29" t="n">
         <v>384</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="28" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="H12" s="29" t="n">
+      <c r="G12" s="29" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="H12" s="30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -41,9 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
@@ -60,6 +57,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -105,19 +105,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -137,96 +131,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,595 +602,595 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BIST RankingBot Yatırımcı Raporu</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı: 64.35/100</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BU AY YAPILACAKLAR</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>AZALT: ASELS.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NAKIT: %50</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Neden Nakit Tutuluyor?</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>- Yeterli sayıda yüksek kaliteli fırsat bulunamadı.</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>- Opportunity filter aktif.</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Tablo çekiciliğe göre sıralıdır; yüksek conviction daha güçlü adayları gösterir.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Qualified opportunities count: 5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Allocation TL</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Expected Return %</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Expected Return TL</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Stop Price</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Risk/Reward</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Conviction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Rejected opportunities count: 5</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.1243871586137416</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>12438.71586137416</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>713.1262528103351</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="8" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="8" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>0.9590875530162508</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Cash allocation %: %50</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="7" t="n">
         <v>0.1065382972466226</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>10653.82972466226</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>1209.604218552528</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="8" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="8" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>2.270740662866885</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="7" t="n">
         <v>0.09833656824386003</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>9833.656824386002</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>147.5572851699831</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="8" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="8" t="n">
         <v>352.6875</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>0.3001066394834209</v>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="7" t="n">
         <v>0.09391563882388926</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>9391.563882388926</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>337.7588530847005</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="8" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="8" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>0.5672232190119821</v>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="7" t="n">
         <v>0.07682233707188654</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>7682.233707188654</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>244.7772522795647</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="8" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>0.6372554171334678</v>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1238,944 +1229,944 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Aylık Yatırımcı Özeti</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Toplam önerilen/satılacak satır: 13</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Renkler: AL yeşil, TUT sarı, SAT kırmızı.</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bu rapor araştırma amaçlıdır; otomatik emir veya yatırım tavsiyesi değildir.</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt %</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta %</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst %</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Hedef Alt Fiyat</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Hedef Orta Fiyat</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Hedef Üst Fiyat</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Stop / Risk Fiyatı</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Ana Sebep</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Risk Notu</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.0420559802578865</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1156036872656343</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="15" t="n">
         <v>38.31776078968454</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="15" t="n">
         <v>39.79358124262377</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="15" t="n">
         <v>44.62414749062538</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="15" t="n">
         <v>37.54126859386067</v>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="15" t="n">
+      <c r="M8" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="15" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.0063614591608023</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.1855133537025062</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>45.7894463918165</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>48.10856867095328</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>53.94085759346403</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>42.78015584943257</v>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="M9" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="19" t="n">
         <v>-0.0046916890080428</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.1020951406282874</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>369.5082104557641</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>376.820729495411</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>409.1528209582517</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>352.6875</v>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.06340373236672001</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.07252410609256819</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>306.6453644744458</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>317.4671354034002</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>277.2324952194509</v>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="18" t="n">
+      <c r="M11" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>102.5999984741211</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <v>-0.0448028308183779</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>0.0559687682788319</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <v>98.00322810051922</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="15" t="n">
         <v>102.0206973756039</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="15" t="n">
         <v>108.3423940141277</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="15" t="n">
         <v>97.46999855041503</v>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="15" t="n">
+      <c r="M12" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="15" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>23.05999946594238</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0633746386509592</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.0814151454989152</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="15" t="n">
         <v>21.59858033249697</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="15" t="n">
         <v>22.38352252170423</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="15" t="n">
         <v>24.93743267766699</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="15" t="n">
         <v>21.56527333559732</v>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="15" t="n">
+      <c r="M13" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="21" t="n">
         <v>384</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="22" t="n">
         <v>-0.0281690730134268</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="22" t="n">
         <v>0.08543155919911009</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="21" t="n">
         <v>373.1830759628441</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="21" t="n">
         <v>389.7266192813116</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="21" t="n">
         <v>416.8057187324583</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="21" t="n">
         <v>359.9101054961429</v>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="21" t="n">
+      <c r="M14" s="20" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="19" t="n">
         <v>-0.0108077431499975</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.1589867372070065</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <v>84.27917726484502</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>94.87335182556761</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>98.74566647309014</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>80.93999710083007</v>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="19" t="n">
         <v>-0.0155083176665838</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.08243455158337749</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <v>102.3871349626753</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>107.313728169094</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>112.5731933646713</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>98.8</v>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="17" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="N16" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="O16" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="15" t="n">
         <v>291.5</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="16" t="n">
         <v>-0.0386983355086648</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <v>0.0471518681568155</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="15" t="n">
         <v>280.2194351992242</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="15" t="n">
         <v>289.4402953699822</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="15" t="n">
         <v>305.2447695677117</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="15" t="n">
         <v>276.925</v>
       </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="14" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="24" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.09996593281665379</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0287358367126191</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="24" t="n">
         <v>87.01823150556903</v>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="24" t="n">
         <v>91.55748946742311</v>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="24" t="n">
         <v>80.10303197931782</v>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N18" s="24" t="inlineStr">
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <v>63.70000076293945</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0615218226622063</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>0.1090908628521543</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="24" t="n">
         <v>59.78106061241949</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="24" t="n">
         <v>63.40140776872636</v>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="24" t="n">
         <v>70.64908880985141</v>
       </c>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="24" t="n">
         <v>59.66295737853054</v>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n">
+      <c r="M19" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="N19" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif; hacim artışı var</t>
         </is>
       </c>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="O19" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="24" t="n">
         <v>33.41999816894531</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="25" t="n">
         <v>-0.0659425781939114</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="25" t="n">
         <v>0.1010665940075984</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="24" t="n">
         <v>32.38346565501426</v>
       </c>
-      <c r="J20" s="25" t="n">
+      <c r="J20" s="24" t="n">
         <v>36.79764355562079</v>
       </c>
-      <c r="K20" s="25" t="n">
+      <c r="K20" s="24" t="n">
         <v>31.21619732644926</v>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M20" s="23" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="N20" s="23" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="23" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
@@ -2210,824 +2201,824 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Öneri Kalitesi</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Aksiyon</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1A Momentum</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>3A Momentum</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>6A Momentum</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Hacim Değişimi</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Trend Durumu</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Beklenen Getiri Orta %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="16" t="n">
         <v>0.1862395774600724</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="16" t="n">
         <v>0.2539185102925374</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="16" t="n">
         <v>0.6764458917342262</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="16" t="n">
         <v>0.041267190077997</v>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="16" t="n">
         <v>0.0307341425767416</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="16" t="n">
         <v>-0.0051604689344056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.0046066414674543</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.001115469846139</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.235030926116428</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.1566089169082498</v>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J5" s="19" t="n">
         <v>0.0298883972589827</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="K5" s="19" t="n">
         <v>0.0573311795813907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.0013486176668915</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.100815418828762</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.3632607485858201</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>-0.1103780044876269</v>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="19" t="n">
         <v>0.023589744633299</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="19" t="n">
         <v>0.0150053319741709</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="19" t="n">
         <v>-0.0025273799494524</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>-0.0189264227791532</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.3768329115958089</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>-0.1760804208636897</v>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="19" t="n">
         <v>0.0273607577956114</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="19" t="n">
         <v>0.035964069170425</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.08474576386540381</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-0.1506622857438071</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>0.1173328587488999</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="16" t="n">
         <v>0.0313938948468988</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.0219305756012054</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="16" t="n">
         <v>-0.0056462096211761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="16" t="n">
         <v>-0.07091056609677771</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.3013544220943314</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>0.35647055682014</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="16" t="n">
         <v>-0.4658997689756274</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="16" t="n">
         <v>0.0324095005412434</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="16" t="n">
         <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>-0.0975323149236192</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="22" t="n">
         <v>0.234726688102894</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="22" t="n">
         <v>1.093784148197624</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="22" t="n">
         <v>-0.3248706883042701</v>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="22" t="n">
         <v>0.0313670501352306</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="22" t="n">
         <v>0.0149130710450822</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>-0.1310556420557422</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>-0.2569639003843752</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>-0.0072963800603302</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>0.4702778794241973</v>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="19" t="n">
         <v>0.0232889396320691</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="19" t="n">
         <v>0.1135370331433445</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="19" t="n">
         <v>-0.0739091970276476</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <v>-0.1231028554971428</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>-0.0160832260863227</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.0886630889314125</v>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="19" t="n">
         <v>0.0203560631794317</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="19" t="n">
         <v>0.0318627708566734</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>-0.0731319554848967</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-0.0642054574638844</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.068744271310724</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="16" t="n">
         <v>-0.1125189107212077</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="16" t="n">
         <v>0.0231561831887904</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="16" t="n">
         <v>-0.0070658820926857</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="27" t="n">
         <v>-0.0805734197027545</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="27" t="n">
         <v>-0.0596758909696701</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="27" t="n">
         <v>0.1458106229539508</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="27" t="n">
         <v>-0.2599604463071995</v>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="27" t="n">
         <v>0.0209928798538189</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="27" t="n">
         <v>0.0070464703305382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="27" t="n">
         <v>-0.0723436224182088</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="27" t="n">
         <v>-0.218580848518051</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="27" t="n">
         <v>-0.07793667413424429</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="27" t="n">
         <v>-0.0069595372522321</v>
       </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="27" t="n">
         <v>0.0279986421832064</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="27" t="n">
         <v>0.0063124281375852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="27" t="n">
         <v>-0.1110708025535955</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="27" t="n">
         <v>0.1808376609273443</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="27" t="n">
         <v>0.3087414111063782</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="27" t="n">
         <v>-0.4371995375985574</v>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="27" t="n">
         <v>0.0254253869317556</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="27" t="n">
         <v>0.0179805767303264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="25" t="n">
         <v>-0.0743629892086322</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <v>-0.1387634300955811</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="25" t="n">
         <v>0.1041495071207343</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="25" t="n">
         <v>-0.137952192271936</v>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="25" t="n">
         <v>0.02615590712964</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="25" t="n">
         <v>-0.0222670617351794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>-0.1356851641707055</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>-0.2830794788478351</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.0153144390476849</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="25" t="n">
         <v>0.1238362901154654</v>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="25" t="n">
         <v>0.0316879382736025</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="25" t="n">
         <v>-0.004687488079071</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>-0.0858862988621121</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>-0.2407996860197412</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <v>-0.053257821777556</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="25" t="n">
         <v>-0.0414981713743457</v>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="25" t="n">
         <v>0.0305942800876695</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="25" t="n">
         <v>-0.0310153372448183</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="27" t="n">
         <v>-0.0597432263673228</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="27" t="n">
         <v>-0.167161244124102</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="27" t="n">
         <v>-0.1621890850921175</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="27" t="n">
         <v>-0.2601417240448666</v>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="27" t="n">
         <v>0.0215890519221315</v>
       </c>
-      <c r="K20" s="28" t="n">
+      <c r="K20" s="27" t="n">
         <v>0.0408327384185252</v>
       </c>
     </row>
@@ -3051,100 +3042,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Hisseler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Alınacaklar</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Tutulacaklar</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Satılacaklar</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Portföy dışı kalanlar</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Nakit kuralı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nitelikli fırsat sayısı</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3170,232 +3161,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
@@ -3421,94 +3412,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Gösterge</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BIST100 Güncel Kapanış</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>13704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>12248.34019042969</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Risk ON / Risk OFF</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Risk ON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Aktif Model</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>volume_heavy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Güven Puanı</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>64.34999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
@@ -3540,342 +3531,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rapor Tarihi: 2026-06-01</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Son Güncelleme: 2026-06-10 13:37</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme: 2026-06-11 06:31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Aktif Pozisyon</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Giriş Tarihi</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Giriş Fiyatı</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Gerçekleşmemiş PnL</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Benchmark Getirisi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H4" s="30" t="n">
+      <c r="G4" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H5" s="30" t="n">
+      <c r="G5" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H6" s="30" t="n">
+      <c r="G6" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="28" t="n">
         <v>104</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H7" s="30" t="n">
+      <c r="G7" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H8" s="30" t="n">
+      <c r="G8" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H9" s="30" t="n">
+      <c r="G9" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="28" t="n">
         <v>-3.637978807091713e-12</v>
       </c>
-      <c r="G10" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H10" s="30" t="n">
+      <c r="G10" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="28" t="n">
         <v>296</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H11" s="30" t="n">
+      <c r="G11" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H11" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="29" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="H12" s="30" t="n">
+      <c r="G12" s="28" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H12" s="29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-11 06:31</t>
+          <t>Son Güncelleme: 2026-06-12 06:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1430000</v>
+        <v>1500000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-12 06:23</t>
+          <t>Son Güncelleme: 2026-06-13 06:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1500000</v>
+        <v>1570000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-13 06:06</t>
+          <t>Son Güncelleme: 2026-06-14 06:24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1570000</v>
+        <v>1640000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-14 06:24</t>
+          <t>Son Güncelleme: 2026-06-15 07:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1640000</v>
+        <v>1710000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-15 07:06</t>
+          <t>Son Güncelleme: 2026-06-16 07:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1710000</v>
+        <v>1780000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-16 07:12</t>
+          <t>Son Güncelleme: 2026-06-17 06:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1780000</v>
+        <v>1850000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-17 06:57</t>
+          <t>Son Güncelleme: 2026-06-18 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1850000</v>
+        <v>1920000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-18 06:42</t>
+          <t>Son Güncelleme: 2026-06-19 06:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1920000</v>
+        <v>1990000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-19 06:54</t>
+          <t>Son Güncelleme: 2026-06-20 06:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1990000</v>
+        <v>2060000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-20 06:07</t>
+          <t>Son Güncelleme: 2026-06-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2060000</v>
+        <v>2130000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-21 06:41</t>
+          <t>Son Güncelleme: 2026-06-22 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2130000</v>
+        <v>2200000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2220,7 +2220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3547,7 +3547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-22 07:09</t>
+          <t>Son Güncelleme: 2026-06-23 05:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2200000</v>
+        <v>2270000</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="YONETICI_OZETI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PORTFOY_ONERISI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ILK_20_SIRALAMA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AL_SAT_OZET" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PORTFOY_DEGISIMI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="PIYASA_REJIMI" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YONETICI_OZETI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOY_ONERISI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ILK_20_SIRALAMA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AL_SAT_OZET" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOY_DEGISIMI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIYASA_REJIMI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,10 +157,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,15 +197,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -638,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 64.35/100</t>
+          <t>Güven Puanı: 79.86/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -749,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: SISE.IS, FROTO.IS, BIMAS.IS, TOASO.IS, ARCLK.IS</t>
+          <t>AL: YKBNK.IS, ASELS.IS, GARAN.IS, EREGL.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -766,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: ASELS.IS</t>
+          <t>AZALT: AKBNK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -783,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
+          <t>ÇIK: TOASO.IS, THYAO.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -960,7 +951,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -969,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1243871586137416</v>
+        <v>0.1214155430149161</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12438.71586137416</v>
+        <v>12141.55430149161</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0573311795813907</v>
+        <v>0.09630203692435679</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>713.1262528103351</v>
+        <v>1169.256410661328</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>48.10856867095328</v>
+        <v>48.06188146604622</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>42.78015584943257</v>
+        <v>41.16234670236221</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9590875530162508</v>
+        <v>1.576709380783573</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1003,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1012,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1065382972466226</v>
+        <v>0.1080839821490107</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10653.82972466226</v>
+        <v>10808.39821490107</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1135370331433445</v>
+        <v>0.0768720785569736</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1209.604218552528</v>
+        <v>830.864036650928</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>94.87335182556761</v>
+        <v>425.0952530103654</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>80.93999710083007</v>
+        <v>369.0912375405512</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.270740662866885</v>
+        <v>1.182646788141987</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -1044,7 +1035,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1053,29 +1044,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09833656824386003</v>
+        <v>0.09261351611588012</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9833.656824386002</v>
+        <v>9261.351611588012</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0150053319741709</v>
+        <v>0.0426715939840771</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>147.5572851699831</v>
+        <v>395.1966357134618</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>376.820729495411</v>
+        <v>149.8319048735307</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>352.6875</v>
+        <v>136.1580975269861</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3001066394834209</v>
+        <v>0.8130455715182764</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1094,27 +1085,27 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09391563882388926</v>
+        <v>0.09145120548407606</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9391.563882388926</v>
+        <v>9145.120548407607</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.035964069170425</v>
+        <v>0.0433601726374674</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>337.7588530847005</v>
+        <v>396.5340057694044</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>306.6453644744458</v>
+        <v>42.08914952339957</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>277.2324952194509</v>
+        <v>38.0275160674077</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.5672232190119821</v>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
+        <v>0.7563941226758241</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1126,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1135,27 +1126,27 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07682233707188654</v>
+        <v>0.08643575323611709</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7682.233707188654</v>
+        <v>8643.575323611709</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0318627708566734</v>
+        <v>0.0224110782826734</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>244.7772522795647</v>
+        <v>193.7118432196461</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>107.313728169094</v>
+        <v>103.7747244456913</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>98.8</v>
+        <v>93.65398867082759</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.6372554171334678</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
+        <v>0.2899211268321331</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1208,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1252,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1294,7 +1285,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 13</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1437,45 +1428,45 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0420559802578865</v>
+        <v>-0.0253879091306941</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.0051604689344056</v>
+        <v>0</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.1156036872656343</v>
+        <v>0.0806432430018387</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>38.31776078968454</v>
+        <v>79.91819145128308</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>39.79358124262377</v>
+        <v>82</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>44.62414749062538</v>
+        <v>88.61274592615077</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>37.54126859386067</v>
+        <v>76.88061453211465</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>64.34999999999999</v>
+        <v>79.86</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1494,7 +1485,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -1503,28 +1494,28 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>45.5</v>
+        <v>43.84000015258789</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.0063614591608023</v>
+        <v>0.036245624409826</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.0573311795813907</v>
+        <v>0.09630203692435679</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.1855133537025062</v>
+        <v>0.2110552392681974</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>45.7894463918165</v>
+        <v>45.4290083322453</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>48.10856867095328</v>
+        <v>48.06188146604622</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>53.94085759346403</v>
+        <v>53.09266187431014</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>42.78015584943257</v>
+        <v>41.16234670236221</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1532,7 +1523,7 @@
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>64.34999999999999</v>
+        <v>79.86</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1541,64 +1532,64 @@
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0046916890080428</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0150053319741709</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1020951406282874</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>369.5082104557641</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>376.820729495411</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>409.1528209582517</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>352.6875</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>379</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.0037105180381591</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.0213779187417526</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.1020952413749239</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>377.5937136635377</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>387.1022312031242</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>417.6940964810962</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>360.05</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1608,168 +1599,168 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>394.75</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.065000031562885</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.0768720785569736</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.2234482270298656</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>369.0912375405512</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>425.0952530103654</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>482.9561876200395</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>369.0912375405512</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>331.75</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.0984893878053735</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>-0.0207253372334769</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.0602116203644447</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>299.0761455955673</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>324.874369372794</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>351.7252050559046</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>299.0761455955673</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>296</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.06340373236672001</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.035964069170425</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.07252410609256819</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>277.2324952194509</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>306.6453644744458</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>317.4671354034002</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>277.2324952194509</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>102.5999984741211</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0448028308183779</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>-0.0056462096211761</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.0559687682788319</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>98.00322810051922</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>102.0206973756039</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>108.3423940141277</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>97.46999855041503</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="D13" s="18" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.07730060422829969</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.0224110782826734</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.0947095426710635</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>93.65398867082759</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>103.7747244456913</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>111.113018581113</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>93.65398867082759</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>23.05999946594238</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0633746386509592</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>-0.0293355143063753</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.0814151454989152</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>21.59858033249697</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>22.38352252170423</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>24.93743267766699</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>21.56527333559732</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="M13" s="17" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1779,37 +1770,37 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>384</v>
+        <v>324.75</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0281690730134268</v>
+        <v>-0.0540366936779931</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.0149130710450822</v>
+        <v>-0.0276025019756407</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.08543155919911009</v>
+        <v>0.1251956377584677</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>373.1830759628441</v>
+        <v>307.2015837280717</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>389.7266192813116</v>
+        <v>315.7860874834107</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>416.8057187324583</v>
+        <v>365.4072833620624</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>359.9101054961429</v>
+        <v>307.2015837280717</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1817,7 +1808,7 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>64.34999999999999</v>
+        <v>79.86</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
@@ -1826,7 +1817,7 @@
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1827,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -1845,45 +1836,45 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>85.19999694824219</v>
+        <v>143.6999969482422</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>-0.0108077431499975</v>
+        <v>-0.0082889988742848</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.1135370331433445</v>
+        <v>0.0426715939840771</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1589867372070065</v>
+        <v>0.1446541396482852</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>84.27917726484502</v>
+        <v>142.5088678353035</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>94.87335182556761</v>
+        <v>149.8319048735307</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>98.74566647309014</v>
+        <v>164.4867963742514</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>80.93999710083007</v>
+        <v>136.1580975269861</v>
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M15" s="17" t="n">
-        <v>64.34999999999999</v>
+        <v>79.86</v>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O15" s="17" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1884,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -1902,278 +1893,107 @@
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>104</v>
+        <v>40.34000015258789</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>-0.0155083176665838</v>
+        <v>-0.0573248407643312</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>0.0318627708566734</v>
+        <v>0.0433601726374674</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.08243455158337749</v>
+        <v>0.0900858360358102</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>102.3871349626753</v>
+        <v>38.0275160674077</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>107.313728169094</v>
+        <v>42.08914952339957</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>112.5731933646713</v>
+        <v>43.97406279201848</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>98.8</v>
+        <v>38.0275160674077</v>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>113.1999969482422</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>-0.0669128100843053</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>-0.0163197887030124</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>0.0289375192237391</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>105.6254670509005</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>111.3525969168652</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>116.4757240360591</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>105.6254670509005</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="17" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>291.5</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-0.0386983355086648</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>-0.0070658820926857</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0.0471518681568155</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>280.2194351992242</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>289.4402953699822</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>305.2447695677117</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>276.925</v>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>89</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.09996593281665379</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0222670617351794</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0287358367126191</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>80.10303197931782</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>87.01823150556903</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>91.55748946742311</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>80.10303197931782</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif</t>
-        </is>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>63.70000076293945</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0615218226622063</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.004687488079071</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0.1090908628521543</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>59.78106061241949</v>
-      </c>
-      <c r="I19" s="24" t="n">
-        <v>63.40140776872636</v>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>70.64908880985141</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>59.66295737853054</v>
-      </c>
-      <c r="L19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="23" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N19" s="23" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O19" s="23" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>33.41999816894531</v>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.0659425781939114</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.0310153372448183</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>0.1010665940075984</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>31.21619732644926</v>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>32.38346565501426</v>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>36.79764355562079</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>31.21619732644926</v>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M20" s="23" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="N20" s="23" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O20" s="23" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+      <c r="M17" s="20" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O20"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2194,7 +2014,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -2203,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2220,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2297,30 +2117,30 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.1862395774600724</v>
+        <v>0.2893082070334623</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.2539185102925374</v>
+        <v>0.1498387665162419</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.6764458917342262</v>
+        <v>0.1786647061558695</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.041267190077997</v>
+        <v>-0.0033987981675275</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2328,10 +2148,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0307341425767416</v>
+        <v>0.0312157650480814</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>-0.0051604689344056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2340,7 +2160,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -2354,70 +2174,70 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.0046066414674543</v>
+        <v>0.3341448368317257</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.001115469846139</v>
+        <v>0.2604945857181591</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.235030926116428</v>
+        <v>0.1900108569762932</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.1566089169082498</v>
+        <v>-0.1319180036543813</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0305389306672666</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.09630203692435679</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.0299835584767572</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.1213361981009177</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.4228718885384146</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>8.364410914851739e-05</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0298883972589827</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0573311795813907</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0.0013486176668915</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.100815418828762</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.3632607485858201</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.1103780044876269</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0.023589744633299</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.0150053319741709</v>
+      <c r="J6" s="16" t="n">
+        <v>0.0211148533864321</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.0213779187417526</v>
       </c>
     </row>
     <row r="7">
@@ -2426,127 +2246,127 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.0371951219512195</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.1653136531365313</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.8699667862938347</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>-0.0591229013786693</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.0310679439959384</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.0768720785569736</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>0.09128289473684199</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0.1429801894918174</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>0.4539139831828924</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>-0.2081217061911366</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0.0274664472873233</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>-0.0207253372334769</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.0025273799494524</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>-0.0189264227791532</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.3768329115958089</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.1760804208636897</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="E9" s="19" t="n">
+        <v>0.1385305469740914</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.1143236885651519</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.209034702177757</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>-0.168874451564738</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0273607577956114</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.035964069170425</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.08474576386540381</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>-0.1506622857438071</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.1173328587488999</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>0.0313938948468988</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0219305756012054</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>-0.0056462096211761</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.07091056609677771</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.3013544220943314</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.35647055682014</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>-0.4658997689756274</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>0.0324095005412434</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>-0.0293355143063753</v>
+      <c r="J9" s="19" t="n">
+        <v>0.0258642813329788</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>0.0224110782826734</v>
       </c>
     </row>
     <row r="10">
@@ -2555,7 +2375,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2565,31 +2385,31 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.0975323149236192</v>
+        <v>0.1276041666666667</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>0.234726688102894</v>
+        <v>0.121761658031088</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>1.093784148197624</v>
+        <v>0.1713255184851216</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>-0.3248706883042701</v>
+        <v>-0.1612508758208084</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.0313670501352306</v>
+        <v>0.0228216736000703</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0.0149130710450822</v>
+        <v>-0.0276025019756407</v>
       </c>
     </row>
     <row r="11">
@@ -2598,12 +2418,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -2612,27 +2432,27 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.1310556420557422</v>
+        <v>0.1749795041904276</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.2569639003843752</v>
+        <v>0.106639870007295</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>-0.0072963800603302</v>
+        <v>0.0528665738737681</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>0.4702778794241973</v>
+        <v>-0.077726791774372</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.0232889396320691</v>
+        <v>0.0262418217864421</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.1135370331433445</v>
+        <v>0.0426715939840771</v>
       </c>
     </row>
     <row r="12">
@@ -2641,7 +2461,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2655,199 +2475,199 @@
         </is>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0739091970276476</v>
+        <v>0.0570968227884278</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.1231028554971428</v>
+        <v>0.4655377772831777</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>-0.0160832260863227</v>
+        <v>0.6648414617414236</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>-0.0886630889314125</v>
+        <v>-0.2714424364148385</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>0.0283049773444281</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>0.0433601726374674</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>0.0629107694670627</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0.0619136826322126</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.1418368479304974</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>-0.0617772476004407</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>0.0235147715905809</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>-0.0163197887030124</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0.0345423149419388</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>-0.1816940257117537</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>-0.0253416715336882</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.1964250089917667</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="19" t="n">
-        <v>0.0203560631794317</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>0.0318627708566734</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="J14" s="24" t="n">
+        <v>0.022792917168649</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.1212597571915075</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0731319554848967</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>-0.0642054574638844</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.068744271310724</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>-0.1125189107212077</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>0.0231561831887904</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>-0.0070658820926857</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>0.0368033654695845</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>0.0517905800698297</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0.1804573492762724</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.2199378275196667</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>0.0216298884764837</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0194030930076112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
-        <v>-0.0805734197027545</v>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>-0.0596758909696701</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>0.1458106229539508</v>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-0.2599604463071995</v>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="E16" s="24" t="n">
+        <v>0.08566325623817581</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>0.028169014084507</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>-0.1479925182067204</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.2301355434142047</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="27" t="n">
-        <v>0.0209928798538189</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>0.0070464703305382</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>-0.0723436224182088</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.218580848518051</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.07793667413424429</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-0.0069595372522321</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0279986421832064</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>0.0063124281375852</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="27" t="n">
-        <v>-0.1110708025535955</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>0.1808376609273443</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0.3087414111063782</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-0.4371995375985574</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="27" t="n">
-        <v>0.0254253869317556</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.0179805767303264</v>
+      <c r="J16" s="24" t="n">
+        <v>0.0217920353963226</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.009701613552635499</v>
       </c>
     </row>
     <row r="17">
@@ -2856,7 +2676,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -2866,31 +2686,31 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0743629892086322</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.1387634300955811</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>0.1041495071207343</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.137952192271936</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>0.0371797344514563</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>0.0601449391773718</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>0.2087071438141818</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.2858393418307774</v>
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>0.02615590712964</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>-0.0222670617351794</v>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0297976459536277</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0146819384378131</v>
       </c>
     </row>
     <row r="18">
@@ -2899,7 +2719,7 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -2909,31 +2729,31 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.1356851641707055</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.2830794788478351</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0153144390476849</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>0.1238362901154654</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>-0.0921431863137641</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.1285291334718965</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.2445853017245718</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.3396670676475924</v>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0316879382736025</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>-0.004687488079071</v>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>0.023247051091997</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.1002252478096075</v>
       </c>
     </row>
     <row r="19">
@@ -2942,7 +2762,7 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -2952,74 +2772,74 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0858862988621121</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.2407996860197412</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.053257821777556</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.0414981713743457</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>-0.0096061480754833</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.1188034318451188</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-0.0427112219541819</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.2797685248578938</v>
       </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0305942800876695</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>-0.0310153372448183</v>
+      <c r="J19" s="24" t="n">
+        <v>0.0178839124827152</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.0999999916062814</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
-        <v>-0.0597432263673228</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>-0.167161244124102</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>-0.1621890850921175</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-0.2601417240448666</v>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>0.0215890519221315</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>0.0408327384185252</v>
+      <c r="E20" s="24" t="n">
+        <v>-0.1274762778640684</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.0029527296674942</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0.2016607055424879</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.3414386978886042</v>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>0.0296807094607482</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0.0999999916062814</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +2864,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3052,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3077,7 +2897,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS, BIMAS.IS, TOASO.IS, FROTO.IS, ARCLK.IS</t>
+          <t>YKBNK.IS, ASELS.IS, SAHOL.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -3089,7 +2909,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>AKBNK.IS, BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -3101,7 +2921,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, TCELL.IS, PETKM.IS, THYAO.IS, SAHOL.IS, AKBNK.IS, YKBNK.IS</t>
+          <t>TOASO.IS, THYAO.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -3113,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, GARAN.IS, TUPRS.IS, PGSUS.IS</t>
+          <t>FROTO.IS, KCHOL.IS, PGSUS.IS, SISE.IS, TUPRS.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -3125,7 +2945,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3163,7 +2983,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3171,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3208,7 +3028,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3040,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3052,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3064,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3076,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3088,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3136,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3148,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3184,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3208,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3234,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3422,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3446,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13704</v>
+        <v>14729.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3456,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12248.34019042969</v>
+        <v>12472.33203125</v>
       </c>
     </row>
     <row r="6">
@@ -3490,7 +3310,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>64.34999999999999</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="9">
@@ -3517,23 +3337,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-01</t>
+          <t>Rapor Tarihi: 2026-06-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3547,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-23 05:57</t>
+          <t>Son Güncelleme: 2026-06-24 01:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3611,23 +3431,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>168.3999938964844</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>0</v>
+      <c r="D4" s="25" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.08372925543086951</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>837.2925543086967</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="5">
@@ -3641,23 +3461,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>244.8999938964844</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>0</v>
+      <c r="D5" s="25" t="n">
+        <v>220.6999969482422</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.09881583320280196</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-988.1583320280206</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="6">
@@ -3671,23 +3491,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>123.0999984741211</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>0</v>
+      <c r="D6" s="25" t="n">
+        <v>143.6999969482422</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.1673436127495302</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1673.436127495303</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="7">
@@ -3701,23 +3521,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>104</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>104</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>0</v>
+      <c r="D7" s="25" t="n">
+        <v>103.0999984741211</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.008653860825758697</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-86.53860825758602</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="8">
@@ -3731,23 +3551,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="25" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0</v>
+      <c r="D8" s="25" t="n">
+        <v>89.84999847412109</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.05457748465300671</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>545.7748465300665</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="9">
@@ -3761,23 +3581,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="25" t="n">
         <v>45.5</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>0</v>
+      <c r="D9" s="25" t="n">
+        <v>46.31999969482422</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.01802197131481797</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>540.6591394445386</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="10">
@@ -3791,29 +3611,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="25" t="n">
         <v>371.25</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>0</v>
+      <c r="D10" s="25" t="n">
+        <v>379</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.02087542087542094</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>626.2626262626254</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3821,57 +3641,117 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
-        <v>296</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>296</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>0</v>
+      <c r="C11" s="25" t="n">
+        <v>384</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>394.75</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.02799479166666674</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>839.84375</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>0.0748467743222782</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>384</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>384</v>
-      </c>
-      <c r="E12" s="29" t="n">
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="E12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="28" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="H12" s="29" t="n">
+      <c r="G12" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>0.0748467743222782</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="E13" s="26" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H13" s="26" t="n">
+        <v>0.0748467743222782</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>2277611.882914566</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0.0748467743222782</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H12"/>
+  <autoFilter ref="A3:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YONETICI_OZETI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOY_ONERISI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ILK_20_SIRALAMA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AL_SAT_OZET" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOY_DEGISIMI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIYASA_REJIMI" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="YONETICI_OZETI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PORTFOY_ONERISI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ILK_20_SIRALAMA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AL_SAT_OZET" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PORTFOY_DEGISIMI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PIYASA_REJIMI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1012,7 +1012,7 @@
         <v>0.0768720785569736</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>830.864036650928</v>
+        <v>830.8640366509281</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>425.0952530103654</v>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09261351611588012</v>
+        <v>0.09261351611588006</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9261.351611588012</v>
+        <v>9261.351611588007</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>395.1966357134618</v>
+        <v>395.1966357134597</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>149.8319048735307</v>
@@ -1062,7 +1062,7 @@
         <v>136.1580975269861</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.8130455715182764</v>
+        <v>0.8130455715182726</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09145120548407606</v>
+        <v>0.09145120548407609</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9145.120548407607</v>
+        <v>9145.120548407609</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0433601726374674</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.5340057694044</v>
+        <v>396.5340057694045</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>42.08914952339957</v>
@@ -1103,7 +1103,7 @@
         <v>38.0275160674077</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.7563941226758241</v>
+        <v>0.7563941226758264</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1560,7 +1560,7 @@
         <v>0.0213779187417526</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1020952413749239</v>
+        <v>0.1020952413749238</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>377.5937136635377</v>
@@ -1842,7 +1842,7 @@
         <v>-0.0082889988742848</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>0.1446541396482852</v>
@@ -1896,7 +1896,7 @@
         <v>40.34000015258789</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>-0.0573248407643312</v>
+        <v>-0.057324840764331</v>
       </c>
       <c r="F16" s="19" t="n">
         <v>0.0433601726374674</v>
@@ -1953,16 +1953,16 @@
         <v>113.1999969482422</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.0669128100843053</v>
+        <v>-0.0669128100843052</v>
       </c>
       <c r="F17" s="22" t="n">
         <v>-0.0163197887030124</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>0.0289375192237391</v>
+        <v>0.0289375192237388</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>105.6254670509005</v>
+        <v>105.6254670509006</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>111.3525969168652</v>
@@ -1971,7 +1971,7 @@
         <v>116.4757240360591</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>105.6254670509005</v>
+        <v>105.6254670509006</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-0.0299835584767572</v>
+        <v>-0.0299835584767574</v>
       </c>
       <c r="F6" s="16" t="n">
         <v>0.1213361981009177</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0211148533864321</v>
+        <v>0.0211148533864322</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0213779187417526</v>
@@ -2266,7 +2266,7 @@
         <v>0.1653136531365313</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.8699667862938347</v>
+        <v>0.8699667862938349</v>
       </c>
       <c r="H7" s="19" t="n">
         <v>-0.0591229013786693</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.0310679439959384</v>
+        <v>0.0310679439959383</v>
       </c>
       <c r="K7" s="19" t="n">
         <v>0.0768720785569736</v>
@@ -2309,7 +2309,7 @@
         <v>0.1429801894918174</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>0.4539139831828924</v>
+        <v>0.4539139831828926</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>-0.2081217061911366</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.0228216736000703</v>
+        <v>0.0228216736000704</v>
       </c>
       <c r="K10" s="22" t="n">
         <v>-0.0276025019756407</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.1749795041904276</v>
+        <v>0.1749795041904278</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>0.106639870007295</v>
@@ -2452,7 +2452,7 @@
         <v>0.0262418217864421</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.0570968227884278</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>0.4655377772831777</v>
+        <v>0.4655377772831774</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0.6648414617414236</v>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0.0629107694670627</v>
+        <v>0.06291076946706289</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0619136826322126</v>
+        <v>0.0619136826322128</v>
       </c>
       <c r="G13" s="22" t="n">
         <v>0.1418368479304974</v>
@@ -2564,10 +2564,10 @@
         <v>0.0345423149419388</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.1816940257117537</v>
+        <v>-0.1816940257117536</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.0253416715336882</v>
+        <v>-0.025341671533688</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>0.1964250089917667</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.022792917168649</v>
+        <v>0.0227929171686489</v>
       </c>
       <c r="K14" s="24" t="n">
         <v>0.1212597571915075</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0216298884764837</v>
+        <v>0.0216298884764838</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>0.0194030930076112</v>
@@ -2667,7 +2667,7 @@
         <v>0.0217920353963226</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.009701613552635499</v>
+        <v>0.0097016135526356</v>
       </c>
     </row>
     <row r="17">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.0371797344514563</v>
+        <v>0.0371797344514566</v>
       </c>
       <c r="F17" s="24" t="n">
         <v>0.0601449391773718</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.2087071438141818</v>
+        <v>0.2087071438141816</v>
       </c>
       <c r="H17" s="24" t="n">
         <v>-0.2858393418307774</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>-0.0921431863137641</v>
+        <v>-0.092143186313764</v>
       </c>
       <c r="F18" s="24" t="n">
         <v>-0.1285291334718965</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.023247051091997</v>
+        <v>0.0232470510919971</v>
       </c>
       <c r="K18" s="24" t="n">
         <v>0.1002252478096075</v>
@@ -2782,7 +2782,7 @@
         <v>-0.1188034318451188</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>-0.0427112219541819</v>
+        <v>-0.042711221954182</v>
       </c>
       <c r="H19" s="24" t="n">
         <v>-0.2797685248578938</v>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>-0.1274762778640684</v>
+        <v>-0.1274762778640682</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>-0.0029527296674942</v>
+        <v>-0.0029527296674941</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>0.2016607055424879</v>
+        <v>0.2016607055424881</v>
       </c>
       <c r="H20" s="24" t="n">
         <v>-0.3414386978886042</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14729.7001953125</v>
+        <v>14539.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12472.33203125</v>
+        <v>12490.64252929687</v>
       </c>
     </row>
     <row r="6">
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3444,7 +3444,7 @@
         <v>837.2925543086967</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3474,7 +3474,7 @@
         <v>-988.1583320280206</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3504,7 +3504,7 @@
         <v>1673.436127495303</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3534,7 +3534,7 @@
         <v>-86.53860825758602</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3564,7 +3564,7 @@
         <v>545.7748465300665</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3594,7 +3594,7 @@
         <v>540.6591394445386</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H9" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3624,7 +3624,7 @@
         <v>626.2626262626254</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H10" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3654,7 +3654,7 @@
         <v>839.84375</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H11" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H12" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H13" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H14" s="26" t="n">
         <v>0.0748467743222782</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -101,7 +101,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,10 +157,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 79.86/100</t>
+          <t>Güven Puanı: 73.60/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: YKBNK.IS, ASELS.IS, GARAN.IS, EREGL.IS, SAHOL.IS</t>
+          <t>AL: TOASO.IS, YKBNK.IS, BIMAS.IS, ASELS.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: AKBNK.IS, BIMAS.IS</t>
+          <t>AZALT: SAHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TOASO.IS, THYAO.IS, TCELL.IS</t>
+          <t>ÇIK: AKBNK.IS, THYAO.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -960,29 +960,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1214155430149161</v>
+        <v>0.1307302687242327</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12141.55430149161</v>
+        <v>13073.02687242327</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.09630203692435679</v>
+        <v>0.113974231337216</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1169.256410661328</v>
+        <v>1489.988189035211</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>48.06188146604622</v>
+        <v>379.8652128859907</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>41.16234670236221</v>
+        <v>322.2593373090542</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.576709380783573</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>2.073844107165309</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +1003,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1080839821490107</v>
+        <v>0.0998691936961647</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10808.39821490107</v>
+        <v>9986.919369616471</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0768720785569736</v>
+        <v>0.0618296226277728</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>830.8640366509281</v>
+        <v>617.487455837381</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>425.0952530103654</v>
+        <v>45.36136277483719</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>369.0912375405512</v>
+        <v>40.14256602612377</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.182646788141987</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>1.024802314987066</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,27 +1044,27 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09261351611588006</v>
+        <v>0.09969335669182537</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9261.351611588007</v>
+        <v>9969.335669182537</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0426715939840769</v>
+        <v>0.0485935360435065</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>395.1966357134597</v>
+        <v>484.4452721702366</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>149.8319048735307</v>
+        <v>392.1739824802714</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>136.1580975269861</v>
+        <v>355.3</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.8130455715182726</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+        <v>0.9718707208701307</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,27 +1085,27 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09145120548407609</v>
+        <v>0.0906900110283438</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9145.120548407609</v>
+        <v>9069.00110283438</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0433601726374674</v>
+        <v>0.07687195361889949</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.5340057694045</v>
+        <v>697.1518321468328</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>42.08914952339957</v>
+        <v>395.7504429549456</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>38.0275160674077</v>
+        <v>344.1830118399116</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.7563941226758264</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
+        <v>1.21158199167857</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1126,29 +1126,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08643575323611709</v>
+        <v>0.07901716985943352</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8643.575323611709</v>
+        <v>7901.716985943352</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0224110782826734</v>
+        <v>0.0417778692166073</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>193.7118432196461</v>
+        <v>330.1168988253858</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>103.7747244456913</v>
+        <v>41.60860666584711</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>93.65398867082759</v>
+        <v>37.71171418264627</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.2899211268321331</v>
+        <v>0.7488308072984767</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1428,45 +1428,45 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0253879091306941</v>
+        <v>-0.0124320701318719</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0</v>
+        <v>0.113974231337216</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0806432430018387</v>
+        <v>0.1171875590725464</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>79.91819145128308</v>
+        <v>336.7606640850317</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>82</v>
+        <v>379.8652128859907</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>88.61274592615077</v>
+        <v>380.9609576437383</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>76.88061453211465</v>
+        <v>322.2593373090542</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>79.86</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>volatilite yüksek</t>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
@@ -1485,45 +1485,45 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>43.84000015258789</v>
+        <v>80.94999694824219</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.036245624409826</v>
+        <v>-0.0253879955685062</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.09630203692435679</v>
+        <v>-0.0223284441988289</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.2110552392681974</v>
+        <v>0.0657353767474502</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>45.4290083322453</v>
+        <v>78.89483878444962</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>48.06188146604622</v>
+        <v>79.14250945848799</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>53.09266187431014</v>
+        <v>86.27127549533984</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>41.16234670236221</v>
+        <v>75.95247007238704</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>79.86</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1547,32 +1547,32 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-0.0037105180381591</v>
+        <v>-0.0037036590902302</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0213779187417526</v>
+        <v>0.0485935360435065</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1020952413749238</v>
+        <v>0.1185388109715825</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>377.5937136635377</v>
+        <v>372.6148315002539</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>387.1022312031242</v>
+        <v>392.1739824802714</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>417.6940964810962</v>
+        <v>418.3335153033719</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>360.05</v>
+        <v>355.3</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>79.86</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
@@ -1589,64 +1589,64 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>394.75</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.065000031562885</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0768720785569736</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.2234482270298656</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>369.0912375405512</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>425.0952530103654</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>482.9561876200395</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>369.0912375405512</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>42.72000122070312</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0618296226277728</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.2319541705328982</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>42.77293923881896</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>45.36136277483719</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>52.62908366901572</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>40.14256602612377</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
@@ -1656,339 +1656,339 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>99.80000305175781</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.07730059814576069</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0224110802475061</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.0947095779071925</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>92.08540312090818</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>102.0366289288521</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>109.2520192159263</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>92.08540312090818</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>140.3999938964844</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0371959299442395</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.1446540636846061</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>135.1776855593391</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>145.0496817236391</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>160.7094235549047</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>133.0903323025352</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n">
-        <v>331.75</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.0984893878053735</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>-0.0207253372334769</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.0602116203644447</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>299.0761455955673</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>324.874369372794</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>351.7252050559046</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>299.0761455955673</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="D14" s="18" t="n">
+        <v>324.75</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.0540366936779931</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>-0.0276025019756407</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.1251956377584677</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>307.2015837280717</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>315.7860874834107</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>365.4072833620624</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>307.2015837280717</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="M14" s="17" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="O14" s="17" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.07730060422829969</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0.0224110782826734</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.0947095426710635</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>93.65398867082759</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>103.7747244456913</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>111.113018581113</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>93.65398867082759</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="D15" s="15" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0197860443083401</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.07687195361889949</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.1760201976314832</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>360.228628716685</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>395.7504429549456</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>432.1874226295701</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>344.1830118399116</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>39.93999862670898</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.0535298595992588</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>0.1506617105180202</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>37.80201610782666</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>41.60860666584711</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>45.95742713789633</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>37.71171418264627</v>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>110.4000015258789</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0448029022074474</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>-0.005646063733711</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.0564225877402071</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>105.4537610538129</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>109.776676081062</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>116.6290552984918</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>104.880001449585</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="17" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M17" s="17" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>324.75</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.0540366936779931</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.0276025019756407</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>0.1251956377584677</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>307.2015837280717</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>315.7860874834107</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>365.4072833620624</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>307.2015837280717</v>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="20" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>143.6999969482422</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0082889988742848</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>0.0426715939840769</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1446541396482852</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>142.5088678353035</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>149.8319048735307</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>164.4867963742514</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>136.1580975269861</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O17" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>-0.057324840764331</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0.0433601726374674</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.0900858360358102</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>38.0275160674077</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>42.08914952339957</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>43.97406279201848</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>38.0275160674077</v>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>113.1999969482422</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-0.0669128100843052</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>-0.0163197887030124</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>0.0289375192237388</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>105.6254670509006</v>
-      </c>
-      <c r="I17" s="21" t="n">
-        <v>111.3525969168652</v>
-      </c>
-      <c r="J17" s="21" t="n">
-        <v>116.4757240360591</v>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>105.6254670509006</v>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -2023,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2117,30 +2117,30 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.2893082070334623</v>
+        <v>0.1520270270270269</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.1498387665162419</v>
+        <v>0.2343891402714932</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1786647061558695</v>
+        <v>0.5061859179640755</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.0033987981675275</v>
+        <v>-0.0620502802037067</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0312157650480814</v>
+        <v>0.0274789775527064</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0</v>
+        <v>0.113974231337216</v>
       </c>
     </row>
     <row r="5">
@@ -2160,30 +2160,30 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.3341448368317257</v>
+        <v>0.2648437023162842</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.2604945857181591</v>
+        <v>0.1883992424013323</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.1900108569762932</v>
+        <v>0.1611463683499709</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-0.1319180036543813</v>
+        <v>0.0093434679284629</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0305389306672666</v>
+        <v>0.0308679868082667</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.09630203692435679</v>
+        <v>-0.0223284441988289</v>
       </c>
     </row>
     <row r="6">
@@ -2208,25 +2208,25 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-0.0299835584767574</v>
+        <v>0.007903276014288699</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.1213361981009177</v>
+        <v>0.1172300876081426</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.4228718885384146</v>
+        <v>0.3720727848721288</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>8.364410914851739e-05</v>
+        <v>0.0018174454223327</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
@@ -2234,53 +2234,53 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0211148533864322</v>
+        <v>0.0200057366856013</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.0213779187417526</v>
+        <v>0.0485935360435065</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.0371951219512195</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.1653136531365313</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.8699667862938349</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.0591229013786693</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0310679439959383</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.0768720785569736</v>
+      <c r="E7" s="16" t="n">
+        <v>0.2882991983498788</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.2813437620031669</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.1627653584387609</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>-0.1048897377237305</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.0301666095614514</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.0618296226277728</v>
       </c>
     </row>
     <row r="8">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2299,246 +2299,246 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>0.0847826418669328</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0.12733028666848</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>0.2254181658484089</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>-0.1643341226904812</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0.025561376483624</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0.0224110802475061</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>0.1423921249254054</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>0.1236438124239507</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>0.0265193008972899</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.07591110266928219</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0.0260315595146627</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="22" t="n">
-        <v>0.09128289473684199</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.1429801894918174</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0.4539139831828926</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-0.2081217061911366</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="E10" s="19" t="n">
+        <v>0.0943555181128896</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.115979381443299</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.2005545286506469</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>-0.1251371753354518</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0274664472873233</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>-0.0207253372334769</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="J10" s="19" t="n">
+        <v>0.0225951356495294</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>-0.0276025019756407</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0335305719921104</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0440340909090908</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.6576454896650092</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>-0.0338091592783363</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0.0317237934150863</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.07687195361889949</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E9" s="19" t="n">
-        <v>0.1385305469740914</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.1143236885651519</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.209034702177757</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>-0.168874451564738</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="E12" s="16" t="n">
+        <v>0.0332583869591531</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.4572736495013934</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.6825878864316</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>-0.2828998656094119</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="19" t="n">
-        <v>0.0258642813329788</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>0.0224110782826734</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="J12" s="16" t="n">
+        <v>0.0278953996079083</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
-        <v>0.1276041666666667</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0.121761658031088</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0.1713255184851216</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>-0.1612508758208084</v>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0.0228216736000704</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>-0.0276025019756407</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.1749795041904278</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.106639870007295</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.0528665738737681</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>-0.077726791774372</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0.0262418217864421</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>0.0426715939840769</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>0.0570968227884278</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.4655377772831774</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.6648414617414236</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>-0.2714424364148385</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>0.0283049773444281</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>0.0433601726374674</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>0.06291076946706289</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>0.0619136826322128</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.1418368479304974</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>-0.0617772476004407</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>0.0235147715905809</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>-0.0163197887030124</v>
+      <c r="E13" s="19" t="n">
+        <v>0.09306932203840509</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.0395480668392451</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.1395436359873534</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-0.0694254310609957</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.0234306483748489</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>-0.005646063733711</v>
       </c>
     </row>
     <row r="14">
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.0345423149419388</v>
+        <v>0.0273320900850602</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.1816940257117536</v>
+        <v>-0.1703454944323723</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.025341671533688</v>
+        <v>-0.0532876173492593</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.1964250089917667</v>
+        <v>0.07232629600781371</v>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.0227929171686489</v>
+        <v>0.0223939659314638</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.1212597571915075</v>
+        <v>0.1135371380632046</v>
       </c>
     </row>
     <row r="15">
@@ -2604,16 +2604,16 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.0368033654695845</v>
+        <v>0.0206239755188029</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.0517905800698297</v>
+        <v>0.0565500735457435</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.1804573492762724</v>
+        <v>0.1889325281188845</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.2199378275196667</v>
+        <v>-0.1669482240085698</v>
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0216298884764838</v>
+        <v>0.0216241237124125</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.0194030930076112</v>
+        <v>0.0101985587659065</v>
       </c>
     </row>
     <row r="16">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -2647,16 +2647,16 @@
         </is>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.08566325623817581</v>
+        <v>-0.0024857082952425</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.028169014084507</v>
+        <v>-0.0369697362167155</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.1479925182067204</v>
+        <v>0.1928499793165377</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.2301355434142047</v>
+        <v>-0.248942220376036</v>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.0217920353963226</v>
+        <v>0.0269977226067913</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.0097016135526356</v>
+        <v>0.0236686907772818</v>
       </c>
     </row>
     <row r="17">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -2690,27 +2690,27 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.0371797344514566</v>
+        <v>0.0405643365602546</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.0601449391773718</v>
+        <v>-0.0111731843575418</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.2087071438141816</v>
+        <v>-0.144927536231884</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.2858393418307774</v>
+        <v>-0.2142556690014324</v>
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.0297976459536277</v>
+        <v>0.0217735937019796</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.0146819384378131</v>
+        <v>0.0201109476789529</v>
       </c>
     </row>
     <row r="18">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>-0.092143186313764</v>
+        <v>-0.1194570702003535</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.1285291334718965</v>
+        <v>-0.0046035885473222</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>0.2445853017245718</v>
+        <v>0.177253374235748</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.3396670676475924</v>
+        <v>-0.281034324338977</v>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.0232470510919971</v>
+        <v>0.0295961492730896</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.1002252478096075</v>
+        <v>0.1002252939750626</v>
       </c>
     </row>
     <row r="19">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -2776,27 +2776,27 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-0.0096061480754833</v>
+        <v>-0.0821337601487582</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>-0.1188034318451188</v>
+        <v>-0.1629343511515142</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>-0.042711221954182</v>
+        <v>0.218631394109467</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>-0.2797685248578938</v>
+        <v>-0.3129650864918111</v>
       </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.0178839124827152</v>
+        <v>0.0231757749170699</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.0999999916062814</v>
+        <v>0.1009728283635982</v>
       </c>
     </row>
     <row r="20">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -2819,27 +2819,27 @@
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>-0.1274762778640682</v>
+        <v>-0.0279652264399948</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>-0.0029527296674941</v>
+        <v>-0.1157894469144051</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>0.2016607055424881</v>
+        <v>-0.0344827435010018</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.3414386978886042</v>
+        <v>-0.260438572511438</v>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.0296807094607482</v>
+        <v>0.0178536031006538</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.0999999916062814</v>
+        <v>0.1000000839371915</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2864,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, ASELS.IS, SAHOL.IS, GARAN.IS, EREGL.IS</t>
+          <t>TOASO.IS, BIMAS.IS, YKBNK.IS, ASELS.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BIMAS.IS</t>
+          <t>SAHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, THYAO.IS, TCELL.IS</t>
+          <t>AKBNK.IS, THYAO.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, KCHOL.IS, PGSUS.IS, SISE.IS, TUPRS.IS, ARCLK.IS, PETKM.IS</t>
+          <t>FROTO.IS, KCHOL.IS, SISE.IS, PGSUS.IS, PETKM.IS, TUPRS.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.74 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14539.599609375</v>
+        <v>14331.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12490.64252929687</v>
+        <v>12508.61002929688</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>79.86</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3337,7 +3337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3353,7 +3353,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-22</t>
+          <t>Rapor Tarihi: 2026-06-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 05:56</t>
+          <t>Son Güncelleme: 2026-06-25 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3435,19 +3435,19 @@
         <v>168.3999938964844</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>182.5</v>
+        <v>177</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>0.08372925543086951</v>
+        <v>0.05106892170555577</v>
       </c>
       <c r="F4" s="25" t="n">
-        <v>837.2925543086967</v>
+        <v>510.6892170555566</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="5">
@@ -3465,19 +3465,19 @@
         <v>244.8999938964844</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>220.6999969482422</v>
+        <v>216.8000030517578</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>-0.09881583320280196</v>
+        <v>-0.1147406759699799</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>-988.1583320280206</v>
+        <v>-1147.406759699801</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="6">
@@ -3495,19 +3495,19 @@
         <v>123.0999984741211</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>143.6999969482422</v>
+        <v>140.3999938964844</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0.1673436127495302</v>
+        <v>0.1405361140276553</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>1673.436127495303</v>
+        <v>1405.361140276553</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="7">
@@ -3525,19 +3525,19 @@
         <v>104</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>103.0999984741211</v>
+        <v>100.8000030517578</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>-0.008653860825758697</v>
+        <v>-0.03076920142540562</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-86.53860825758602</v>
+        <v>-307.6920142540566</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="8">
@@ -3555,19 +3555,19 @@
         <v>85.19999694824219</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>89.84999847412109</v>
+        <v>86.44999694824219</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>0.05457748465300671</v>
+        <v>0.01467136202785735</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>545.7748465300665</v>
+        <v>146.7136202785732</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="9">
@@ -3585,19 +3585,19 @@
         <v>45.5</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>46.31999969482422</v>
+        <v>45.09999847412109</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>0.01802197131481797</v>
+        <v>-0.008791242327008897</v>
       </c>
       <c r="F9" s="25" t="n">
-        <v>540.6591394445386</v>
+        <v>-263.7372698102699</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="10">
@@ -3615,19 +3615,19 @@
         <v>371.25</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>0.02087542087542094</v>
+        <v>0.007407407407407307</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>626.2626262626254</v>
+        <v>222.222222222219</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="11">
@@ -3645,19 +3645,19 @@
         <v>384</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>394.75</v>
+        <v>367.5</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>0.02799479166666674</v>
+        <v>-0.04296875</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>839.84375</v>
+        <v>-1289.0625</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="12">
@@ -3675,19 +3675,19 @@
         <v>43.84000015258789</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>43.84000015258789</v>
+        <v>42.72000122070312</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0</v>
+        <v>-0.02554742080261263</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>0</v>
+        <v>-18169.52418518253</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="13">
@@ -3705,19 +3705,19 @@
         <v>101.5</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>101.5</v>
+        <v>99.80000305175781</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>0</v>
+        <v>-0.01674873840632696</v>
       </c>
       <c r="F13" s="25" t="n">
-        <v>0</v>
+        <v>-11911.83289680385</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>2311235.193725377</v>
+        <v>2269390.190761669</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>0.0748467743222782</v>
+        <v>0.045767673329867</v>
       </c>
     </row>
     <row r="14">
@@ -3735,23 +3735,53 @@
         <v>40.34000015258789</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>40.34000015258789</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="E14" s="26" t="n">
+        <v>-0.009915754198460136</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-7052.161434034933</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>2269390.190761669</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0.045767673329867</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>341</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>341</v>
+      </c>
+      <c r="E15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F15" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="25" t="n">
-        <v>2311235.193725377</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.0748467743222782</v>
+      <c r="G15" s="25" t="n">
+        <v>2269390.190761669</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>0.045767673329867</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H14"/>
+  <autoFilter ref="A3:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,7 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +197,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +689,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 73.60/100</t>
+          <t>Güven Puanı: 73.39/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +749,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, YKBNK.IS, BIMAS.IS, ASELS.IS, EREGL.IS</t>
+          <t>AL: TOASO.IS, BIMAS.IS, ASELS.IS, YKBNK.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +766,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: SAHOL.IS, GARAN.IS</t>
+          <t>AZALT: AKBNK.IS, THYAO.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +783,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: AKBNK.IS, THYAO.IS, TCELL.IS</t>
+          <t>ÇIK: TCELL.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -960,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1307302687242327</v>
+        <v>0.1289731132681991</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13073.02687242327</v>
+        <v>12897.31132681991</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.113974231337216</v>
+        <v>0.115580752659782</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1489.988189035211</v>
+        <v>1490.680950441377</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>379.8652128859907</v>
+        <v>374.2773425173569</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>322.2593373090542</v>
+        <v>316.9899217139279</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.073844107165309</v>
+        <v>2.094931308126066</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -994,7 +1003,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.0998691936961647</v>
+        <v>0.1011527915019432</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9986.919369616471</v>
+        <v>10115.27915019432</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0618296226277728</v>
+        <v>0.0495151050042483</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>617.487455837381</v>
+        <v>500.8591092691555</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>45.36136277483719</v>
+        <v>394.0929219290953</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>40.14256602612377</v>
+        <v>356.725</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.024802314987066</v>
+        <v>0.9903021000849659</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1035,7 +1044,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,29 +1053,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09969335669182537</v>
+        <v>0.09889355190160248</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9969.335669182537</v>
+        <v>9889.355190160248</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.09195762956560349</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>484.4452721702366</v>
+        <v>909.4016612194343</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>392.1739824802714</v>
+        <v>407.8461746427529</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>355.3</v>
+        <v>350.1116022986699</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718707208701307</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.468513366385918</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,25 +1094,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.0906900110283438</v>
+        <v>0.09217028756482212</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9069.00110283438</v>
+        <v>9217.028756482212</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.07687195361889949</v>
+        <v>0.0576923532547533</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>697.1518321468328</v>
+        <v>531.7520789781913</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>395.7504429549456</v>
+        <v>42.83654030681751</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>344.1830118399116</v>
+        <v>37.99627980287145</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.21158199167857</v>
+        <v>0.9332274067594398</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1117,7 +1126,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1126,25 +1135,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07901716985943352</v>
+        <v>0.07881025576343306</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7901.716985943352</v>
+        <v>7881.025576343306</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0417778692166073</v>
+        <v>0.0615384684378439</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>330.1168988253858</v>
+        <v>484.9862436876431</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>41.60860666584711</v>
+        <v>102.9692314384709</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>37.71171418264627</v>
+        <v>91.99443421817186</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.7488308072984767</v>
+        <v>1.192518827769908</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1199,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1222,7 +1231,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1285,7 +1294,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1437,28 +1446,28 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>341</v>
+        <v>335.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0124320701318719</v>
+        <v>0.08979294277640611</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.113974231337216</v>
+        <v>0.115580752659782</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.1171875590725464</v>
+        <v>0.2375061062526389</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>336.7606640850317</v>
+        <v>365.6255323014843</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>379.8652128859907</v>
+        <v>374.2773425173569</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>380.9609576437383</v>
+        <v>415.1832986477604</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>322.2593373090542</v>
+        <v>316.9899217139279</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1466,7 +1475,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>73.59999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1490,32 +1499,32 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>80.94999694824219</v>
+        <v>77.19999694824219</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>-0.0253879955685062</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>-0.0223284441988289</v>
+        <v>0</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.0657353767474502</v>
+        <v>0.08064316590219429</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>78.89483878444962</v>
+        <v>75.24004376783152</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>79.14250945848799</v>
+        <v>77.19999694824219</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>86.27127549533984</v>
+        <v>83.42564910978817</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>75.95247007238704</v>
+        <v>72.33902467510369</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1523,7 +1532,7 @@
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>73.59999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1551,28 +1560,28 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>374</v>
+        <v>375.5</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-0.0037036590902302</v>
+        <v>0.007965308684240601</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0495151050042483</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1185388109715825</v>
+        <v>0.1219923730948281</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>372.6148315002539</v>
+        <v>378.4909734109323</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>392.1739824802714</v>
+        <v>394.0929219290953</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>418.3335153033719</v>
+        <v>421.3081360971079</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>355.3</v>
+        <v>356.725</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
@@ -1580,7 +1589,7 @@
         </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>73.59999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
@@ -1608,28 +1617,28 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>42.72000122070312</v>
+        <v>40.5</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.0012391857819089</v>
+        <v>-0.0277778108086147</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0618296226277728</v>
+        <v>0.0576923532547533</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.2319541705328982</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>42.77293923881896</v>
+        <v>39.3749986622511</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>45.36136277483719</v>
+        <v>42.83654030681751</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>52.62908366901572</v>
+        <v>49.89414390658238</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>40.14256602612377</v>
+        <v>37.99627980287145</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1637,7 +1646,7 @@
         </is>
       </c>
       <c r="M11" s="14" t="n">
-        <v>73.59999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1651,116 +1660,116 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n">
-        <v>99.80000305175781</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.07730059814576069</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0224110802475061</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.0947095779071925</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>92.08540312090818</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>102.0366289288521</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>109.2520192159263</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>92.08540312090818</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="D12" s="18" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.0511886546061877</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.003753763602968</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.0948783870299643</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>311.6845269618673</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>329.733111343575</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>359.6675501393433</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>311.6845269618673</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="M12" s="17" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="O12" s="17" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>140.3999938964844</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0371959299442395</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.1446540636846061</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>135.1776855593391</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>145.0496817236391</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>160.7094235549047</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>133.0903323025352</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="20" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0090225980336067</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.09195762956560349</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.2400530158649427</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>370.1300596344479</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>407.8461746427529</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>463.1598014255561</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>350.1116022986699</v>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
@@ -1770,230 +1779,287 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>137.6000061035156</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.021747555102864</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.1359378449072387</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>134.607542388625</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>142.1569655138391</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>156.3050543924504</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>130.3952868713416</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>40.31999969482422</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0535298595992588</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1506616898834902</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>38.16167577211812</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>42.00448336888823</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>46.39467898494825</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>38.07033416602601</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>324.75</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.0540366936779931</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-0.0276025019756407</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.1251956377584677</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>307.2015837280717</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>315.7860874834107</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>365.4072833620624</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>307.2015837280717</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="D16" s="21" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>-0.0486593267137479</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.0259137953415948</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>0.0354684235195519</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>105.1231443981309</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>107.6365256147538</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>114.4192607989105</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>104.975</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="17" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M16" s="20" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
-        <v>367.5</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0197860443083401</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.07687195361889949</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.1760201976314832</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>360.228628716685</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>395.7504429549456</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>432.1874226295701</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>344.1830118399116</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="D17" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.0104710915185266</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0.0615384684378439</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0.1086499313597237</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>98.01569587729709</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>102.9692314384709</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>107.5390433418932</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>91.99443421817186</v>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M15" s="14" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="M17" s="14" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>39.93999862670898</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>-0.0535298595992588</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>0.1506617105180202</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>37.80201610782666</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>41.60860666584711</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>45.95742713789633</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>37.71171418264627</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D17" s="18" t="n">
-        <v>110.4000015258789</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>-0.0448029022074474</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>-0.005646063733711</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.0564225877402071</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>105.4537610538129</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>109.776676081062</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>116.6290552984918</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>104.880001449585</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="D18" s="24" t="n">
+        <v>100.0999984741211</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.035516201414184</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0011987972727639</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0637570370071823</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>96.5448267667547</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>99.97999886894664</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>106.4820777812545</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>95.09499855041503</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="17" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
+      <c r="M18" s="23" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2023,7 +2089,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2131,16 +2197,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.1520270270270269</v>
+        <v>0.133445945945946</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.2343891402714932</v>
+        <v>0.2046678635547576</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.5061859179640755</v>
+        <v>0.4548397662180752</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.0620502802037067</v>
+        <v>-0.0116038599912299</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2148,10 +2214,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0274789775527064</v>
+        <v>0.0275858096662773</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.113974231337216</v>
+        <v>0.115580752659782</v>
       </c>
     </row>
     <row r="5">
@@ -2170,20 +2236,20 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2648437023162842</v>
+        <v>0.2062499523162841</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1883992424013323</v>
+        <v>0.1237558041004351</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.1611463683499709</v>
+        <v>0.1406483871484101</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.0093434679284629</v>
+        <v>0.052406556718852</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2191,10 +2257,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0308679868082667</v>
+        <v>0.0314829822881825</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>-0.0223284441988289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2217,16 +2283,16 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.007903276014288699</v>
+        <v>0.0119456688325279</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.1172300876081426</v>
+        <v>0.125893347993403</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.3720727848721288</v>
+        <v>0.3889816239989208</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>0.0018174454223327</v>
+        <v>0.050693712681016</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
@@ -2234,10 +2300,10 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0200057366856013</v>
+        <v>0.0199940864748226</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0495151050042483</v>
       </c>
     </row>
     <row r="7">
@@ -2260,16 +2326,16 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.2882991983498788</v>
+        <v>0.2213510309518509</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.2813437620031669</v>
+        <v>0.1897767012551967</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.1627653584387609</v>
+        <v>0.1268781732757837</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>-0.1048897377237305</v>
+        <v>-0.0446712703445201</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -2277,96 +2343,96 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0301666095614514</v>
+        <v>0.0309101258904759</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0618296226277728</v>
+        <v>0.0576923532547533</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E8" s="22" t="n">
-        <v>0.0847826418669328</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.12733028666848</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0.2254181658484089</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-0.1643341226904812</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="n">
+        <v>0.1069924178601515</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.1154499151103565</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.2110599078341013</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.06298216644738459</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J8" s="22" t="n">
-        <v>0.025561376483624</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0.0224110802475061</v>
+      <c r="J8" s="19" t="n">
+        <v>0.0225917764825157</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.003753763602968</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>0.1423921249254054</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0.1236438124239507</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0.0265193008972899</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>-0.07591110266928219</v>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>0.0260315595146627</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>0.0331174361060366</v>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.0177514792899408</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.1066666666666666</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.6622163109598647</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.0232957968164582</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.0313097693458234</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0.09195762956560349</v>
       </c>
     </row>
     <row r="10">
@@ -2375,7 +2441,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2385,418 +2451,418 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0.1196094743297571</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0978570628539705</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.013885027158536</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>-0.0262607665016781</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0.0261799379091377</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.0430891156567985</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.4637618860199548</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.6915658454855684</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>-0.2489915402241069</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>0.027897638217083</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>0.0943555181128896</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.115979381443299</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.2005545286506469</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.1251371753354518</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="E12" s="22" t="n">
+        <v>0.0940594059405941</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0288640449727937</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.141732529886271</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>-0.0175226429459831</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>0.0233927009786461</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>-0.0259137953415948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.0543478260869565</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.0812766598731722</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.157467591731516</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>-0.1193390721930266</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0225951356495294</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>-0.0276025019756407</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="J13" s="16" t="n">
+        <v>0.0258018854733409</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>0.0615384684378439</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>0.0306715367835248</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>0.0439207128134846</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>0.1693885792554692</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-0.0945961021975754</v>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>0.0214874891877041</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>0.0037924388242341</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0335305719921104</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0440340909090908</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.6576454896650092</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>-0.0338091592783363</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>0.0261437541099225</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.1744741899256834</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.0642896501606563</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.1032383740741167</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0223792303886866</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>0.1135370331433445</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>0.0623162284795912</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0.0038888719346787</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>-0.1236663451862256</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-0.1571035689083807</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0317237934150863</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.07687195361889949</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J16" s="27" t="n">
+        <v>0.0219213998657456</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.009701613552635499</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.0332583869591531</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.4572736495013934</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.6825878864316</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>-0.2828998656094119</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>0.0278953996079083</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.0215069748919078</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.0497246989863076</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.1526486441787931</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.194847350862909</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.027093047329245</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.049809084093068</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.09306932203840509</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0.0395480668392451</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.1395436359873534</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.0694254310609957</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.1257918841022494</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>0.0152390434952649</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>0.1617559031755004</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.244537031862525</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0234306483748489</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>-0.005646063733711</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="J18" s="27" t="n">
+        <v>0.0294114799322848</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.06673212298112791</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n">
-        <v>0.0273320900850602</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>-0.1703454944323723</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>-0.0532876173492593</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>0.07232629600781371</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0223939659314638</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.1135371380632046</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>0.0206239755188029</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>0.0565500735457435</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>0.1889325281188845</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.1669482240085698</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="E19" s="27" t="n">
+        <v>-0.07197290524828059</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.1249501119830651</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>0.2137709158152536</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-0.263310195817227</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0216241237124125</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0101985587659065</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>-0.0024857082952425</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>-0.0369697362167155</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.1928499793165377</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.248942220376036</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0269977226067913</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0236686907772818</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>0.0405643365602546</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.0111731843575418</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.144927536231884</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.2142556690014324</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0217735937019796</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0201109476789529</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.1194570702003535</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0046035885473222</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.177253374235748</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.281034324338977</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0295961492730896</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.1002252939750626</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0821337601487582</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.1629343511515142</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.218631394109467</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.3129650864918111</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0231757749170699</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.1009728283635982</v>
+      <c r="J19" s="27" t="n">
+        <v>0.0229094532146862</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.1011980384014693</v>
       </c>
     </row>
     <row r="20">
@@ -2815,31 +2881,31 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.0279652264399948</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1157894469144051</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>-0.0344827435010018</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.260438572511438</v>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>-0.0347155118617591</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1257642054661912</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.0714286118706297</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.215290463291456</v>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="24" t="n">
-        <v>0.0178536031006538</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.1000000839371915</v>
+      <c r="J20" s="25" t="n">
+        <v>0.017847407354936</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>-0.0011987972727639</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +2963,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, BIMAS.IS, YKBNK.IS, ASELS.IS, EREGL.IS</t>
+          <t>TOASO.IS, BIMAS.IS, YKBNK.IS, ASELS.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2975,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, GARAN.IS</t>
+          <t>AKBNK.IS, THYAO.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2987,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, THYAO.IS, TCELL.IS</t>
+          <t>TCELL.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2999,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, KCHOL.IS, SISE.IS, PGSUS.IS, PETKM.IS, TUPRS.IS, ARCLK.IS</t>
+          <t>KCHOL.IS, FROTO.IS, PGSUS.IS, SISE.IS, PETKM.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3011,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.74 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %4.56 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3064,7 +3130,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3202,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3300,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3332,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14331.2001953125</v>
+        <v>14259.7998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3342,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12508.61002929688</v>
+        <v>12525.76452636719</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +3376,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>73.39</v>
       </c>
     </row>
     <row r="9">
@@ -3337,23 +3403,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-24</t>
+          <t>Rapor Tarihi: 2026-06-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-25 05:56</t>
+          <t>Son Güncelleme: 2026-06-26 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3431,23 +3497,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>177</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.05106892170555577</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>510.6892170555566</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="D4" s="28" t="n">
+        <v>180.6999969482422</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.0730404008168708</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>730.4040081687072</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="5">
@@ -3461,23 +3527,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>216.8000030517578</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.1147406759699799</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-1147.406759699801</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="D5" s="28" t="n">
+        <v>219.1999969482422</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>-0.1049407823142096</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>-1049.407823142095</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="6">
@@ -3491,29 +3557,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>140.3999938964844</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>0.1405361140276553</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1405.361140276553</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="D6" s="28" t="n">
+        <v>137.6000061035156</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>0.1177904777345942</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>1177.904777345941</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3521,29 +3587,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
-        <v>104</v>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>100.8000030517578</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.03076920142540562</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-307.6920142540566</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="C7" s="28" t="n">
+        <v>85.19999694824219</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>86.34999847412109</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>0.01349767097500632</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>134.9767097500626</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3551,29 +3617,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>86.44999694824219</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>0.01467136202785735</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>146.7136202785732</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="C8" s="28" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>44.2400016784668</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.02769227080292758</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-830.7681240878264</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3581,29 +3647,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>45.09999847412109</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>-0.008791242327008897</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>-263.7372698102699</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="C9" s="28" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0.01144781144781137</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>343.4343434343427</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3611,59 +3677,59 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>374</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>0.007407407407407307</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>222.222222222219</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="C10" s="28" t="n">
+        <v>384</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-0.02734375</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-820.3125</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>384</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>367.5</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>-0.04296875</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>-1289.0625</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.045767673329867</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>-0.07618613460225387</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>-54184.17091597966</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3671,29 +3737,29 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
-        <v>43.84000015258789</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>42.72000122070312</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>-0.02554742080261263</v>
-      </c>
-      <c r="F12" s="25" t="n">
-        <v>-18169.52418518253</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="C12" s="28" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>97</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>-0.04433497536945807</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>-31531.37897749967</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -3701,87 +3767,57 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>99.80000305175781</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>-0.01674873840632696</v>
-      </c>
-      <c r="F13" s="25" t="n">
-        <v>-11911.83289680385</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H13" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="C13" s="28" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>40.31999969482422</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>-0.0004957971662870042</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>-352.614797141403</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>39.93999862670898</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.009915754198460136</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-7052.161434034933</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.045767673329867</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C14" s="28" t="n">
         <v>341</v>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>341</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>2269390.190761669</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>0.045767673329867</v>
+      <c r="D14" s="28" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>-0.0161290322580645</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>-542.3114646904942</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>2219947.37671106</v>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>0.0405574872072023</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H15"/>
+  <autoFilter ref="A3:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -197,15 +197,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -638,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 73.39/100</t>
+          <t>Güven Puanı: 73.46/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -749,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, BIMAS.IS, ASELS.IS, YKBNK.IS, SAHOL.IS</t>
+          <t>AL: TOASO.IS, YKBNK.IS, ASELS.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -766,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: AKBNK.IS, THYAO.IS, GARAN.IS, EREGL.IS</t>
+          <t>AZALT: AKBNK.IS, BIMAS.IS, THYAO.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -783,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TCELL.IS, ARCLK.IS</t>
+          <t>ÇIK: TCELL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -969,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1289731132681991</v>
+        <v>0.1286261716247234</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12897.31132681991</v>
+        <v>12862.61716247234</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.115580752659782</v>
+        <v>0.1111298169216609</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1490.680950441377</v>
+        <v>1429.420290398965</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>374.2773425173569</v>
+        <v>361.1171904995398</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>316.9899217139279</v>
+        <v>306.9595859379225</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.094931308126066</v>
+        <v>2.002015606474425</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1003,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1012,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1011527915019432</v>
+        <v>0.09876010286701303</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10115.27915019432</v>
+        <v>9876.010286701303</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0495151050042483</v>
+        <v>0.0576923532547533</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>500.8591092691555</v>
+        <v>569.770274207949</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>394.0929219290953</v>
+        <v>43.00577092194722</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>356.725</v>
+        <v>38.16395266206861</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9903021000849659</v>
+        <v>0.9397943629868905</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1053,29 +1044,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09889355190160248</v>
+        <v>0.09418198775809977</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9889.355190160248</v>
+        <v>9418.198775809977</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.09195762956560349</v>
+        <v>0.0768720835510508</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>909.4016612194343</v>
+        <v>723.9965631944689</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>407.8461746427529</v>
+        <v>389.2892582037049</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>350.1116022986699</v>
+        <v>338.6494229435847</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.468513366385918</v>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>1.216129384176888</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1094,25 +1085,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09217028756482212</v>
+        <v>0.09292983765935728</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9217.028756482212</v>
+        <v>9292.983765935727</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0426715939840771</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>531.7520789781913</v>
+        <v>396.5464301606291</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>42.83654030681751</v>
+        <v>144.3057422434339</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>37.99627980287145</v>
+        <v>131.2317517386179</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.9332274067594398</v>
+        <v>0.8238767911137752</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1126,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1135,25 +1126,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07881025576343306</v>
+        <v>0.08550190009080656</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7881.025576343306</v>
+        <v>8550.190009080656</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0615384684378439</v>
+        <v>0.0417777788571567</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>484.9862436876431</v>
+        <v>357.2079473860423</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>102.9692314384709</v>
+        <v>43.87967893272472</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>91.99443421817186</v>
+        <v>39.65704675903567</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.192518827769908</v>
+        <v>0.7144596717054376</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1176,10 +1167,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000</v>
+        <v>49999.99999999999</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1208,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1252,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1294,7 +1285,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 11</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1446,28 +1437,28 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>335.5</v>
+        <v>325</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.08979294277640611</v>
+        <v>0.1012146812708825</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.115580752659782</v>
+        <v>0.1111298169216609</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2375061062526389</v>
+        <v>0.1296241549962105</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>365.6255323014843</v>
+        <v>357.8947714130368</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>374.2773425173569</v>
+        <v>361.1171904995398</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>415.1832986477604</v>
+        <v>367.1278503737684</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>316.9899217139279</v>
+        <v>306.9595859379225</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1475,7 +1466,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>73.39</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1503,28 +1494,28 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>77.19999694824219</v>
+        <v>77.25</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.0253879955685062</v>
+        <v>-0.0253879091306941</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.08064316590219429</v>
+        <v>0.0856124069061925</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>75.24004376783152</v>
+        <v>75.28878401965387</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>77.19999694824219</v>
+        <v>77.25</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>83.42564910978817</v>
+        <v>83.86355843350337</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>72.33902467510369</v>
+        <v>72.40781641561108</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1532,7 +1523,7 @@
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>73.39</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1546,57 +1537,57 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>375.5</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.007965308684240601</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0495151050042483</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.1219923730948281</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>378.4909734109323</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>394.0929219290953</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>421.3081360971079</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>356.725</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0037105180381591</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0219942686510214</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.0938733706755232</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>373.1104109947094</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>382.7368536098076</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>409.6555773179834</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>355.775</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="14" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="M10" s="17" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
@@ -1617,28 +1608,28 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>40.5</v>
+        <v>40.65999984741211</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0277778108086147</v>
+        <v>-0.0234457107155366</v>
       </c>
       <c r="F11" s="16" t="n">
         <v>0.0576923532547533</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.2319541705328982</v>
+        <v>0.2257407445924774</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>39.3749986622511</v>
+        <v>39.70669725329592</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>42.83654030681751</v>
+        <v>43.00577092194722</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>49.89414390658238</v>
+        <v>49.83861848809694</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>37.99627980287145</v>
+        <v>38.16395266206861</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1646,7 +1637,7 @@
         </is>
       </c>
       <c r="M11" s="14" t="n">
-        <v>73.39</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1674,28 +1665,28 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>328.5</v>
+        <v>330.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0511886546061877</v>
+        <v>-0.0557185041218549</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>0.003753763602968</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.0948783870299643</v>
+        <v>0.0731182729479942</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>311.6845269618673</v>
+        <v>312.3211047616965</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>329.733111343575</v>
+        <v>331.9915573116817</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>359.6675501393433</v>
+        <v>354.9338687775491</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>311.6845269618673</v>
+        <v>312.3211047616965</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1703,7 +1694,7 @@
         </is>
       </c>
       <c r="M12" s="17" t="n">
-        <v>73.39</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="N12" s="17" t="inlineStr">
         <is>
@@ -1722,168 +1713,168 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>138.3999938964844</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0082889988742848</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.0426715939840771</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.1593907013593682</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>137.2527965028754</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>144.3057422434339</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>160.4596659917773</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>131.2317517386179</v>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>42.11999893188477</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.058474649461224</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>0.1392962007538372</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>39.65704675903567</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>43.87967893272472</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>47.98715475885199</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>39.65704675903567</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
-        <v>373.5</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0090225980336067</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.09195762956560349</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.2400530158649427</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>370.1300596344479</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>407.8461746427529</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>463.1598014255561</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>350.1116022986699</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="D15" s="15" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0004373968096377</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.0768720835510508</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.1760203496822197</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>361.3418810533159</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>389.2892582037049</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>425.1313564101224</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>338.6494229435847</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="14" t="inlineStr">
+      <c r="O15" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>137.6000061035156</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.021747555102864</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.1359378449072387</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>134.607542388625</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>142.1569655138391</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>156.3050543924504</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>130.3952868713416</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>40.31999969482422</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0535298595992588</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1506616898834902</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>38.16167577211812</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>42.00448336888823</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>46.39467898494825</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>38.07033416602601</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1902,28 +1893,28 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>110.5</v>
+        <v>110.9000015258789</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.0486593267137479</v>
+        <v>-0.0474823379901831</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.0259137953415948</v>
+        <v>-0.0144632354250776</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.0354684235195519</v>
+        <v>0.0550611293560816</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>105.1231443981309</v>
+        <v>105.6342101703153</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>107.6365256147538</v>
+        <v>109.2960286951687</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>114.4192607989105</v>
+        <v>117.006280855485</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>104.975</v>
+        <v>105.355001449585</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
@@ -1931,7 +1922,7 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>73.39</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
@@ -1945,121 +1936,64 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>97</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.0104710915185266</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>0.0615384684378439</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0.1086499313597237</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>98.01569587729709</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>102.9692314384709</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>107.5390433418932</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>91.99443421817186</v>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>198.1999969482422</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0484401082858588</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.009413442464124899</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.1744271468165548</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>188.5991676338125</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>200.0657412159042</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>232.771456914974</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>188.2899971008301</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O17" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>100.0999984741211</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.035516201414184</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0011987972727639</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0637570370071823</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>96.5448267667547</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>99.97999886894664</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>106.4820777812545</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>95.09499855041503</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O18"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2089,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2106,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2197,16 +2131,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.133445945945946</v>
+        <v>0.097972972972973</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.2046678635547576</v>
+        <v>0.1926605504587155</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.4548397662180752</v>
+        <v>0.4041814534285399</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.0116038599912299</v>
+        <v>0.0254876783377191</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2214,10 +2148,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0275858096662773</v>
+        <v>0.0277544831724269</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.115580752659782</v>
+        <v>0.1111298169216609</v>
       </c>
     </row>
     <row r="5">
@@ -2240,16 +2174,16 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2062499523162841</v>
+        <v>0.20703125</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1237558041004351</v>
+        <v>0.1486988847583643</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.1406483871484101</v>
+        <v>0.1430235716370911</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.052406556718852</v>
+        <v>0.0812551529663021</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2257,53 +2191,53 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0314829822881825</v>
+        <v>0.0313409940737147</v>
       </c>
       <c r="K5" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0119456688325279</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.125893347993403</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.3889816239989208</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.050693712681016</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>0.0092507402870352</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.1121138654633615</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.4205681130590899</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.08831525157047281</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.0199940864748226</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0495151050042483</v>
+      <c r="J6" s="19" t="n">
+        <v>0.0199787850023338</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.0219942686510214</v>
       </c>
     </row>
     <row r="7">
@@ -2326,16 +2260,16 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.2213510309518509</v>
+        <v>0.2261761168429352</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.1897767012551967</v>
+        <v>0.225436994377288</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.1268781732757837</v>
+        <v>0.1376608264657579</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>-0.0446712703445201</v>
+        <v>-0.0113870743773584</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -2343,7 +2277,7 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0309101258904759</v>
+        <v>0.0306941366786843</v>
       </c>
       <c r="K7" s="16" t="n">
         <v>0.0576923532547533</v>
@@ -2369,16 +2303,16 @@
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>0.1069924178601515</v>
+        <v>0.1145745577085088</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.1154499151103565</v>
+        <v>0.1269165247018739</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>0.2110599078341013</v>
+        <v>0.2193548387096773</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>-0.06298216644738459</v>
+        <v>-0.025973242436669</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -2386,7 +2320,7 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.0225917764825157</v>
+        <v>0.0225893046698586</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>0.003753763602968</v>
@@ -2398,127 +2332,127 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.1261187321250085</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.1364868225932054</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.021950884245822</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.005760502741636</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.0258968297470734</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0.0426715939840771</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.0896555746493421</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.5870894361109649</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.775902772282451</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>-0.1904680915015399</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0.0277547649129958</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0177514792899408</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.1066666666666666</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.6622163109598647</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.0232957968164582</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="E11" s="16" t="n">
+        <v>-0.0493096646942801</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.06952662721893491</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.6232600132635673</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.078770713758614</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="16" t="n">
-        <v>0.0313097693458234</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>0.09195762956560349</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.1196094743297571</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0978570628539705</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.013885027158536</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.0262607665016781</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0261799379091377</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.0430891156567985</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.4637618860199548</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.6915658454855684</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>-0.2489915402241069</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0.027897638217083</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>0.0417778692166073</v>
+      <c r="J11" s="16" t="n">
+        <v>0.0316052241444195</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.0768720835510508</v>
       </c>
     </row>
     <row r="12">
@@ -2541,16 +2475,16 @@
         </is>
       </c>
       <c r="E12" s="22" t="n">
-        <v>0.0940594059405941</v>
+        <v>0.0980198170879098</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0288640449727937</v>
+        <v>0.0462264294894236</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.141732529886271</v>
+        <v>0.1452847240059438</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>-0.0175226429459831</v>
+        <v>0.0161628276083301</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -2558,311 +2492,311 @@
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.0233927009786461</v>
+        <v>0.023328758071726</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>-0.0259137953415948</v>
+        <v>-0.0144632354250776</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0.0481226364410856</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.0470152865980195</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.2024015567157342</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-0.0378984824125733</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.0215201685312865</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>0.009413442464124899</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.0543478260869565</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.0812766598731722</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.157467591731516</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>-0.1193390721930266</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0.0592390972635019</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0.1007848660939432</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.1703970939841539</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>-0.09047421021702989</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
-        <v>0.0258018854733409</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>0.0615384684378439</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="J14" s="24" t="n">
+        <v>0.0257353684650022</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.06255951557298681</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>0.0249554181347848</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.1601752428145885</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.0619335174456089</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>0.1253424872033501</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>0.0222932257410407</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.1212599801684322</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
-        <v>0.0306715367835248</v>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>0.0439207128134846</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>0.1693885792554692</v>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-0.0945961021975754</v>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="E16" s="24" t="n">
+        <v>0.0587889455683758</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>0.0140765760928118</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>-0.1278450067626362</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.1223342607910339</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="27" t="n">
-        <v>0.0214874891877041</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>0.0037924388242341</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="J16" s="24" t="n">
+        <v>0.021857194251186</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.0477932433117227</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>0.0261437541099225</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.1744741899256834</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.0642896501606563</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>0.1032383740741167</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="E17" s="24" t="n">
+        <v>0.0023802422428664</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>0.0129968263821267</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>0.1569812562150523</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.1584950338608513</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0268138653389995</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0236686907772818</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>0.0038572954450379</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.064690066309239</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>-0.0378927780939064</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.1473805790456531</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0223792303886866</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>0.1135370331433445</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="J18" s="24" t="n">
+        <v>0.0182983990130513</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.0999999916062814</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
-        <v>0.0623162284795912</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>0.0038888719346787</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>-0.1236663451862256</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-0.1571035689083807</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="E19" s="24" t="n">
+        <v>-0.1140271680663239</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>0.0213875767230238</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>0.1773903133981555</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.2178459598945363</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
-        <v>0.0219213998657456</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.009701613552635499</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.0215069748919078</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.0497246989863076</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>0.1526486441787931</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.194847350862909</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="27" t="n">
-        <v>0.027093047329245</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>0.049809084093068</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>-0.1257918841022494</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>0.0152390434952649</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0.1617559031755004</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-0.244537031862525</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0294114799322848</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>0.06673212298112791</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>-0.07197290524828059</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>-0.1249501119830651</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>0.2137709158152536</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-0.263310195817227</v>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>0.0229094532146862</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>0.1011980384014693</v>
+      <c r="J19" s="24" t="n">
+        <v>0.0294438886992158</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.0999999916062814</v>
       </c>
     </row>
     <row r="20">
@@ -2871,7 +2805,7 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -2881,31 +2815,31 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.0347155118617591</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1257642054661912</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.0714286118706297</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.215290463291456</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>-0.07197290524828059</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.0874271451573958</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0.2118371650205139</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.2281881659293725</v>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.017847407354936</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>-0.0011987972727639</v>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>0.0223518238238337</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0.0999999916062814</v>
       </c>
     </row>
   </sheetData>
@@ -2930,7 +2864,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2938,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2963,7 +2897,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, BIMAS.IS, YKBNK.IS, ASELS.IS, SAHOL.IS</t>
+          <t>TOASO.IS, YKBNK.IS, GARAN.IS, EREGL.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2909,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, THYAO.IS, GARAN.IS, EREGL.IS</t>
+          <t>AKBNK.IS, BIMAS.IS, THYAO.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2921,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, ARCLK.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, FROTO.IS, PGSUS.IS, SISE.IS, PETKM.IS, TUPRS.IS</t>
+          <t>SAHOL.IS, FROTO.IS, PGSUS.IS, SISE.IS, ARCLK.IS, PETKM.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -3011,7 +2945,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %4.56 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3049,7 +2983,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3057,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3118,7 +3052,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3064,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3088,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3136,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3234,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3308,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3376,7 +3310,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.39</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3410,16 +3344,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-25</t>
+          <t>Rapor Tarihi: 2026-06-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3433,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-26 05:59</t>
+          <t>Son Güncelleme: 2026-06-27 05:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3497,22 +3431,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>180.6999969482422</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.0730404008168708</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>730.4040081687072</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H4" s="29" t="n">
+      <c r="D4" s="25" t="n">
+        <v>180.1000061035156</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.06947750968579758</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>694.7750968579767</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H4" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3527,22 +3461,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="25" t="n">
         <v>219.1999969482422</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="26" t="n">
         <v>-0.1049407823142096</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="25" t="n">
         <v>-1049.407823142095</v>
       </c>
-      <c r="G5" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H5" s="29" t="n">
+      <c r="G5" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H5" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3557,22 +3491,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>137.6000061035156</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>0.1177904777345942</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>1177.904777345941</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H6" s="29" t="n">
+      <c r="D6" s="25" t="n">
+        <v>138.3999938964844</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.1242891601300853</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1242.891601300851</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H6" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3587,22 +3521,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>86.34999847412109</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0.01349767097500632</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>134.9767097500626</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H7" s="29" t="n">
+      <c r="D7" s="25" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.01232397992215506</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>123.2397992215501</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H7" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3617,22 +3551,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="25" t="n">
         <v>45.5</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>44.2400016784668</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.02769227080292758</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-830.7681240878264</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H8" s="29" t="n">
+      <c r="D8" s="25" t="n">
+        <v>45.31999969482422</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.003956050663204036</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-118.6815198961194</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H8" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3647,22 +3581,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="25" t="n">
         <v>371.25</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>375.5</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0.01144781144781137</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>343.4343434343427</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H9" s="29" t="n">
+      <c r="D9" s="25" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.008754208754208737</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>262.6262626262615</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H9" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3677,22 +3611,22 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="25" t="n">
         <v>384</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>373.5</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-0.02734375</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-820.3125</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H10" s="29" t="n">
+      <c r="D10" s="25" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.05859375</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>-1757.8125</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H10" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3707,22 +3641,22 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="25" t="n">
         <v>43.84000015258789</v>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>-0.07618613460225387</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>-54184.17091597966</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H11" s="29" t="n">
+      <c r="D11" s="25" t="n">
+        <v>40.65999984741211</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>-0.07253650305902348</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>-51588.52460381074</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H11" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3737,22 +3671,22 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="25" t="n">
         <v>101.5</v>
       </c>
-      <c r="D12" s="28" t="n">
-        <v>97</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>-0.04433497536945807</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>-31531.37897749967</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H12" s="29" t="n">
+      <c r="D12" s="25" t="n">
+        <v>97.44999694824219</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>-0.03990150789909175</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>-28378.26246333471</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H12" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3767,22 +3701,22 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="25" t="n">
         <v>40.34000015258789</v>
       </c>
-      <c r="D13" s="28" t="n">
-        <v>40.31999969482422</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>-0.0004957971662870042</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>-352.614797141403</v>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H13" s="29" t="n">
+      <c r="D13" s="25" t="n">
+        <v>42.11999893188477</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.04412490759950294</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>31381.97714722413</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H13" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>
@@ -3797,22 +3731,22 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="25" t="n">
         <v>341</v>
       </c>
-      <c r="D14" s="28" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>-0.0161290322580645</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>-542.3114646904942</v>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>2219947.37671106</v>
-      </c>
-      <c r="H14" s="29" t="n">
+      <c r="D14" s="25" t="n">
+        <v>325</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.04692082111436946</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-1577.633351826898</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>2256106.809120123</v>
+      </c>
+      <c r="H14" s="26" t="n">
         <v>0.0405574872072023</v>
       </c>
     </row>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1286261716247234</v>
+        <v>0.1286261716247233</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12862.61716247234</v>
+        <v>12862.61716247233</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1429.420290398965</v>
+        <v>1429.420290398962</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>361.1171904995398</v>
+        <v>361.1171904995397</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>306.9595859379225</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.002015606474425</v>
+        <v>2.002015606474419</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09876010286701303</v>
+        <v>0.09876010286701312</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9876.010286701303</v>
+        <v>9876.010286701312</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>569.770274207949</v>
+        <v>569.7702742079515</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>43.00577092194722</v>
+        <v>43.00577092194723</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>38.16395266206861</v>
+        <v>38.16395266206862</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9397943629868905</v>
+        <v>0.939794362986896</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09418198775809977</v>
+        <v>0.09418198775809983</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9418.198775809977</v>
+        <v>9418.198775809982</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0768720835510508</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>723.9965631944689</v>
+        <v>723.9965631944693</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>389.2892582037049</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>338.6494229435847</v>
+        <v>338.6494229435848</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.216129384176888</v>
+        <v>1.216129384176894</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09292983765935728</v>
+        <v>0.09292983765935721</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9292.983765935727</v>
+        <v>9292.983765935722</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.5464301606291</v>
+        <v>396.546430160627</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>144.3057422434339</v>
@@ -1103,7 +1103,7 @@
         <v>131.2317517386179</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.8238767911137752</v>
+        <v>0.8238767911137712</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>49999.99999999999</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1443,7 +1443,7 @@
         <v>0.1012146812708825</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.1296241549962105</v>
@@ -1452,7 +1452,7 @@
         <v>357.8947714130368</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>361.1171904995398</v>
+        <v>361.1171904995397</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>367.1278503737684</v>
@@ -1557,7 +1557,7 @@
         <v>-0.0037105180381591</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0219942686510214</v>
+        <v>0.0219942686510217</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>0.0938733706755232</v>
@@ -1611,25 +1611,25 @@
         <v>40.65999984741211</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0234457107155366</v>
+        <v>-0.0234457107155365</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.2257407445924774</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>39.70669725329592</v>
+        <v>39.70669725329593</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>43.00577092194722</v>
+        <v>43.00577092194723</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>49.83861848809694</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>38.16395266206861</v>
+        <v>38.16395266206862</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>-0.0557185041218549</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0.0731182729479942</v>
@@ -1680,7 +1680,7 @@
         <v>312.3211047616965</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>331.9915573116817</v>
+        <v>331.9915573116818</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>354.9338687775491</v>
@@ -1728,10 +1728,10 @@
         <v>-0.0082889988742848</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1593907013593682</v>
+        <v>0.159390701359368</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>137.2527965028754</v>
@@ -1857,7 +1857,7 @@
         <v>425.1313564101224</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>338.6494229435847</v>
+        <v>338.6494229435848</v>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
         <v>0.1926605504587155</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.4041814534285399</v>
+        <v>0.4041814534285401</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.0254876783377191</v>
@@ -2151,7 +2151,7 @@
         <v>0.0277544831724269</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
     </row>
     <row r="5">
@@ -2237,7 +2237,7 @@
         <v>0.0199787850023338</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0219942686510214</v>
+        <v>0.0219942686510217</v>
       </c>
     </row>
     <row r="7">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0306941366786843</v>
+        <v>0.0306941366786842</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
     </row>
     <row r="8">
@@ -2323,7 +2323,7 @@
         <v>0.0225893046698586</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
     </row>
     <row r="9">
@@ -2366,7 +2366,7 @@
         <v>0.0258968297470734</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
     </row>
     <row r="10">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0.0316052241444195</v>
+        <v>0.0316052241444194</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>0.0768720835510508</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.023328758071726</v>
+        <v>0.0233287580717261</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>-0.0144632354250776</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.0481226364410856</v>
+        <v>0.0481226364410858</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>0.0470152865980195</v>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.0592390972635019</v>
+        <v>0.0592390972635021</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.1007848660939432</v>
+        <v>0.1007848660939434</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.1703970939841539</v>
+        <v>0.1703970939841541</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>-0.09047421021702989</v>
@@ -2581,7 +2581,7 @@
         <v>0.0257353684650022</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.06255951557298681</v>
+        <v>0.0625595155729869</v>
       </c>
     </row>
     <row r="15">
@@ -2607,7 +2607,7 @@
         <v>0.0249554181347848</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.1601752428145885</v>
+        <v>-0.1601752428145886</v>
       </c>
       <c r="G15" s="24" t="n">
         <v>-0.0619335174456089</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.021857194251186</v>
+        <v>0.0218571942511859</v>
       </c>
       <c r="K16" s="24" t="n">
         <v>0.0477932433117227</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.0268138653389995</v>
+        <v>0.0268138653389994</v>
       </c>
       <c r="K17" s="24" t="n">
         <v>0.0236686907772818</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.0038572954450379</v>
+        <v>0.0038572954450377</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.064690066309239</v>
+        <v>-0.0646900663092389</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>-0.0378927780939064</v>
+        <v>-0.0378927780939065</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>-0.1473805790456531</v>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-0.1140271680663239</v>
+        <v>-0.114027168066324</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.0213875767230238</v>
+        <v>0.0213875767230236</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>0.1773903133981555</v>
+        <v>0.1773903133981553</v>
       </c>
       <c r="H19" s="24" t="n">
         <v>-0.2178459598945363</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.0223518238238337</v>
+        <v>0.0223518238238338</v>
       </c>
       <c r="K20" s="24" t="n">
         <v>0.0999999916062814</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3675,13 +3675,13 @@
         <v>101.5</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>97.44999694824219</v>
+        <v>97.4499969482422</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.03990150789909175</v>
+        <v>-0.03990150789909164</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>-28378.26246333471</v>
+        <v>-28378.2624633346</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>2256106.809120123</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14259.7998046875</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12525.76452636719</v>
+        <v>12543.48702636719</v>
       </c>
     </row>
     <row r="6">
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3447,7 +3447,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="5">
@@ -3477,7 +3477,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="6">
@@ -3507,7 +3507,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="7">
@@ -3537,7 +3537,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="8">
@@ -3567,7 +3567,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="9">
@@ -3597,7 +3597,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="10">
@@ -3627,7 +3627,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="11">
@@ -3657,7 +3657,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="12">
@@ -3687,7 +3687,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="13">
@@ -3717,7 +3717,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="14">
@@ -3747,7 +3747,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,11 +99,6 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,9 +152,6 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -172,6 +164,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -181,15 +182,6 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -197,6 +189,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +613,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +681,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 73.46/100</t>
+          <t>Güven Puanı: 75.49/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +741,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, YKBNK.IS, ASELS.IS, GARAN.IS, EREGL.IS</t>
+          <t>AL: TOASO.IS, ASELS.IS, YKBNK.IS, EREGL.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +758,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: AKBNK.IS, BIMAS.IS, THYAO.IS, KCHOL.IS</t>
+          <t>AZALT: AKBNK.IS, BIMAS.IS, GARAN.IS, THYAO.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +775,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TCELL.IS</t>
+          <t>ÇIK: TCELL.IS, KCHOL.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -960,29 +961,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1286261716247233</v>
+        <v>0.1187312562404738</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12862.61716247233</v>
+        <v>11873.12562404738</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1111298169216608</v>
+        <v>0.0885068840144367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1429.420290398962</v>
+        <v>1050.853352496398</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>361.1171904995397</v>
+        <v>341.2469081385259</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>306.9595859379225</v>
+        <v>295.9389557075669</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.002015606474419</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
+        <v>1.580026089364279</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -994,7 +995,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +1004,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09876010286701312</v>
+        <v>0.09969717153026461</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9876.010286701312</v>
+        <v>9969.71715302646</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0576923532547535</v>
+        <v>0.07687227844927789</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>569.7702742079515</v>
+        <v>766.3948730479922</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>43.00577092194723</v>
+        <v>384.9818395456169</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>38.16395266206862</v>
+        <v>334.9701730769033</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.939794362986896</v>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.21979807654197</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1036,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,27 +1045,27 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09418198775809983</v>
+        <v>0.09946612601007221</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9418.198775809982</v>
+        <v>9946.61260100722</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0768720835510508</v>
+        <v>0.0517422093657887</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>723.9965631944693</v>
+        <v>514.6597116817077</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>389.2892582037049</v>
+        <v>42.15382967717832</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>338.6494229435848</v>
+        <v>37.61313124246275</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.216129384176894</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
+        <v>0.8406715195008853</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1076,7 +1077,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,27 +1086,27 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09292983765935721</v>
+        <v>0.09263864985518612</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9292.983765935722</v>
+        <v>9263.864985518612</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0426715939840769</v>
+        <v>0.0521950301469675</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.546430160627</v>
+        <v>483.5277121965806</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>144.3057422434339</v>
+        <v>43.35043604481616</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>131.2317517386179</v>
+        <v>38.83821727971362</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.8238767911137712</v>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
+        <v>0.9105133036748783</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1126,62 +1127,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08550190009080656</v>
+        <v>0.08946679636400325</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8550.190009080656</v>
+        <v>8946.679636400324</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0417777788571567</v>
+        <v>0.0615383787458729</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>357.2079473860423</v>
+        <v>550.5641599827916</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>43.87967893272472</v>
+        <v>103.4999919277226</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>39.65704675903567</v>
+        <v>92.48939489153216</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.7144596717054376</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
+        <v>1.197458549982861</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr"/>
+      <c r="I25" s="12" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1199,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1222,7 +1223,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1244,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1285,7 +1286,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1423,577 +1424,691 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>77.19999694824219</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0253877384495302</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0856124069061925</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>75.24006361741569</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>77.19999694824219</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>83.80927450013192</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>72.36299207104064</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>325</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.1012146812708825</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.1111298169216608</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.1296241549962105</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>357.8947714130368</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>361.1171904995397</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>367.1278503737684</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>306.9595859379225</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="D9" s="17" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0425415966915239</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.0885068840144367</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.1296240786332305</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>300.1632094372072</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>341.2469081385259</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>354.1371486515178</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>295.9389557075669</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0253879091306941</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0856124069061925</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>75.28878401965387</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>83.86355843350337</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>72.40781641561108</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="D10" s="14" t="n">
+        <v>371</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0037105176120389</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0219942018242906</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.085651551868344</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>369.6233979659336</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>379.1598488768119</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>402.7767257431556</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>40.08000183105469</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0277778126436635</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.0517422093657887</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.2319541705328982</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>38.96666704943396</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>42.15382967717832</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>49.37672541073402</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>37.61313124246275</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>137.3000030517578</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.007255186297481</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.0426715907258359</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.1446542915756432</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>136.3038659509726</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>143.1588125886385</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>157.1610377265435</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>130.1810334807738</v>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>329</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.051580557859116</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0.003753763602968</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.1176163250763418</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>312.0299964643509</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>330.2349882253765</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>367.6957709501165</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>312.0299964643509</v>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M13" s="13" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>374.5</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0037105180381591</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0219942686510217</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.0938733706755232</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>373.1104109947094</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>382.7368536098076</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>409.6555773179834</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>355.775</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.0161982288834289</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.07687227844927789</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.1760202663201471</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>351.7091331741742</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>384.9818395456169</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>420.4272452094526</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>334.9701730769033</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>41.20000076293945</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>-0.0573248407643312</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0.0521950301469675</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.1107635436316054</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>38.83821727971362</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>43.35043604481616</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>45.76345884506748</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>38.83821727971362</v>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M15" s="16" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>109.5999984741211</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>-0.06342762253785331</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>-0.0259136860515759</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.0289375215740421</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>102.6483311407552</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>106.7598585224095</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>112.771550794481</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>102.6483311407552</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>0.0013325969181725</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0.0615383787458729</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>0.1339262703921544</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>97.62992819952183</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>103.4999919277226</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>110.5578113632351</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v>92.48939489153216</v>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>40.65999984741211</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0234457107155365</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0576923532547535</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.2257407445924774</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>39.70669725329593</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>43.00577092194723</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>49.83861848809694</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>38.16395266206862</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>195.6999969482422</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>-0.0567376780722056</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.0048224528887045</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.0931571382971832</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>184.5964335226612</v>
+      </c>
+      <c r="I18" s="23" t="n">
+        <v>194.7562429326397</v>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>213.9308486287079</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <v>184.5964335226612</v>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>330.75</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.0557185041218549</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.0037537636029683</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.0731182729479942</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>312.3211047616965</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>331.9915573116818</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>354.9338687775491</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>312.3211047616965</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>19.20000076293945</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>-0.0355161231779836</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.0011987972727639</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>0.0637570370071823</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>18.51809117082552</v>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>19.17698385438777</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>20.42413592212011</v>
+      </c>
+      <c r="K19" s="23" t="n">
+        <v>18.06516413653845</v>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="17" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>138.3999938964844</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0082889988742848</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.0426715939840769</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.159390701359368</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>137.2527965028754</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>144.3057422434339</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>160.4596659917773</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>131.2317517386179</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>42.11999893188477</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>-0.058474649461224</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>0.1392962007538372</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>39.65704675903567</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>43.87967893272472</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>47.98715475885199</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>39.65704675903567</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N14" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>361.5</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0004373968096377</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.0768720835510508</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.1760203496822197</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>361.3418810533159</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>389.2892582037049</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>425.1313564101224</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>338.6494229435848</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>110.9000015258789</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.0474823379901831</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.0144632354250776</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>0.0550611293560816</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>105.6342101703153</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>109.2960286951687</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>117.006280855485</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>105.355001449585</v>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>198.1999969482422</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>-0.0484401082858588</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>0.009413442464124899</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.1744271468165548</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>188.5991676338125</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>200.0657412159042</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>232.771456914974</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>188.2899971008301</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
+      <c r="M19" s="22" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2023,7 +2138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2112,734 +2227,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.2062499523162841</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.1539610640872546</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.1505311399001552</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>0.1126751215487678</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>0.0313277530337499</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.097972972972973</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.1926605504587155</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.4041814534285401</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.0254876783377191</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E5" s="18" t="n">
+        <v>0.0591216216216217</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.1206434316353888</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.3310906547240273</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.07495271326499869</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0277544831724269</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.1111298169216608</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="J5" s="18" t="n">
+        <v>0.0280080451234977</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0885068840144367</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.20703125</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1486988847583643</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.1430235716370911</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.0812551529663021</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E6" s="15" t="n">
+        <v>-0.0001815096221894</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.0920418806874523</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.3837933920600045</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0.1305601821820861</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>0.0200078717909501</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0219942018242906</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0.208685223627425</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.2079566444368767</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.139283726076546</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0.0237258246259215</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0313409940737147</v>
-      </c>
-      <c r="K5" s="19" t="n">
+      <c r="J7" s="18" t="n">
+        <v>0.0307743322840939</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0517422093657887</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.1171684405784707</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.1292365778260664</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0247377425071808</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0.0379426002611251</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>0.0259248704033182</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>0.0426715907258359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.1086773378264531</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.2276119402985075</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.0160404485072016</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.0226086953990568</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.003753763602968</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0598290598290598</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.0808767951625093</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.5811587366181907</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>0.1245901410082888</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.0315102474448905</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>0.07687227844927789</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>0.0658549773349965</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.4967812918639764</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.751686189256072</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>-0.1518902565442526</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0.0277410798482514</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>0.0521950301469675</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0.0851484997437732</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.0300751588566836</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.1506561519592766</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0.0584659158050941</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.0233805152780982</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>-0.0259136860515759</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>0.0597826086956521</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0.111856339981202</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.1793619412251483</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>-0.0485611030178532</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.0256954108126556</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>0.0615383787458729</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0.0349021186234845</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0.0160954867418874</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.2048498197431085</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.0170105173026695</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>0.0214820549705343</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>-0.0048224528887045</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.0154485490052367</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-0.1767823272063465</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>-0.0627502256282759</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>0.15449227409447</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.0222440191112051</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0.1212598686799699</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.0060245584030921</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>0.0143510328026927</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>0.1830581408894263</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>-0.1189271392146106</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0.0268062082262847</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.0236686907772818</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.0411522618978632</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>0.0005650062345514</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.1339853002273074</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.09132005910616819</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.0219585496251258</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.009701613552635499</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.0715495093769523</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.0881496754604664</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>0.2333497870993663</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>-0.1679923126599778</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.022350643703123</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.07594938363664309</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.0202507091217102</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>-0.08054300023419821</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>-0.053122128756019</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>-0.1033775326630218</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>0.0185132711703563</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.1004505040129337</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>-0.1312216999309126</v>
+      </c>
+      <c r="F20" s="24" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0.0092507402870352</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.1121138654633615</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.4205681130590899</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.08831525157047281</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="G20" s="24" t="n">
+        <v>0.1657560147784205</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.1786406559219421</v>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.0199787850023338</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.0219942686510217</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.2261761168429352</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.225436994377288</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.1376608264657579</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>-0.0113870743773584</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>0.0306941366786842</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0576923532547535</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.1145745577085088</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.1269165247018739</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.2193548387096773</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>-0.025973242436669</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0.0225893046698586</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.0037537636029683</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.1261187321250085</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.1364868225932054</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.021950884245822</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.005760502741636</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>0.0258968297470734</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>0.0426715939840769</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.0896555746493421</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.5870894361109649</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.775902772282451</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>-0.1904680915015399</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.0277547649129958</v>
-      </c>
-      <c r="K10" s="16" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0493096646942801</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.06952662721893491</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.6232600132635673</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.078770713758614</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0316052241444194</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.0768720835510508</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>0.0980198170879098</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0462264294894236</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.1452847240059438</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>0.0161628276083301</v>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>0.0233287580717261</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>-0.0144632354250776</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.0481226364410858</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0.0470152865980195</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.2024015567157342</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.0378984824125733</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0215201685312865</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>0.009413442464124899</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>0.0592390972635021</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>0.1007848660939434</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.1703970939841541</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>-0.09047421021702989</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0257353684650022</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.0625595155729869</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>0.0249554181347848</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.1601752428145886</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.0619335174456089</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>0.1253424872033501</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0222932257410407</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.1212599801684322</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>0.0587889455683758</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>0.0140765760928118</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>-0.1278450067626362</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.1223342607910339</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0218571942511859</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0477932433117227</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>0.0023802422428664</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>0.0129968263821267</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>0.1569812562150523</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.1584950338608513</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0268138653389994</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0236686907772818</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>0.0038572954450377</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0646900663092389</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-0.0378927780939065</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.1473805790456531</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0182983990130513</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0999999916062814</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.114027168066324</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>0.0213875767230236</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.1773903133981553</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.2178459598945363</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0294438886992158</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.0999999916062814</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.07197290524828059</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.0874271451573958</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>0.2118371650205139</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.2281881659293725</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
       <c r="J20" s="24" t="n">
-        <v>0.0223518238238338</v>
+        <v>0.0295530359715273</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.0999999916062814</v>
+        <v>-0.0011987972727639</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2979,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +3012,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, YKBNK.IS, GARAN.IS, EREGL.IS, ASELS.IS</t>
+          <t>TOASO.IS, YKBNK.IS, ASELS.IS, EREGL.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +3024,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BIMAS.IS, THYAO.IS, KCHOL.IS</t>
+          <t>AKBNK.IS, BIMAS.IS, GARAN.IS, THYAO.IS</t>
         </is>
       </c>
     </row>
@@ -2921,7 +3036,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>TCELL.IS, KCHOL.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +3048,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, FROTO.IS, PGSUS.IS, SISE.IS, ARCLK.IS, PETKM.IS, TUPRS.IS</t>
+          <t>FROTO.IS, SISE.IS, PGSUS.IS, TUPRS.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3060,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %4.72 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3098,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3088,7 +3203,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3251,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3349,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +3357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3381,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14274</v>
+        <v>14183.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3391,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12543.48702636719</v>
+        <v>12562.15602539062</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +3425,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.45999999999999</v>
+        <v>75.48999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3344,16 +3459,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-26</t>
+          <t>Rapor Tarihi: 2026-06-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-29 06:26</t>
+          <t>Son Güncelleme: 2026-06-30 06:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3431,23 +3546,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="27" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>180.1000061035156</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.06947750968579758</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>694.7750968579767</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D4" s="27" t="n">
+        <v>177.1000061035156</v>
+      </c>
+      <c r="E4" s="28" t="n">
+        <v>0.05166278219926279</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>516.627821992628</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="5">
@@ -3461,23 +3576,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="27" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>219.1999969482422</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.1049407823142096</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-1049.407823142095</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D5" s="27" t="n">
+        <v>219.3000030517578</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>-0.1045324274509672</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>-1045.324274509674</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="6">
@@ -3491,23 +3606,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="27" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>138.3999938964844</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>0.1242891601300853</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1242.891601300851</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D6" s="27" t="n">
+        <v>137.3000030517578</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0.1153534098590743</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>1153.534098590744</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="7">
@@ -3521,23 +3636,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="27" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>0.01232397992215506</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>123.2397992215501</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D7" s="27" t="n">
+        <v>85.44999694824219</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0.002934272405571425</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>29.34272405571392</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="8">
@@ -3551,23 +3666,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="27" t="n">
         <v>45.5</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>45.31999969482422</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.003956050663204036</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-118.6815198961194</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D8" s="27" t="n">
+        <v>44.93999862670898</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>-0.01230772248991241</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>-369.2316746973738</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="9">
@@ -3581,23 +3696,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="27" t="n">
         <v>371.25</v>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>374.5</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>0.008754208754208737</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>262.6262626262615</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D9" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>-0.0006734006734007147</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>-20.20202020202123</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="10">
@@ -3611,23 +3726,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="27" t="n">
         <v>384</v>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>361.5</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>-0.05859375</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>-1757.8125</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D10" s="27" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>-0.06901041666666663</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>-2070.3125</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="11">
@@ -3641,23 +3756,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="27" t="n">
         <v>43.84000015258789</v>
       </c>
-      <c r="D11" s="25" t="n">
-        <v>40.65999984741211</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>-0.07253650305902348</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>-51588.52460381074</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D11" s="27" t="n">
+        <v>40.08000183105469</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>-0.08576638477295373</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>-60997.7192785145</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="12">
@@ -3671,23 +3786,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="27" t="n">
         <v>101.5</v>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>97.4499969482422</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>-0.03990150789909164</v>
-      </c>
-      <c r="F12" s="25" t="n">
-        <v>-28378.2624633346</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D12" s="27" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>-0.03940886699507384</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>-28027.8924244442</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="13">
@@ -3701,23 +3816,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="27" t="n">
         <v>40.34000015258789</v>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>42.11999893188477</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>0.04412490759950294</v>
-      </c>
-      <c r="F13" s="25" t="n">
-        <v>31381.97714722413</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H13" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D13" s="27" t="n">
+        <v>41.20000076293945</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>0.02131880533214114</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>15162.10000509804</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
     <row r="14">
@@ -3731,23 +3846,23 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="27" t="n">
         <v>341</v>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>325</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.04692082111436946</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-1577.633351826898</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>2256106.809120123</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.0415936952714535</v>
+      <c r="D14" s="27" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>-0.08064516129032262</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>-2711.557323452482</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>2228490.98662882</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>0.0349679068383319</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,6 +157,9 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -164,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -171,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -613,7 +621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -630,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -681,7 +689,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 75.49/100</t>
+          <t>Güven Puanı: 73.51/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -741,7 +749,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, ASELS.IS, YKBNK.IS, EREGL.IS, SAHOL.IS</t>
+          <t>AL: TOASO.IS, GARAN.IS, BIMAS.IS, ASELS.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -758,7 +766,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: AKBNK.IS, BIMAS.IS, GARAN.IS, THYAO.IS</t>
+          <t>AZALT: AKBNK.IS, THYAO.IS, YKBNK.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -775,7 +783,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TCELL.IS, KCHOL.IS, PETKM.IS</t>
+          <t>ÇIK: TCELL.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -961,29 +969,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1187312562404738</v>
+        <v>0.1192721735859763</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>11873.12562404738</v>
+        <v>11927.21735859763</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0885068840144367</v>
+        <v>0.1075944563040492</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1050.853352496398</v>
+        <v>1283.30246691853</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>341.2469081385259</v>
+        <v>341.1390925416471</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>295.9389557075669</v>
+        <v>290.8567375053864</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.580026089364279</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>1.933068023199164</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -995,7 +1003,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1004,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09969717153026461</v>
+        <v>0.1013931535874839</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9969.71715302646</v>
+        <v>10139.31535874839</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.07687227844927789</v>
+        <v>0.0795560183272892</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>766.3948730479922</v>
+        <v>806.6435585067518</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>384.9818395456169</v>
+        <v>148.9787305291659</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>334.9701730769033</v>
+        <v>130.8531477486779</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.21979807654197</v>
+        <v>1.536163074748743</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1045,27 +1053,27 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09946612601007221</v>
+        <v>0.09865741062053629</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9946.61260100722</v>
+        <v>9865.741062053628</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0517422093657887</v>
+        <v>0.0485933259961082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>514.6597116817077</v>
+        <v>479.4091716215627</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>42.15382967717832</v>
+        <v>382.9987123200785</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>37.61313124246275</v>
+        <v>346.9875</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.8406715195008853</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+        <v>0.9718665199221657</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1077,7 +1085,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1086,29 +1094,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09263864985518612</v>
+        <v>0.09359909550416579</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9263.864985518612</v>
+        <v>9359.909550416578</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0521950301469675</v>
+        <v>0.0768722134832022</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>483.5277121965806</v>
+        <v>719.5169651430863</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>43.35043604481616</v>
+        <v>371.5209136517048</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>38.83821727971362</v>
+        <v>323.2093174402703</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.9105133036748783</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.217075857032437</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1127,62 +1135,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08946679636400325</v>
+        <v>0.08707816670183768</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8946.679636400324</v>
+        <v>8707.816670183769</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0615383787458729</v>
+        <v>0.0706177639409747</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>550.5641599827916</v>
+        <v>614.9265420563218</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>103.4999919277226</v>
+        <v>104.385231984245</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>92.48939489153216</v>
+        <v>92.49025918236823</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.197458549982861</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
+        <v>1.374368901483381</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="D25" s="12" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>50000.00000000001</v>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1200,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1223,7 +1231,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1244,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1286,7 +1294,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1424,691 +1432,634 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>308</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0124320687288295</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.1075944563040492</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.1261892695744424</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>304.1709228315205</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>341.1390925416471</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>346.8662950289283</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>290.8567375053864</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>77.19999694824219</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0253877384495302</v>
-      </c>
-      <c r="F8" s="15" t="n">
+      <c r="D9" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0253879955685062</v>
+      </c>
+      <c r="F9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>0.0856124069061925</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>75.24006361741569</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>77.19999694824219</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>83.80927450013192</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>72.36299207104064</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="G9" s="19" t="n">
+        <v>0.08561253175330159</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>75.04512434122502</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>83.59216494500423</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>72.19412251685469</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M9" s="17" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.0425415966915239</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.0885068840144367</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.1296240786332305</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>300.1632094372072</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>341.2469081385259</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>354.1371486515178</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>295.9389557075669</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.0037105176120389</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.0485933259961082</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.132352990185063</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>363.8947334422028</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>382.9987123200785</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>413.5919296650943</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>346.9875</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>138</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0072551138029504</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0795560183272892</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.193842776901062</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>136.9987942951929</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>148.9787305291659</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>164.7503032123466</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>130.8531477486779</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="16" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="M11" s="14" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O11" s="14" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>371</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0037105176120389</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0219942018242906</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.085651551868344</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>369.6233979659336</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>379.1598488768119</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>402.7767257431556</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>352.45</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="D12" s="18" t="n">
+        <v>326</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.0557183387298561</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.003753763602968</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.0731182729479942</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>307.8358215740669</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>327.2237269345676</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>349.8365569810461</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>307.8358215740669</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>345</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0197860443083401</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.0768722134832022</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.2317506214474041</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>338.1738147136227</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>371.5209136517048</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>424.9539643993544</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>323.2093174402703</v>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>40.13999938964844</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.0177083448864976</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.1046024808035823</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>37.99700673884659</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>40.85081234258413</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>44.33874290525995</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>37.67576025480658</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.007822789977818</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.0706177639409747</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.1358528461501646</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>98.26272202283727</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>104.385231984245</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>110.7456524996411</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>92.49025918236823</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="13" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="M15" s="14" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>40.08000183105469</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0277778126436635</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.0517422093657887</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.2319541705328982</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>38.96666704943396</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>42.15382967717832</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>49.37672541073402</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>37.61313124246275</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>107.4000015258789</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>-0.0448027560808507</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.0056461366774436</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>0.0564225381710495</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>102.588185454432</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>106.7936064381061</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>113.4597822115436</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>102.030001449585</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>137.3000030517578</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.007255186297481</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0.0426715907258359</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.1446542915756432</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>136.3038659509726</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>143.1588125886385</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>157.1610377265435</v>
-      </c>
-      <c r="K12" s="14" t="n">
-        <v>130.1810334807738</v>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N12" s="13" t="inlineStr">
+      <c r="D17" s="18" t="n">
+        <v>40.47999954223633</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0901384342712845</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.026105717237156</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.09721897968183819</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>36.83119576419683</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>41.53675896404615</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>44.41542379525382</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>36.83119576419683</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>329</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.051580557859116</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0.003753763602968</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>0.1176163250763418</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>312.0299964643509</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>330.2349882253765</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>367.6957709501165</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>312.0299964643509</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.0567376780722056</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0048224528887045</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.1051306575728901</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>182.5212592930282</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>192.5668553660357</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>213.8427822403542</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>182.5212592930282</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="13" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N13" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
+      <c r="M18" s="23" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>357.5</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.0161982288834289</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>0.07687227844927789</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.1760202663201471</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>351.7091331741742</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>384.9818395456169</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>420.4272452094526</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>334.9701730769033</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>41.20000076293945</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>-0.0573248407643312</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>0.0521950301469675</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.1107635436316054</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>38.83821727971362</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>43.35043604481616</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>45.76345884506748</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>38.83821727971362</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>109.5999984741211</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>-0.06342762253785331</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>-0.0259136860515759</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0.0289375215740421</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>102.6483311407552</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>106.7598585224095</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>112.771550794481</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>102.6483311407552</v>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N16" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="19" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>0.0013325969181725</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>0.0615383787458729</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>0.1339262703921544</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>97.62992819952183</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>103.4999919277226</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>110.5578113632351</v>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v>92.48939489153216</v>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="16" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>195.6999969482422</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0567376780722056</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0048224528887045</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.0931571382971832</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>184.5964335226612</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>194.7562429326397</v>
-      </c>
-      <c r="J18" s="23" t="n">
-        <v>213.9308486287079</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>184.5964335226612</v>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>19.20000076293945</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0355161231779836</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.0011987972727639</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.0637570370071823</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>18.51809117082552</v>
-      </c>
-      <c r="I19" s="23" t="n">
-        <v>19.17698385438777</v>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>20.42413592212011</v>
-      </c>
-      <c r="K19" s="23" t="n">
-        <v>18.06516413653845</v>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="22" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="N19" s="22" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O19" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O19"/>
+  <autoFilter ref="A7:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2138,7 +2089,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2155,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2227,734 +2178,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.0405405405405405</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.1344383057090239</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.3291202895039857</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>0.0905274016867432</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.027829971582165</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.1075944563040492</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>0.2062499523162841</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.1539610640872546</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0.1505311399001552</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>0.1126751215487678</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E5" s="19" t="n">
+        <v>0.2087911943134301</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.1737805151074227</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.1426005713374192</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.0730250980207471</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.0313277530337499</v>
-      </c>
-      <c r="K4" s="15" t="n">
+      <c r="J5" s="19" t="n">
+        <v>0.0312069966438007</v>
+      </c>
+      <c r="K5" s="19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>0.0591216216216217</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.1206434316353888</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.3310906547240273</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.07495271326499869</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="E6" s="16" t="n">
+        <v>-0.0110374342014369</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.06575426047494209</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.3686946450283104</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.137998360091919</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.020100802691767</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.0485933259961082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.1210398189323396</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.1440375433869931</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.015394098141263</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.028116501409156</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0280080451234977</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.0885068840144367</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="J7" s="16" t="n">
+        <v>0.0258943922149351</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.0795560183272892</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0001815096221894</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.0920418806874523</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0.3837933920600045</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.1305601821820861</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="E8" s="19" t="n">
+        <v>0.118353344768439</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.129004329004329</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.2325141776937618</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.0127105153690736</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.0225112815198325</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.003753763602968</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.1015625</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.0764430577223089</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.5610859728506787</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.1373510955290962</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0200078717909501</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0219942018242906</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="J9" s="16" t="n">
+        <v>0.0315806993619271</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0.0768722134832022</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0.2010772468248522</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.2267725517152612</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.123111289998417</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.0040081699593914</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0.0306955552106629</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>0.0177083448864976</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>0.208685223627425</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.2079566444368767</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.139283726076546</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.0237258246259215</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="E11" s="16" t="n">
+        <v>0.09550561797752791</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.114357713018393</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.1800643630169451</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>-0.0878507026962331</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0307743322840939</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0.0517422093657887</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="J11" s="16" t="n">
+        <v>0.0256909785519578</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.0706177639409747</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>0.0467836561709942</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0267686720134183</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.1431613093616857</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>0.0218775253361387</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>0.02342229465431</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>-0.0056461366774436</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>0.1171684405784707</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.1292365778260664</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.0247377425071808</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.0379426002611251</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="E13" s="19" t="n">
+        <v>0.0257601232970436</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.4876870274260509</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.7356348450531796</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-0.1734088502350548</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J8" s="15" t="n">
-        <v>0.0259248704033182</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>0.0426715907258359</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="J13" s="19" t="n">
+        <v>0.0278150966248688</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>0.026105717237156</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.1086773378264531</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.119047619047619</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0.2276119402985075</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.0160404485072016</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>0.0226086953990568</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.003753763602968</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0598290598290598</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.0808767951625093</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.5811587366181907</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.1245901410082888</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0403225806451612</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.0025773195876288</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.1991334160479538</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.0159376697174218</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="18" t="n">
-        <v>0.0315102474448905</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>0.07687227844927789</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="J14" s="25" t="n">
+        <v>0.0215142684327434</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>-0.0048224528887045</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>0.0658549773349965</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.4967812918639764</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.751686189256072</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>-0.1518902565442526</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>0.0277410798482514</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>0.0521950301469675</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.0076290366169758</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.1544999694824218</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.0395191935597799</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.0523806805880611</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0218445468993738</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>0.0808130856985159</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>0.0851484997437732</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.0300751588566836</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.1506561519592766</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>0.0584659158050941</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>-0.0263736431415264</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0.0412008951134119</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0.1723030117531336</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-0.1184166199344576</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J12" s="21" t="n">
-        <v>0.0233805152780982</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>-0.0259136860515759</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="J16" s="27" t="n">
+        <v>0.0263786514325273</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0121673317168956</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>0.0597826086956521</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>0.111856339981202</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.1793619412251483</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>-0.0485611030178532</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>0.0256954108126556</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>0.0615383787458729</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>0.0397862972082394</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>0.0028636883305923</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>-0.103889398296107</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.0943762766172319</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.021937418480809</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0755819672039007</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>0.0349021186234845</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>0.0160954867418874</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.2048498197431085</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>0.0170105173026695</v>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.0710493847698464</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.0789473684210526</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>0.2934423393672529</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.1672261723215927</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0214820549705343</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>-0.0048224528887045</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="J18" s="27" t="n">
+        <v>0.0225986625249971</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.0591900342525799</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="26" t="n">
-        <v>0.0154485490052367</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.1767823272063465</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>-0.0627502256282759</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>0.15449227409447</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="E19" s="27" t="n">
+        <v>-0.0447115531334509</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.0800926067211009</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>-0.0326192655663796</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-0.0892604208174311</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="26" t="n">
-        <v>0.0222440191112051</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>0.1212598686799699</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="J19" s="27" t="n">
+        <v>0.0185044158451256</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.07594938363664309</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.0060245584030921</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>0.0143510328026927</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>0.1830581408894263</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.1189271392146106</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0268062082262847</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.0236686907772818</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>0.0411522618978632</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>0.0005650062345514</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.1339853002273074</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.09132005910616819</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="E20" s="27" t="n">
+        <v>-0.1712922353456524</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>-0.0678048482755335</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>0.1781751799839863</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-0.155712295870134</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0219585496251258</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.009701613552635499</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.0715495093769523</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.0881496754604664</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>0.2333497870993663</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>-0.1679923126599778</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.022350643703123</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.07594938363664309</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.0202507091217102</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.08054300023419821</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>-0.053122128756019</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>-0.1033775326630218</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0185132711703563</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.1004505040129337</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.1312216999309126</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>0.1657560147784205</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.1786406559219421</v>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.0295530359715273</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>-0.0011987972727639</v>
+      <c r="J20" s="27" t="n">
+        <v>0.028274682178536</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.0649745159602987</v>
       </c>
     </row>
   </sheetData>
@@ -2979,7 +2930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2987,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3012,7 +2963,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, YKBNK.IS, ASELS.IS, EREGL.IS, SAHOL.IS</t>
+          <t>TOASO.IS, BIMAS.IS, GARAN.IS, ASELS.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -3024,7 +2975,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BIMAS.IS, GARAN.IS, THYAO.IS</t>
+          <t>AKBNK.IS, THYAO.IS, YKBNK.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -3036,7 +2987,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, KCHOL.IS, PETKM.IS</t>
+          <t>TCELL.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -3048,7 +2999,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, SISE.IS, PGSUS.IS, TUPRS.IS, ARCLK.IS</t>
+          <t>FROTO.IS, SISE.IS, PGSUS.IS, TUPRS.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3011,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %4.72 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.73 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3106,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3167,7 +3118,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3130,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3154,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>NEW BUY</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3274,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3300,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3357,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3381,7 +3332,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14183.2001953125</v>
+        <v>14121.7998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3391,7 +3342,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12562.15602539062</v>
+        <v>12580.33452636719</v>
       </c>
     </row>
     <row r="6">
@@ -3425,7 +3376,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>75.48999999999999</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3459,7 +3410,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -3468,7 +3419,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-29</t>
+          <t>Rapor Tarihi: 2026-06-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3482,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-30 06:00</t>
+          <t>Son Güncelleme: 2026-07-01 06:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3546,23 +3497,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="27" t="n">
-        <v>177.1000061035156</v>
-      </c>
-      <c r="E4" s="28" t="n">
-        <v>0.05166278219926279</v>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>516.627821992628</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D4" s="28" t="n">
+        <v>175.1000061035156</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.03978629720823945</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>397.8629720823956</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="5">
@@ -3576,23 +3527,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="27" t="n">
-        <v>219.3000030517578</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>-0.1045324274509672</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>-1045.324274509674</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D5" s="28" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>-0.07104938476984657</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>-710.4938476984662</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="6">
@@ -3606,23 +3557,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="27" t="n">
-        <v>137.3000030517578</v>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>0.1153534098590743</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>1153.534098590744</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D6" s="28" t="n">
+        <v>138</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>0.1210398189323396</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>1210.398189323396</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="7">
@@ -3636,23 +3587,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D7" s="27" t="n">
-        <v>85.44999694824219</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>0.002934272405571425</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>29.34272405571392</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D7" s="28" t="n">
+        <v>84.55000305175781</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-0.007629036616975893</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-76.29036616975827</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="8">
@@ -3666,23 +3617,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>45.5</v>
       </c>
-      <c r="D8" s="27" t="n">
-        <v>44.93999862670898</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>-0.01230772248991241</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>-369.2316746973738</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D8" s="28" t="n">
+        <v>44.29999923706055</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.02637364314152646</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-791.2092942457966</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="9">
@@ -3696,23 +3647,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>371.25</v>
       </c>
-      <c r="D9" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>-0.0006734006734007147</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>-20.20202020202123</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D9" s="28" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>-0.01616161616161615</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>-484.8484848484877</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="10">
@@ -3726,23 +3677,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <v>384</v>
       </c>
-      <c r="D10" s="27" t="n">
-        <v>357.5</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>-0.06901041666666663</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>-2070.3125</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D10" s="28" t="n">
+        <v>345</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-0.1015625</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-3046.875</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="11">
@@ -3756,23 +3707,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>43.84000015258789</v>
       </c>
-      <c r="D11" s="27" t="n">
-        <v>40.08000183105469</v>
-      </c>
-      <c r="E11" s="28" t="n">
-        <v>-0.08576638477295373</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>-60997.7192785145</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D11" s="28" t="n">
+        <v>40.13999938964844</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>-0.08439782732804213</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>-60024.39058963221</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="12">
@@ -3786,23 +3737,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <v>101.5</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="28" t="n">
         <v>97.5</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="29" t="n">
         <v>-0.03940886699507384</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="28" t="n">
         <v>-28027.8924244442</v>
       </c>
-      <c r="G12" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="G12" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="13">
@@ -3816,23 +3767,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <v>40.34000015258789</v>
       </c>
-      <c r="D13" s="27" t="n">
-        <v>41.20000076293945</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>0.02131880533214114</v>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>15162.10000509804</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D13" s="28" t="n">
+        <v>40.47999954223633</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>0.003470485600368889</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>2468.236325593432</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
     <row r="14">
@@ -3846,23 +3797,23 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="28" t="n">
         <v>341</v>
       </c>
-      <c r="D14" s="27" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>-0.08064516129032262</v>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>-2711.557323452482</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>2228490.98662882</v>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>0.0349679068383319</v>
+      <c r="D14" s="28" t="n">
+        <v>308</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>-0.09677419354838712</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>-3253.86878814298</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>2214532.25016672</v>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>0.0304874346677976</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -101,7 +101,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,10 +157,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,15 +170,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -199,13 +190,13 @@
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -638,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 73.51/100</t>
+          <t>Güven Puanı: 73.74/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -749,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, GARAN.IS, BIMAS.IS, ASELS.IS, SAHOL.IS</t>
+          <t>AL: GARAN.IS, ASELS.IS, BIMAS.IS, SAHOL.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -766,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: AKBNK.IS, THYAO.IS, YKBNK.IS, EREGL.IS</t>
+          <t>AZALT: AKBNK.IS, YKBNK.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -783,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TCELL.IS, KCHOL.IS</t>
+          <t>ÇIK: THYAO.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -960,7 +951,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -969,29 +960,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1192721735859763</v>
+        <v>0.114139660311098</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>11927.21735859763</v>
+        <v>11413.9660311098</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1075944563040492</v>
+        <v>0.0578014188524056</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1283.30246691853</v>
+        <v>659.743431331307</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>341.1390925416471</v>
+        <v>146.5054965110582</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>290.8567375053864</v>
+        <v>131.3297765631322</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.933068023199164</v>
+        <v>1.116491917099201</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1003,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1012,29 +1003,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1013931535874839</v>
+        <v>0.1083332960868082</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10139.31535874839</v>
+        <v>10833.32960868082</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0795560183272892</v>
+        <v>0.0439164979259993</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>806.6435585067518</v>
+        <v>475.7618972912979</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>148.9787305291659</v>
+        <v>387.5539998550273</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>130.8531477486779</v>
+        <v>346.7915811320096</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.536163074748743</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.6666007293040886</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1053,27 +1044,27 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09865741062053629</v>
+        <v>0.1033626958735918</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9865.741062053628</v>
+        <v>10336.26958735918</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485933259961082</v>
+        <v>0.0184997569678012</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>479.4091716215627</v>
+        <v>191.2184753198196</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>382.9987123200785</v>
+        <v>371.2431614147635</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>346.9875</v>
+        <v>346.275</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718665199221657</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
+        <v>0.3699951393560218</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1094,29 +1085,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09359909550416579</v>
+        <v>0.09368745046372863</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9359.909550416578</v>
+        <v>9368.745046372864</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0768722134832022</v>
+        <v>0.0625594679672478</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>719.5169651430863</v>
+        <v>586.1037056218747</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>371.5209136517048</v>
+        <v>104.2370821862499</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>323.2093174402703</v>
+        <v>93.05917785086693</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.217075857032437</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>1.217477107560113</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1135,29 +1126,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08707816670183768</v>
+        <v>0.08047689726477339</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8707.816670183769</v>
+        <v>8047.689726477339</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0706177639409747</v>
+        <v>0.0345253730965184</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>614.9265420563218</v>
+        <v>277.8494903716482</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>104.385231984245</v>
+        <v>41.83620466731881</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>92.49025918236823</v>
+        <v>37.18927267083114</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.374368901483381</v>
+        <v>0.4295059194655455</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1176,10 +1167,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000.00000000001</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1208,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1252,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1294,7 +1285,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 11</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1437,45 +1428,45 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>308</v>
+        <v>328.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0124320687288295</v>
+        <v>-0.0573247356291898</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1075944563040492</v>
+        <v>-0.0060568152394418</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.1261892695744424</v>
+        <v>0.2096024936288811</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>304.1709228315205</v>
+        <v>309.6688243458111</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>341.1390925416471</v>
+        <v>326.5103361938434</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>346.8662950289283</v>
+        <v>397.3544191570875</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>290.8567375053864</v>
+        <v>309.6688243458111</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>73.51000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1484,7 +1475,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1503,28 +1494,28 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>77</v>
+        <v>77.84999847412109</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.0253879955685062</v>
+        <v>-0.0310387374300392</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.08561253175330159</v>
+        <v>0.0756738918268213</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>75.04512434122502</v>
+        <v>75.4336328125539</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>77</v>
+        <v>77.84999847412109</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>83.59216494500423</v>
+        <v>83.74121083736995</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>72.19412251685469</v>
+        <v>72.98887999180168</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1532,7 +1523,7 @@
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>73.51000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1546,173 +1537,173 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
-        <v>365.25</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.0037105176120389</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0485933259961082</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.132352990185063</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>363.8947334422028</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>382.9987123200785</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>413.5919296650943</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>346.9875</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="D10" s="21" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>-0.0156773487587726</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>0.0184997569678012</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0.085651551868344</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>358.7856063774274</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>371.2431614147635</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>395.7199906560114</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>346.275</v>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="14" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="M10" s="20" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.065000031562885</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>0.0439164979259993</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.1431977512695257</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>347.1187382822789</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>387.5539998550273</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>424.4121651588114</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>346.7915811320096</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
-        <v>138</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0072551138029504</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0795560183272892</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.193842776901062</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>136.9987942951929</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>148.9787305291659</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>164.7503032123466</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>130.8531477486779</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
+      <c r="D12" s="21" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.007255186297481</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0578014188524056</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.1938424747605409</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>137.4951566977989</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>146.5054965110582</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>165.3471827543349</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>131.3297765631322</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="14" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>326</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.0557183387298561</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.003753763602968</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.0731182729479942</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>307.8358215740669</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>327.2237269345676</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>349.8365569810461</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>307.8358215740669</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1722,45 +1713,45 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0197860443083401</v>
+        <v>-0.1202789269533691</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0768722134832022</v>
+        <v>-0.0207253991955953</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.2317506214474041</v>
+        <v>0.1082855521223511</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>338.1738147136227</v>
+        <v>268.3149272792224</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>371.5209136517048</v>
+        <v>298.6787532453434</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>424.9539643993544</v>
+        <v>338.0270933973171</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>323.2093174402703</v>
+        <v>268.3149272792224</v>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M13" s="14" t="n">
-        <v>73.51000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1769,7 +1760,7 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1788,28 +1779,28 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>40.13999938964844</v>
+        <v>40.59999847412109</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>-0.053387959227386</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>0.0177083448864976</v>
+        <v>0.0114598677495567</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>0.1046024808035823</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>37.99700673884659</v>
+        <v>38.43244741095278</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>40.85081234258413</v>
+        <v>41.06526908726673</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>44.33874290525995</v>
+        <v>44.84685903513582</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>37.67576025480658</v>
+        <v>38.10687584438732</v>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
@@ -1817,7 +1808,7 @@
         </is>
       </c>
       <c r="M14" s="17" t="n">
-        <v>73.51000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="N14" s="17" t="inlineStr">
         <is>
@@ -1831,57 +1822,57 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.007822789977818</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.0706177639409747</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.1358528461501646</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>98.26272202283727</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>104.385231984245</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>110.7456524996411</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>92.49025918236823</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>195</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.038998563167911</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.0023753368781342</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1410511046048663</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>187.3952801822574</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>195.4631906912362</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>222.504965397949</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O15" s="14" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
@@ -1893,173 +1884,116 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>107.4000015258789</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.0448027560808507</v>
+        <v>0.0104710915185266</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.0056461366774436</v>
+        <v>0.0625594679672478</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.0564225381710495</v>
+        <v>0.1293435773389155</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>102.588185454432</v>
+        <v>99.12721253611095</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>106.7936064381061</v>
+        <v>104.2370821862499</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>113.4597822115436</v>
+        <v>110.7886032137061</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>102.030001449585</v>
+        <v>93.05917785086693</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>40.43999862670898</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>-0.08038392844382709</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>0.0345253730965184</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>0.125270489479642</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>37.18927267083114</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>41.83620466731881</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>45.50593704923286</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>37.18927267083114</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="20" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
+      <c r="M17" s="20" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>40.47999954223633</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>-0.0901384342712845</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>0.026105717237156</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.09721897968183819</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>36.83119576419683</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>41.53675896404615</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>44.41542379525382</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>36.83119576419683</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0567376780722056</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0048224528887045</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.1051306575728901</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>182.5212592930282</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>192.5668553660357</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>213.8427822403542</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>182.5212592930282</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O18"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2089,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2106,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2183,30 +2117,30 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.0405405405405405</v>
+        <v>0.0949999999999999</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.1344383057090239</v>
+        <v>0.1163976210705182</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.3291202895039857</v>
+        <v>0.2268907563025211</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.0905274016867432</v>
+        <v>0.0249012369443828</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2214,10 +2148,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.027829971582165</v>
+        <v>0.0224191724045745</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1075944563040492</v>
+        <v>-0.0060568152394418</v>
       </c>
     </row>
     <row r="5">
@@ -2240,16 +2174,16 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2087911943134301</v>
+        <v>0.1804397585524995</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1737805151074227</v>
+        <v>0.1795454314260771</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.1426005713374192</v>
+        <v>0.1519014020431326</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.0730250980207471</v>
+        <v>0.0353464693198231</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2257,139 +2191,139 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0312069966438007</v>
+        <v>0.0312210570173315</v>
       </c>
       <c r="K5" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>-0.0376928481841954</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>0.0416444605261814</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>0.3495338524200444</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>0.1382485610813038</v>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>0.0199431900602463</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>0.0184997569678012</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>-0.0110374342014369</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.06575426047494209</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.3686946450283104</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.137998360091919</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="E7" s="22" t="n">
+        <v>-0.0895156345800122</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>0.1592505854800936</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>0.6211790393013101</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>0.1583183153530907</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.020100802691767</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0485933259961082</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="J7" s="22" t="n">
+        <v>0.0329406314720409</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>0.0439164979259993</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>0.1210398189323396</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.1440375433869931</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.015394098141263</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>0.028116501409156</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="E8" s="22" t="n">
+        <v>0.0753105335280488</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0.1391060637482473</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>0.014767039515241</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>0.0373583025077255</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>0.0258943922149351</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0795560183272892</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.118353344768439</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.129004329004329</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.2325141776937618</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.0127105153690736</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0.0225112815198325</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.003753763602968</v>
+      <c r="J8" s="22" t="n">
+        <v>0.0258852831655878</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0.0578014188524056</v>
       </c>
     </row>
     <row r="9">
@@ -2398,30 +2332,30 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.1015625</v>
+        <v>0.0082644628099173</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0764430577223089</v>
+        <v>0.1141552511415524</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.5610859728506787</v>
+        <v>0.3114093283394077</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>0.1373510955290962</v>
+        <v>0.0940731785552246</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -2429,10 +2363,10 @@
         </is>
       </c>
       <c r="J9" s="16" t="n">
-        <v>0.0315806993619271</v>
+        <v>0.0278609039481065</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0768722134832022</v>
+        <v>-0.0207253991955953</v>
       </c>
     </row>
     <row r="10">
@@ -2455,16 +2389,16 @@
         </is>
       </c>
       <c r="E10" s="19" t="n">
-        <v>0.2010772468248522</v>
+        <v>0.160663207702417</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.2267725517152612</v>
+        <v>0.2295577804746884</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.123111289998417</v>
+        <v>0.1347121257481198</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>0.0040081699593914</v>
+        <v>-0.008217096639550199</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -2472,53 +2406,53 @@
         </is>
       </c>
       <c r="J10" s="19" t="n">
-        <v>0.0306955552106629</v>
+        <v>0.0307034818156819</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>0.0177083448864976</v>
+        <v>0.0114598677495567</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.09550561797752791</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.114357713018393</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.1800643630169451</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>-0.0878507026962331</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0256909785519578</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.0706177639409747</v>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.0087946038355053</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.0010266783629826</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.1991168988658911</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.0242028346028209</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>0.0215298288627306</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>0.0023753368781342</v>
       </c>
     </row>
     <row r="12">
@@ -2527,7 +2461,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2537,74 +2471,74 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E12" s="22" t="n">
-        <v>0.0467836561709942</v>
+        <v>0.0514468945912092</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0267686720134183</v>
+        <v>0.1149444802320109</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.1431613093616857</v>
+        <v>0.1937249558137976</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0.0218775253361387</v>
+        <v>-0.1066021595305367</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.02342229465431</v>
+        <v>0.0256922563795143</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>-0.0056461366774436</v>
+        <v>0.0625594679672478</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.0257601232970436</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0.4876870274260509</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.7356348450531796</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.1734088502350548</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0002472715955949</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0.4525111167195956</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.7121913591462934</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>-0.1942078931186766</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0278150966248688</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>0.026105717237156</v>
+      <c r="J13" s="22" t="n">
+        <v>0.0277505310635149</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>0.0345253730965184</v>
       </c>
     </row>
     <row r="14">
@@ -2613,7 +2547,7 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -2623,289 +2557,289 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>0.0403225806451612</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.0025773195876288</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.1991334160479538</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0.0159376697174218</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0.00184328984555</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0.0264399941644859</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.1625668122806651</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>-0.0028604535941085</v>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0215142684327434</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>-0.0048224528887045</v>
+      <c r="J14" s="24" t="n">
+        <v>0.0234197101909721</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.0459102174194094</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-0.0475583425974055</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>0.0332659882012171</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0.1834124335903009</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.1203039278513452</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>0.0263043245416862</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0136615265883807</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>0.0255517377076142</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>0.0062678410456731</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>-0.0811654063081359</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.0895376170679819</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>0.0219538516988067</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.0085665331108739</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>-0.0076290366169758</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.1544999694824218</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.0395191935597799</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>0.0523806805880611</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="E17" s="24" t="n">
+        <v>-0.0416198483029232</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.1572700471399996</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-0.0488496936173054</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>0.0162607712753948</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0218445468993738</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>0.0808130856985159</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="J17" s="24" t="n">
+        <v>0.0218156781753923</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0151907216513159</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
-        <v>-0.0263736431415264</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>0.0412008951134119</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0.1723030117531336</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-0.1184166199344576</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="E18" s="24" t="n">
+        <v>-0.0557442435494193</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.08499514791187671</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.3196898870988882</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.1446507246310463</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
-        <v>0.0263786514325273</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.0121673317168956</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="J18" s="24" t="n">
+        <v>0.0223858877554156</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.0283622708857007</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
-        <v>0.0397862972082394</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>0.0028636883305923</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.103889398296107</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.0943762766172319</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="E19" s="24" t="n">
+        <v>-0.0733518488424925</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.08103126653781929</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-0.0167487384063269</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.0795946804121215</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="27" t="n">
-        <v>0.021937418480809</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>0.0755819672039007</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="J19" s="24" t="n">
+        <v>0.0184988641637385</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.0402611029398059</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
-        <v>-0.0710493847698464</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>-0.0789473684210526</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0.2934423393672529</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-0.1672261723215927</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0225986625249971</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>0.0591900342525799</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>-0.0447115531334509</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>-0.0800926067211009</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>-0.0326192655663796</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-0.0892604208174311</v>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="E20" s="24" t="n">
+        <v>-0.1983122620944811</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.1046182556640031</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0.1677934520852231</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.1349944277205902</v>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="27" t="n">
-        <v>0.0185044158451256</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>0.07594938363664309</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>-0.1712922353456524</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>-0.0678048482755335</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>0.1781751799839863</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-0.155712295870134</v>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>0.028274682178536</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>0.0649745159602987</v>
+      <c r="J20" s="24" t="n">
+        <v>0.0279055661248015</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0.0294396733991557</v>
       </c>
     </row>
   </sheetData>
@@ -2930,7 +2864,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2938,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2963,7 +2897,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, BIMAS.IS, GARAN.IS, ASELS.IS, SAHOL.IS</t>
+          <t>BIMAS.IS, ASELS.IS, GARAN.IS, SAHOL.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2909,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, THYAO.IS, YKBNK.IS, EREGL.IS</t>
+          <t>AKBNK.IS, YKBNK.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2921,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, KCHOL.IS</t>
+          <t>THYAO.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, SISE.IS, PGSUS.IS, TUPRS.IS, ARCLK.IS, PETKM.IS</t>
+          <t>TCELL.IS, SISE.IS, PGSUS.IS, FROTO.IS, TUPRS.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -3011,7 +2945,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.73 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3049,7 +2983,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3057,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3106,7 +3040,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3052,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3064,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3088,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3136,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3184,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>NEW BUY</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3234,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3308,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3332,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14121.7998046875</v>
+        <v>14350.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3342,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12580.33452636719</v>
+        <v>12599.15602539062</v>
       </c>
     </row>
     <row r="6">
@@ -3376,7 +3310,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.51000000000001</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3403,23 +3337,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-06-30</t>
+          <t>Rapor Tarihi: 2026-07-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3433,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-01 06:15</t>
+          <t>Son Güncelleme: 2026-07-02 05:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3497,23 +3431,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>175.1000061035156</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.03978629720823945</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>397.8629720823956</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D4" s="25" t="n">
+        <v>176.6000061035156</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.04869366095150696</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>486.936609515069</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="5">
@@ -3527,23 +3461,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>227.5</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>-0.07104938476984657</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>-710.4938476984662</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D5" s="25" t="n">
+        <v>236.3000030517578</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.03511633752168108</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-351.1633752168127</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="6">
@@ -3557,23 +3491,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>138</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>0.1210398189323396</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>1210.398189323396</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D6" s="25" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.1251015574067322</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1251.015574067322</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="7">
@@ -3587,23 +3521,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>84.55000305175781</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.007629036616975893</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-76.29036616975827</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D7" s="25" t="n">
+        <v>85.19999694824219</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="8">
@@ -3617,23 +3551,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="25" t="n">
         <v>45.5</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>44.29999923706055</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.02637364314152646</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-791.2092942457966</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D8" s="25" t="n">
+        <v>44.86000061035156</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.01406592065161405</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-421.9776195484228</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="9">
@@ -3647,23 +3581,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="25" t="n">
         <v>371.25</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>365.25</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>-0.01616161616161615</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-484.8484848484877</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D9" s="25" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>-0.01818181818181819</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>-545.4545454545478</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="10">
@@ -3677,23 +3611,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="25" t="n">
         <v>384</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>345</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-0.1015625</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-3046.875</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D10" s="25" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.033203125</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>-996.09375</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="11">
@@ -3707,23 +3641,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="25" t="n">
         <v>43.84000015258789</v>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>40.13999938964844</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>-0.08439782732804213</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>-60024.39058963221</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D11" s="25" t="n">
+        <v>40.59999847412109</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>-0.07390514751801469</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>-52561.91517778265</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="12">
@@ -3737,23 +3671,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="25" t="n">
         <v>101.5</v>
       </c>
-      <c r="D12" s="28" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>-0.03940886699507384</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>-28027.8924244442</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D12" s="25" t="n">
+        <v>98.09999847412109</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>-0.03349755197910254</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>-23823.71925257007</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
     <row r="13">
@@ -3767,57 +3701,27 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="25" t="n">
         <v>40.34000015258789</v>
       </c>
-      <c r="D13" s="28" t="n">
-        <v>40.47999954223633</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0.003470485600368889</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>2468.236325593432</v>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0.0304874346677976</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>341</v>
-      </c>
-      <c r="D14" s="28" t="n">
-        <v>308</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>-0.09677419354838712</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>-3253.86878814298</v>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>2214532.25016672</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0.0304874346677976</v>
+      <c r="D13" s="25" t="n">
+        <v>40.43999862670898</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.00247889126779488</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>1763.006731310859</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>2228122.581627613</v>
+      </c>
+      <c r="H13" s="26" t="n">
+        <v>0.047183275640324</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H14"/>
+  <autoFilter ref="A3:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +101,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
@@ -131,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,10 +162,13 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,6 +189,15 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -188,15 +205,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +688,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 73.74/100</t>
+          <t>Güven Puanı: 75.78/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +748,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: GARAN.IS, ASELS.IS, BIMAS.IS, SAHOL.IS, EREGL.IS</t>
+          <t>AL: THYAO.IS, TOASO.IS, GARAN.IS, YKBNK.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +765,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: AKBNK.IS, YKBNK.IS, KCHOL.IS</t>
+          <t>AZALT: EREGL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +782,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, TOASO.IS</t>
+          <t>ÇIK: ASELS.IS, BIMAS.IS, AKBNK.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -951,7 +959,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -960,29 +968,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.114139660311098</v>
+        <v>0.1418636374261981</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>11413.9660311098</v>
+        <v>14186.36374261981</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0578014188524056</v>
+        <v>0.2096024767266591</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>659.743431331307</v>
+        <v>2973.496976198389</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>146.5054965110582</v>
+        <v>403.1000253691591</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>131.3297765631322</v>
+        <v>314.6818085013919</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.116491917099201</v>
+        <v>3.761810910577642</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -994,7 +1002,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +1011,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1083332960868082</v>
+        <v>0.1178243448889261</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10833.32960868082</v>
+        <v>11782.43448889261</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0439164979259993</v>
+        <v>0.1082854760144804</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>475.7618972912979</v>
+        <v>1275.866527239167</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>387.5539998550273</v>
+        <v>339.4124270294346</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>346.7915811320096</v>
+        <v>289.192557303994</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6666007293040886</v>
+        <v>1.944161714065119</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1043,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,27 +1052,27 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1033626958735918</v>
+        <v>0.08428062914572654</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10336.26958735918</v>
+        <v>8428.062914572654</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0184997569678012</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>191.2184753198196</v>
+        <v>279.1158350710165</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>371.2431614147635</v>
+        <v>143.1900829499451</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>346.275</v>
+        <v>131.4463346282519</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3699951393560218</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+        <v>0.6416393123868253</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1076,7 +1084,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,29 +1093,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09368745046372863</v>
+        <v>0.07913982403504768</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9368.745046372864</v>
+        <v>7913.982403504769</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0625594679672478</v>
+        <v>0.026062379703303</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>586.1037056218747</v>
+        <v>206.2572143653998</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>104.2370821862499</v>
+        <v>41.55552637798377</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>93.05917785086693</v>
+        <v>38.03716888153436</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.217477107560113</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.4285825244247249</v>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1125,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1126,62 +1134,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08047689726477339</v>
+        <v>0.07689156450410166</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8047.689726477339</v>
+        <v>7689.156450410166</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0204183581564147</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>277.8494903716482</v>
+        <v>156.9999503251811</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>41.83620466731881</v>
+        <v>197.6550328608278</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>37.18927267083114</v>
+        <v>184.0149971008301</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4295059194655455</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
+        <v>0.4083671631282952</v>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1222,7 +1230,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1423,572 +1431,572 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>384.75</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.065000031562885</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>-0.0395584808260567</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.1232090104953282</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>359.74123785618</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>369.5298745021747</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>432.1546667880776</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>359.1972700535711</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>-0.0557185041218549</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.2096024767266591</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.2789832810411945</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>314.6818085013919</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>403.1000253691591</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>426.2211784069781</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>314.6818085013919</v>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-0.0056818181818182</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.1082854760144804</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.1307693897609034</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>304.5099431818182</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>339.4124270294346</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>346.2981256142767</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>289.192557303994</v>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>328.5</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0573247356291898</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>-0.0060568152394418</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.2096024936288811</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>309.6688243458111</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>326.5103361938434</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>397.3544191570875</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>309.6688243458111</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D11" s="16" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0314232688469682</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>-0.0037105176120389</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.1453543644432943</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>346.2661813872089</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>356.1734899536961</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>409.4641852884778</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>339.625</v>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M11" s="15" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>77.94999694824219</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0860928157553027</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>-0.0301236938145638</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.1166665836624449</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>71.23906222285076</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>75.60185510732715</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>87.04415678869161</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>71.23906222285076</v>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>138.6000061035156</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-0.008288998220071</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.152022502552924</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>137.4511508996218</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>143.1900829499451</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>159.6703258852226</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>131.4463346282519</v>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>-0.0277778108086147</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>0.026062379703303</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>0.1235848352080751</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>39.3749986622511</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>41.55552637798377</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>45.50518582592704</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>38.03716888153436</v>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>193.6999969482422</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>-0.0097348326847777</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0.0204183581564147</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0.0729759755823018</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>191.8143598869091</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>197.6550328608278</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>207.835443195829</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>184.0149971008301</v>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>108.4000015258789</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.0448027560808507</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>-0.0050943225797922</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.0555149911412387</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>103.5433826983511</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>107.8477769504561</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>114.4178266502983</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>102.980001449585</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>40.79999923706055</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>-0.08933527791281801</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>0.0176860473833884</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>0.0831932668372119</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>37.15511996637498</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <v>41.52158995680941</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>44.19428446054737</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>37.15511996637498</v>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>77.84999847412109</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0310387374300392</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0756738918268213</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>75.4336328125539</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>77.84999847412109</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>83.74121083736995</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>72.98887999180168</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>364.5</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-0.0156773487587726</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0.0184997569678012</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0.085651551868344</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>358.7856063774274</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>371.2431614147635</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>395.7199906560114</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>346.275</v>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.065000031562885</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0.0439164979259993</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.1431977512695257</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>347.1187382822789</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>387.5539998550273</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>424.4121651588114</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>346.7915811320096</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.007255186297481</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0578014188524056</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.1938424747605409</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>137.4951566977989</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>146.5054965110582</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>165.3471827543349</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>131.3297765631322</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>305</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.1202789269533691</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>-0.0207253991955953</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.1082855521223511</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>268.3149272792224</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>298.6787532453434</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>338.0270933973171</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>268.3149272792224</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>40.59999847412109</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0.0114598677495567</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.1046024808035823</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>38.43244741095278</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>41.06526908726673</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>44.84685903513582</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>38.10687584438732</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>195</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.038998563167911</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>0.0023753368781342</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1410511046048663</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>187.3952801822574</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>195.4631906912362</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>222.504965397949</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>185.25</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>98.09999847412109</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>0.0104710915185266</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>0.0625594679672478</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>0.1293435773389155</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>99.12721253611095</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>104.2370821862499</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>110.7886032137061</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>93.05917785086693</v>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>40.43999862670898</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-0.08038392844382709</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>0.0345253730965184</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>0.125270489479642</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>37.18927267083114</v>
-      </c>
-      <c r="I17" s="21" t="n">
-        <v>41.83620466731881</v>
-      </c>
-      <c r="J17" s="21" t="n">
-        <v>45.50593704923286</v>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>37.18927267083114</v>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>73.73999999999999</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2031,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2112,734 +2120,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0.0032594524119948</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0.2014051522248243</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0.6605524603694604</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.1642761747828451</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0.0332069265060805</v>
+      </c>
+      <c r="K4" s="17" t="n">
+        <v>-0.0395584808260567</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0.1220538720538719</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>0.1182885906040267</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>0.2411545623836126</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>0.0522229076658125</v>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>0.0224334775809057</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>0.2096024767266591</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>0.024247491638796</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>0.1238532110091743</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>0.3253137272692095</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>0.0978604114157553</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>0.0278488860342956</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>0.1082854760144804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.0949999999999999</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.1163976210705182</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.2268907563025211</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.0249012369443828</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E7" s="17" t="n">
+        <v>-0.0567927122885886</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.0401215198792757</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.2985077075395863</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0.1429597223795853</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>0.0199656126278064</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>-0.0037105176120389</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.202004607283819</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0.1421244974101418</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.1525546975089651</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.009977621456205</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0224191724045745</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>-0.0060568152394418</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="J8" s="17" t="n">
+        <v>0.0309684020932089</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>-0.0301236938145638</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>0.1008737444298299</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.1195727246378437</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.0048847588973104</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>0.037302304693062</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>0.0258068945174537</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>0.1780104346058495</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.1821366603671084</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.1181667210118826</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>-0.0159662669399445</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>0.0304053224501931</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.026062379703303</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>0.0270413079516411</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-0.0107252608313827</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.1904170582967865</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>0.0442814511889992</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0.0215379322371052</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.0204183581564147</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.0245746540560038</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0.0111940728712529</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.1643394554513417</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0.0116528588929327</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0.0233762470758074</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>-0.0050943225797922</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.1804397585524995</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1795454314260771</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.1519014020431326</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.0353464693198231</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E13" s="23" t="n">
+        <v>0.0124069481257009</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0.4369268837550237</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0.7361359388446289</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>-0.1809919303685616</v>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0312210570173315</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="J13" s="23" t="n">
+        <v>0.0276987119262011</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.0176860473833884</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>-0.0376928481841954</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>0.0416444605261814</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>0.3495338524200444</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>0.1382485610813038</v>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.07552377435497119</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>0.07730535355143869</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.1764653814689465</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.119120152504353</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0254734136752352</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.061538384265372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>0.0411764705882353</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.0133778928547187</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.0766823014202294</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>-0.0845110267848225</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="22" t="n">
-        <v>0.0199431900602463</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>0.0184997569678012</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>-0.0895156345800122</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0.1592505854800936</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>0.6211790393013101</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>0.1583183153530907</v>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J15" s="25" t="n">
+        <v>0.0217761950942461</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0147321564810616</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.007986587658763001</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.0549753574314962</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0.3537619695978546</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.1513126326984402</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J7" s="22" t="n">
-        <v>0.0329406314720409</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>0.0439164979259993</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0.0753105335280488</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.1391060637482473</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0.014767039515241</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>0.0373583025077255</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0258852831655878</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0.0578014188524056</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0223765626924933</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0416218430715982</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0082644628099173</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.1141552511415524</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.3114093283394077</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.0940731785552246</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>-0.0392918762265791</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>0.0102725492697408</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>0.1745273510818865</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>-0.1217720897143876</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="16" t="n">
-        <v>0.0278609039481065</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>-0.0207253991955953</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="J17" s="25" t="n">
+        <v>0.0262685190895596</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.0191753146075474</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.160663207702417</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.2295577804746884</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1347121257481198</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.008217096639550199</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0307034818156819</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>0.0114598677495567</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.0562913634818335</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0948275611400447</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.0123762376237623</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.0735625397864777</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>0.0183868314613509</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0566279411125097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.0087946038355053</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0010266783629826</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.1991168988658911</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.0242028346028209</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0.0215298288627306</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>0.0023753368781342</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>-0.0590219244532953</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.1834146639195883</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.0655952982027229</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.0235374281295358</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.021795916664336</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.1002252939750626</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>0.0514468945912092</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.1149444802320109</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.1937249558137976</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>-0.1066021595305367</v>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>0.0256922563795143</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>0.0625594679672478</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0002472715955949</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>0.4525111167195956</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.7121913591462934</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>-0.1942078931186766</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>0.0277505310635149</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>0.0345253730965184</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n">
-        <v>0.00184328984555</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>0.0264399941644859</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.1625668122806651</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>-0.0028604535941085</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0234197101909721</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.0459102174194094</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0475583425974055</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>0.0332659882012171</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>0.1834124335903009</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.1203039278513452</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0263043245416862</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0136615265883807</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>0.0255517377076142</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>0.0062678410456731</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>-0.0811654063081359</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.0895376170679819</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.1632653130302539</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.0727630054637942</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>0.162045664959572</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.1150046819072787</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0219538516988067</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0085665331108739</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.0416198483029232</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.1572700471399996</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.0488496936173054</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>0.0162607712753948</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0218156781753923</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0151907216513159</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0557442435494193</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.08499514791187671</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.3196898870988882</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.1446507246310463</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0223858877554156</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0283622708857007</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0733518488424925</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.08103126653781929</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.0167487384063269</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.0795946804121215</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0184988641637385</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.0402611029398059</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.1983122620944811</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1046182556640031</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>0.1677934520852231</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.1349944277205902</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.0279055661248015</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.0294396733991557</v>
+      <c r="J20" s="25" t="n">
+        <v>0.0274420209648397</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.1000000839371915</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2872,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2880,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +2905,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, ASELS.IS, GARAN.IS, SAHOL.IS, EREGL.IS</t>
+          <t>THYAO.IS, TOASO.IS, GARAN.IS, YKBNK.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2917,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, YKBNK.IS, KCHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2929,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TOASO.IS</t>
+          <t>ASELS.IS, BIMAS.IS, AKBNK.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2941,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, SISE.IS, PGSUS.IS, FROTO.IS, TUPRS.IS, ARCLK.IS, PETKM.IS</t>
+          <t>SAHOL.IS, PGSUS.IS, TUPRS.IS, SISE.IS, ARCLK.IS, FROTO.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2953,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.50 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.91 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2991,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +2999,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3040,7 +3048,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3060,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3072,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3108,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3144,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3180,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3216,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3242,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +3250,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3274,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14350.599609375</v>
+        <v>14455</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3284,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12599.15602539062</v>
+        <v>12619.5165234375</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +3318,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.73999999999999</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="9">
@@ -3337,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3345,7 +3353,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3353,7 +3361,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-01</t>
+          <t>Rapor Tarihi: 2026-07-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-02 05:47</t>
+          <t>Son Güncelleme: 2026-07-03 05:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3431,23 +3439,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="26" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>176.6000061035156</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.04869366095150696</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>486.936609515069</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.047183275640324</v>
+      <c r="D4" s="26" t="n">
+        <v>177</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>0.05106892170555577</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>510.6892170555566</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="5">
@@ -3461,23 +3469,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <v>244.8999938964844</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>236.3000030517578</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.03511633752168108</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-351.1633752168127</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.047183275640324</v>
+      <c r="D5" s="26" t="n">
+        <v>239.8000030517578</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>-0.0208247895950634</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>-208.2478959506352</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="6">
@@ -3491,23 +3499,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>0.1251015574067322</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1251.015574067322</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.047183275640324</v>
+      <c r="D6" s="26" t="n">
+        <v>138.6000061035156</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>0.1259139546833792</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>1259.139546833792</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="7">
@@ -3521,23 +3529,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.047183275640324</v>
+      <c r="D7" s="26" t="n">
+        <v>83.69999694824219</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>-0.01760563443342877</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-176.0563443342871</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="8">
@@ -3551,89 +3559,89 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <v>45.5</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>44.86000061035156</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.01406592065161405</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-421.9776195484228</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.047183275640324</v>
+      <c r="D8" s="26" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>-0.02197802197802201</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-659.3406593406617</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>364.5</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>-0.01818181818181819</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>-545.4545454545478</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.047183275640324</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>-0.07618613460225387</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>-54184.17091597966</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>384</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>-0.033203125</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>-996.09375</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.047183275640324</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>97.55000305175781</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>-0.03891622609105605</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>-27677.52238555369</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3641,87 +3649,117 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C11" s="25" t="n">
-        <v>43.84000015258789</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>40.59999847412109</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>-0.07390514751801469</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>-52561.91517778265</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.047183275640324</v>
+      <c r="C11" s="26" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>40.79999923706055</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>0.0114030511336809</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>8109.938571063103</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>98.09999847412109</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>-0.03349755197910254</v>
-      </c>
-      <c r="F12" s="25" t="n">
-        <v>-23823.71925257007</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>0.047183275640324</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>40.43999862670898</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>0.00247889126779488</v>
-      </c>
-      <c r="F13" s="25" t="n">
-        <v>1763.006731310859</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>2228122.581627613</v>
-      </c>
-      <c r="H13" s="26" t="n">
-        <v>0.047183275640324</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>0.0548015178050205</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>193.6999969482422</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>193.6999969482422</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>2229243.858205974</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>0.0548015178050205</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H13"/>
+  <autoFilter ref="A3:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -165,9 +165,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -180,6 +177,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -189,15 +195,6 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -205,6 +202,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -620,7 +626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -637,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -688,7 +694,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 75.78/100</t>
+          <t>Güven Puanı: 69.53/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -748,7 +754,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: THYAO.IS, TOASO.IS, GARAN.IS, YKBNK.IS, KCHOL.IS</t>
+          <t>AL: THYAO.IS, ASELS.IS, TOASO.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -765,7 +771,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: EREGL.IS</t>
+          <t>AZALT: YKBNK.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -782,7 +788,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: ASELS.IS, BIMAS.IS, AKBNK.IS, TCELL.IS</t>
+          <t>ÇIK: BIMAS.IS, AKBNK.IS, KCHOL.IS, TUPRS.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -968,25 +974,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1418636374261981</v>
+        <v>0.1380396172060904</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>14186.36374261981</v>
+        <v>13803.96172060904</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.2096024767266591</v>
+        <v>0.211966460056985</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2973.496976198389</v>
+        <v>2925.976900679626</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>403.1000253691591</v>
+        <v>404.796797659033</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>314.6818085013919</v>
+        <v>317.3</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>3.761810910577642</v>
+        <v>4.239329201139705</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1002,7 +1008,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1011,25 +1017,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1178243448889261</v>
+        <v>0.1275711168923382</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11782.43448889261</v>
+        <v>12757.11168923382</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1082854760144804</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1275.866527239167</v>
+        <v>1606.608962717493</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>339.4124270294346</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>289.192557303994</v>
+        <v>373.1666787300279</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.944161714065119</v>
+        <v>1.910596481506183</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1043,7 +1049,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1052,29 +1058,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.08428062914572654</v>
+        <v>0.1058567831986978</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>8428.062914572654</v>
+        <v>10585.67831986978</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.1047501473143974</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>279.1158350710165</v>
+        <v>1108.851363429182</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>143.1900829499451</v>
+        <v>333.6345444889481</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>131.4463346282519</v>
+        <v>285.1645786331716</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6416393123868253</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.879046790671904</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1090,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1093,27 +1099,27 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.07913982403504768</v>
+        <v>0.06951830094919656</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>7913.982403504769</v>
+        <v>6951.830094919656</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.026062379703303</v>
+        <v>0.0319463736658787</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>206.2572143653998</v>
+        <v>222.0857618740043</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>41.55552637798377</v>
+        <v>137.7648408843948</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>38.03716888153436</v>
+        <v>126.5130091330145</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.4285825244247249</v>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
+        <v>0.6103973750054179</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1125,7 +1131,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1134,62 +1140,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07689156450410166</v>
+        <v>0.05901418175367707</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7689.156450410166</v>
+        <v>5901.418175367707</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0204183581564147</v>
+        <v>0.0176861201711677</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>156.9999503251811</v>
+        <v>104.3731910298665</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>197.6550328608278</v>
+        <v>40.80921186599804</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>184.0149971008301</v>
+        <v>36.51765369294939</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4083671631282952</v>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
+        <v>0.1979746325938461</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1207,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1230,7 +1236,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1251,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1293,7 +1299,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1431,577 +1437,691 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.0618301731244848</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.1259383002873109</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.2830390713974848</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>424.2011541632316</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>449.8123509647807</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>512.5741090232953</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>373.1666787300279</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>334</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0457252883240006</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.211966460056985</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.3728564655733453</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>349.2722463002162</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>404.796797659033</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>458.5340595014973</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>317.3</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>302</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.0194805194805194</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.1047501473143974</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.1307691594971161</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>296.1168831168831</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>333.6345444889481</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>341.4922861681291</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>285.1645786331716</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>384.75</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.065000031562885</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>-0.0395584808260567</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0.1232090104953282</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>359.74123785618</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>369.5298745021747</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>432.1546667880776</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>359.1972700535711</v>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="D11" s="18" t="n">
+        <v>357</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.0174048288175393</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>-0.0036970289786339</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.1185391429973565</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>350.7864761121385</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>355.6801606546277</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>399.3184740500563</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>339.15</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M8" s="15" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="M11" s="17" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="15" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.1195457879117688</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-0.0525384894872815</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.05159344410234</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>64.93349814150704</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>69.87528640031299</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>77.55501650254757</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>64.93349814150704</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
         <is>
           <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>38.02000045776367</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0528151211788878</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0.004366982061861</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.1062296048253292</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>36.01196952636552</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>38.18603311775468</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>42.05885008185074</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>35.62858599261265</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>-0.0557185041218549</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0.2096024767266591</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.2789832810411945</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>314.6818085013919</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>403.1000253691591</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>426.2211784069781</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>314.6818085013919</v>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M9" s="18" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="D14" s="15" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.0374467634999697</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.0319463736658787</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>0.10818310737263</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>128.5008570727541</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>137.7648408843948</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>147.9424448342461</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>126.5130091330145</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>189.6000061035156</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0452929246956146</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-0.0056061959533879</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1633018392220255</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>181.012467304781</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>188.5370713165358</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>220.562035816727</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>180.1200057983398</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>40.09999847412109</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.08933528472534991</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.0176861201711677</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>0.0827585226318214</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>36.51765369294939</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>40.80921186599804</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>43.41861510537765</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>36.51765369294939</v>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>-0.0056818181818182</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.1082854760144804</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.1307693897609034</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>304.5099431818182</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>339.4124270294346</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>346.2981256142767</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>289.192557303994</v>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N10" s="18" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>107.1999969482422</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>-0.036339177299891</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>0.0165181297928999</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>0.0625387106897197</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>103.3044372525922</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>108.9707404116317</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>113.9041465433271</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>101.8399971008301</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="18" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
-        <v>357.5</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>-0.0314232688469682</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>-0.0037105176120389</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>0.1453543644432943</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>346.2661813872089</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>356.1734899536961</v>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>409.4641852884778</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>339.625</v>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
+      <c r="D18" s="24" t="n">
+        <v>248.1999969482422</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.0501087082729111</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0049330944485646</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0825054415792305</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>235.7630157078253</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>246.9756029211631</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>268.6778472964206</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>235.7630157078253</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="15" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N11" s="15" t="inlineStr">
+      <c r="M18" s="23" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>-0.1036949211912278</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.0265262577132464</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0.0283369659971981</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>84.70082994742897</v>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>91.99326864609822</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>97.17784328673523</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>84.70082994742897</v>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M19" s="23" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="N19" s="23" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="15" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>77.94999694824219</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0860928157553027</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>-0.0301236938145638</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>0.1166665836624449</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>71.23906222285076</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>75.60185510732715</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>87.04415678869161</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>71.23906222285076</v>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N12" s="15" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="15" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>138.6000061035156</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>-0.008288998220071</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.152022502552924</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>137.4511508996218</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>143.1900829499451</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>159.6703258852226</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>131.4463346282519</v>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="18" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>-0.0277778108086147</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>0.026062379703303</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0.1235848352080751</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>39.3749986622511</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>41.55552637798377</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>45.50518582592704</v>
-      </c>
-      <c r="K14" s="19" t="n">
-        <v>38.03716888153436</v>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="18" t="inlineStr">
-        <is>
-          <t>volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>193.6999969482422</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>-0.0097348326847777</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>0.0204183581564147</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>0.0729759755823018</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>191.8143598869091</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>197.6550328608278</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>207.835443195829</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>184.0149971008301</v>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="18" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N15" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>108.4000015258789</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.0448027560808507</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>-0.0050943225797922</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>0.0555149911412387</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>103.5433826983511</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>107.8477769504561</v>
-      </c>
-      <c r="J16" s="16" t="n">
-        <v>114.4178266502983</v>
-      </c>
-      <c r="K16" s="16" t="n">
-        <v>102.980001449585</v>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N16" s="15" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="15" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>40.79999923706055</v>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>-0.08933527791281801</v>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>0.0176860473833884</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>0.0831932668372119</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>37.15511996637498</v>
-      </c>
-      <c r="I17" s="22" t="n">
-        <v>41.52158995680941</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>44.19428446054737</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>37.15511996637498</v>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="21" t="inlineStr">
+      <c r="O19" s="23" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2031,7 +2151,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2048,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2120,734 +2240,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.1028295376121464</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.1872213967310549</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.7354474600180945</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>0.1479301578856047</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.0329578488985884</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.1259383002873109</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.1142618849040868</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.1142618849040868</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.2178669097538741</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.0518244165888697</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>0.0224280868678006</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0.211966460056985</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.015126050420168</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.1205936920222634</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.2475735288045928</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.1072235894432254</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.0278732141834907</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.1047501473143974</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
-        <v>0.0032594524119948</v>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>0.2014051522248243</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>0.6605524603694604</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.1642761747828451</v>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="E7" s="19" t="n">
+        <v>-0.0379105092590879</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.038666804466857</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.2514712161136745</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.146071376548857</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
-        <v>0.0332069265060805</v>
-      </c>
-      <c r="K4" s="17" t="n">
-        <v>-0.0395584808260567</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="J7" s="19" t="n">
+        <v>0.0199673156767437</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>-0.0036970289786339</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>0.0982873912754496</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.06498194945848371</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.0355607634123917</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.0031833671194287</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.0317317702632586</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>-0.0525384894872815</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>0.08011362595745369</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>0.0982091747769389</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>-0.0026232549035423</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.0046509123633177</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0.0314494270957156</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>0.004366982061861</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
-        <v>0.1220538720538719</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>0.1182885906040267</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>0.2411545623836126</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>0.0522229076658125</v>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="E10" s="16" t="n">
+        <v>0.0308880308880308</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.057843565416608</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>-0.07217851387470781</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.0324754297631857</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0.026168505119796</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>0.0319463736658787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.0083681530871555</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>-0.0181253230935878</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.1252238109088959</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.0419370262581584</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>0.0216342637490465</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>-0.0056061959533879</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.4413204787850318</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.6781684227851839</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>-0.2000140581789575</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
-        <v>0.0224334775809057</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>0.2096024767266591</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>0.024247491638796</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>0.1238532110091743</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>0.3253137272692095</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>0.0978604114157553</v>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="J12" s="16" t="n">
+        <v>0.0276553695056337</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>0.0176861201711677</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0064875307482625</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0.0028063182233972</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.1166666348775227</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>-0.0013946075335394</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>0.0234179516127443</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>0.0165181297928999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0689061163233626</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.0304687619209289</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.3817014734464747</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.1543428661897617</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
-        <v>0.0278488860342956</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>0.1082854760144804</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="J14" s="25" t="n">
+        <v>0.0227948736710902</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>-0.0049330944485646</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
-        <v>-0.0567927122885886</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>0.0401215198792757</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>0.2985077075395863</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>0.1429597223795853</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="E15" s="25" t="n">
+        <v>0.0271739130434782</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>0.0488346459533259</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.09235721479558261</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>-0.1459904557577096</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J7" s="17" t="n">
-        <v>0.0199656126278064</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>-0.0037105176120389</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="J15" s="25" t="n">
+        <v>0.0257945186668304</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>-0.0265262577132464</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.202004607283819</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0.1421244974101418</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0.1525546975089651</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>0.009977621456205</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>0.0309684020932089</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>-0.0301236938145638</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>-0.0250659498927598</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0.0052882985421611</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0.147580014167697</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-0.1342950651390403</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0.0262733290323232</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0121672257670984</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>0.1008737444298299</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0.1195727246378437</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.0048847588973104</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>0.037302304693062</v>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0258068945174537</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>0.0169393061154679</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.0268305643193377</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>-0.107179455879407</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.0827674871750347</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0218716122937669</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0270714525721503</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>0.1780104346058495</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.1821366603671084</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.1181667210118826</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>-0.0159662669399445</v>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>0.0304053224501931</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>0.026062379703303</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.0502369957512588</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.0956679224870062</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>-0.044804618772834</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.0867375485681951</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>0.0183815906397974</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.0759494774088542</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0.0270413079516411</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>-0.0107252608313827</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.1904170582967865</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0.0442814511889992</v>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>0.0215379322371052</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0.0204183581564147</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>-0.09942912022230491</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.0534999847412109</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>0.1417370562293971</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-0.1125146473289018</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="27" t="n">
+        <v>0.027371838733298</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.09098899757469089</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.0245746540560038</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>0.0111940728712529</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>0.1643394554513417</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>0.0116528588929327</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>0.0233762470758074</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>-0.0050943225797922</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>0.0124069481257009</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>0.4369268837550237</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>0.7361359388446289</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>-0.1809919303685616</v>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>0.0276987119262011</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0176860473833884</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>0.07552377435497119</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>0.07730535355143869</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.1764653814689465</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.119120152504353</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0254734136752352</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.061538384265372</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>0.0411764705882353</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0133778928547187</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>-0.0766823014202294</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>-0.0845110267848225</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0217761950942461</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0147321564810616</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>0.007986587658763001</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.0549753574314962</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0.3537619695978546</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.1513126326984402</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0223765626924933</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0416218430715982</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0392918762265791</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>0.0102725492697408</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>0.1745273510818865</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.1217720897143876</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0262685190895596</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.0191753146075474</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0562913634818335</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0948275611400447</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.0123762376237623</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.0735625397864777</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="E20" s="27" t="n">
+        <v>-0.0547403900411772</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>-0.1683217225612643</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>-0.09388789028605229</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-0.0589861050729501</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0183868314613509</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0566279411125097</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0590219244532953</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.1834146639195883</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.0655952982027229</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.0235374281295358</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.021795916664336</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.1002252939750626</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.1632653130302539</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.0727630054637942</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>0.162045664959572</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.1150046819072787</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0274420209648397</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.1000000839371915</v>
+      <c r="J20" s="27" t="n">
+        <v>0.0217198916869541</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.09098899757469089</v>
       </c>
     </row>
   </sheetData>
@@ -2872,7 +2992,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2880,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2905,7 +3025,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TOASO.IS, GARAN.IS, YKBNK.IS, KCHOL.IS</t>
+          <t>ASELS.IS, THYAO.IS, TOASO.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2917,7 +3037,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>YKBNK.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2929,7 +3049,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, BIMAS.IS, AKBNK.IS, TCELL.IS</t>
+          <t>BIMAS.IS, AKBNK.IS, KCHOL.IS, TUPRS.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2941,7 +3061,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, PGSUS.IS, TUPRS.IS, SISE.IS, ARCLK.IS, FROTO.IS, PETKM.IS</t>
+          <t>SISE.IS, PGSUS.IS, ARCLK.IS, PETKM.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3073,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.91 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.71 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2991,7 +3111,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2999,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3048,7 +3168,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3192,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3228,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3264,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3336,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3362,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3274,7 +3394,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14455</v>
+        <v>14417.900390625</v>
       </c>
     </row>
     <row r="5">
@@ -3284,7 +3404,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12619.5165234375</v>
+        <v>12639.74602539062</v>
       </c>
     </row>
     <row r="6">
@@ -3318,7 +3438,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>75.78</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="9">
@@ -3345,15 +3465,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3361,7 +3481,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-02</t>
+          <t>Rapor Tarihi: 2026-07-03</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3375,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-03 05:40</t>
+          <t>Son Güncelleme: 2026-07-04 05:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3439,29 +3559,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>177</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>0.05106892170555577</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>510.6892170555566</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>0.0548015178050205</v>
+      <c r="D4" s="28" t="n">
+        <v>174.1000061035156</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.033848054712728</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>338.4805471272794</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3469,29 +3589,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
-        <v>244.8999938964844</v>
-      </c>
-      <c r="D5" s="26" t="n">
-        <v>239.8000030517578</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-0.0208247895950634</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>-208.2478959506352</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>0.0548015178050205</v>
+      <c r="C5" s="28" t="n">
+        <v>123.0999984741211</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>0.08448417266280694</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>844.8417266280685</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3499,29 +3619,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
-        <v>123.0999984741211</v>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>138.6000061035156</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0.1259139546833792</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>1259.139546833792</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0.0548015178050205</v>
+      <c r="C6" s="28" t="n">
+        <v>85.19999694824219</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.01701874413355953</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-170.1874413355963</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3529,59 +3649,59 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>83.69999694824219</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>-0.01760563443342877</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>-176.0563443342871</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0.0548015178050205</v>
+      <c r="C7" s="28" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>44.34000015258789</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-0.02549450214092552</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-764.8350642277655</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D8" s="26" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>-0.02197802197802201</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>-659.3406593406617</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0.0548015178050205</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>38.02000045776367</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.1327554670293646</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-94416.71969714283</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3589,177 +3709,117 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
-        <v>43.84000015258789</v>
-      </c>
-      <c r="D9" s="26" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>-0.07618613460225387</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>-54184.17091597966</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0.0548015178050205</v>
+      <c r="C9" s="28" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>40.09999847412109</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>-0.005949471431804132</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>-4231.310311300098</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="D10" s="26" t="n">
-        <v>97.55000305175781</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>-0.03891622609105605</v>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>-27677.52238555369</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>0.0548015178050205</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>334</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>0.002250562640660148</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>74.00308946839505</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>40.79999923706055</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>0.0114030511336809</v>
-      </c>
-      <c r="F11" s="26" t="n">
-        <v>8109.938571063103</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>0.0548015178050205</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>302</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>-0.01387755102040822</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>-456.3221797124534</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="E12" s="27" t="n">
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="E12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>0.0548015178050205</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>7.275957614183426e-12</v>
-      </c>
-      <c r="G13" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>0.0548015178050205</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n">
-        <v>193.6999969482422</v>
-      </c>
-      <c r="D14" s="26" t="n">
-        <v>193.6999969482422</v>
-      </c>
-      <c r="E14" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>2229243.858205974</v>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>0.0548015178050205</v>
+      <c r="F12" s="28" t="n">
+        <v>-1.164153218269348e-10</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>2153877.312550157</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>0.0520943075470665</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H14"/>
+  <autoFilter ref="A3:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1023,19 +1023,19 @@
         <v>12757.11168923382</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.608962717493</v>
+        <v>1606.608962717495</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647807</v>
+        <v>449.8123509647808</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>373.1666787300279</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.910596481506183</v>
+        <v>1.910596481506187</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567831986978</v>
+        <v>0.1058567831986977</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67831986978</v>
+        <v>10585.67831986977</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.1047501473143974</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830094919656</v>
+        <v>0.06951830094919655</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830094919656</v>
+        <v>6951.830094919655</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0319463736658787</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901418175367707</v>
+        <v>0.05901418175367706</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>5901.418175367707</v>
@@ -1155,7 +1155,7 @@
         <v>40.80921186599804</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0.1979746325938461</v>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,19 +1457,19 @@
         <v>0.0618301731244848</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974848</v>
+        <v>0.2830390713974846</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>424.2011541632316</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647807</v>
+        <v>449.8123509647808</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232953</v>
+        <v>512.5741090232951</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>373.1666787300279</v>
@@ -1682,7 +1682,7 @@
         <v>73.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195457879117688</v>
+        <v>-0.1195457879117687</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.0525384894872815</v>
@@ -1691,7 +1691,7 @@
         <v>0.05159344410234</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>64.93349814150704</v>
+        <v>64.93349814150706</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>69.87528640031299</v>
@@ -1700,7 +1700,7 @@
         <v>77.55501650254757</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>64.93349814150704</v>
+        <v>64.93349814150706</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.004366982061861</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296048253292</v>
+        <v>0.1062296048253293</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>36.01196952636552</v>
@@ -1859,7 +1859,7 @@
         <v>-0.0056061959533879</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1633018392220255</v>
+        <v>0.1633018392220254</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>181.012467304781</v>
@@ -1868,7 +1868,7 @@
         <v>188.5370713165358</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>220.562035816727</v>
+        <v>220.5620358167269</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>180.1200057983398</v>
@@ -1919,7 +1919,7 @@
         <v>0.0827585226318214</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="I16" s="15" t="n">
         <v>40.80921186599804</v>
@@ -1928,7 +1928,7 @@
         <v>43.41861510537765</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1976,13 +1976,13 @@
         <v>0.0625387106897197</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>103.3044372525922</v>
+        <v>103.3044372525923</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>108.9707404116317</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>113.9041465433271</v>
+        <v>113.9041465433272</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>101.8399971008301</v>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2279,7 +2279,7 @@
         <v>0.0329578488985884</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
     </row>
     <row r="5">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0224280868678006</v>
+        <v>0.0224280868678007</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.211966460056985</v>
@@ -2520,7 +2520,7 @@
         <v>0.0308880308880308</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.057843565416608</v>
+        <v>0.0578435654166078</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>-0.07217851387470781</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0083681530871555</v>
+        <v>-0.0083681530871556</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0181253230935878</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4413204787850318</v>
+        <v>0.4413204787850315</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.6781684227851839</v>
+        <v>0.6781684227851834</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>-0.2000140581789575</v>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0064875307482625</v>
+        <v>-0.0064875307482624</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0028063182233972</v>
+        <v>0.0028063182233974</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1166666348775227</v>
+        <v>0.1166666348775229</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>-0.0013946075335394</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0262733290323232</v>
+        <v>0.0262733290323233</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0121672257670984</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0218716122937669</v>
+        <v>0.0218716122937668</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>0.0270714525721503</v>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0502369957512588</v>
+        <v>-0.0502369957512587</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.0956679224870062</v>
+        <v>-0.09566792248700599</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.044804618772834</v>
+        <v>-0.0448046187728339</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>-0.0867375485681951</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.027371838733298</v>
+        <v>0.0273718387332981</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -2950,7 +2950,7 @@
         <v>-0.0547403900411772</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.1683217225612643</v>
+        <v>-0.1683217225612644</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>-0.09388789028605229</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0217198916869541</v>
+        <v>0.021719891686954</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3716,13 +3716,13 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.005949471431804132</v>
+        <v>-0.005949471431804354</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4231.310311300098</v>
+        <v>-4231.310311300214</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3722,7 +3722,7 @@
         <v>-4231.310311300214</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -974,25 +974,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1380396172060904</v>
+        <v>0.1380396116533548</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13803.96172060904</v>
+        <v>13803.96116533548</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2925.976900679626</v>
+        <v>2925.97545737571</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.796797659033</v>
+        <v>404.7967655847673</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>317.3</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.239329201139705</v>
+        <v>4.239327280524994</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1275711168923382</v>
+        <v>0.1275711214916294</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>12757.11168923382</v>
+        <v>12757.11214916294</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.608962717495</v>
+        <v>1606.609020640185</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647808</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>373.1666787300279</v>
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567831986977</v>
+        <v>0.1058567503448248</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67831986977</v>
+        <v>10585.67503448248</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1108.851363429182</v>
+        <v>1108.84956541144</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>333.6345444889481</v>
+        <v>333.6345030112316</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>285.1645786331716</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.879046790671904</v>
+        <v>1.879044326954746</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830094919655</v>
+        <v>0.06951830345552337</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830094919655</v>
+        <v>6951.830345552337</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0319463736658787</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>222.0857618740043</v>
+        <v>222.0857698808096</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>137.7648408843948</v>
@@ -1117,7 +1117,7 @@
         <v>126.5130091330145</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.6103973750054179</v>
+        <v>0.6103973750054204</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901418175367706</v>
+        <v>0.05901421305466755</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5901.418175367707</v>
+        <v>5901.421305466755</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>104.3731910298665</v>
+        <v>104.3741130890362</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>40.80921186599804</v>
+        <v>40.80921775520021</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1979746325938461</v>
+        <v>0.1979761226473516</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,19 +1457,19 @@
         <v>0.0618301731244848</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974846</v>
+        <v>0.2830390713974848</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>424.2011541632316</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647808</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232951</v>
+        <v>512.5741090232953</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>373.1666787300279</v>
@@ -1511,22 +1511,22 @@
         <v>334</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0457252883240006</v>
+        <v>0.0457252439987692</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.3728564655733453</v>
+        <v>0.3728564122007715</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>349.2722463002162</v>
+        <v>349.2722314955889</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>404.796797659033</v>
+        <v>404.7967655847673</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>458.5340595014973</v>
+        <v>458.5340416750577</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>317.3</v>
@@ -1571,19 +1571,19 @@
         <v>-0.0194805194805194</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1307691594971161</v>
+        <v>0.1307690576798095</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>296.1168831168831</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>333.6345444889481</v>
+        <v>333.6345030112316</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>341.4922861681291</v>
+        <v>341.4922554193025</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>285.1645786331716</v>
@@ -1628,19 +1628,19 @@
         <v>-0.0174048288175393</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.0036970289786339</v>
+        <v>-0.0036968005684216</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1185391429973565</v>
+        <v>0.1185386588107133</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>350.7864761121385</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>355.6801606546277</v>
+        <v>355.6802421970735</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>399.3184740500563</v>
+        <v>399.3183011954247</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>339.15</v>
@@ -1682,25 +1682,25 @@
         <v>73.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195457879117687</v>
+        <v>-0.1195457879117688</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.0525384894872815</v>
+        <v>-0.0525383720373842</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0515933378844173</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>64.93349814150706</v>
+        <v>64.93349814150704</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>69.87528640031299</v>
+        <v>69.87529506224291</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>77.55501650254757</v>
+        <v>77.55500866897577</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>64.93349814150706</v>
+        <v>64.93349814150704</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.004366982061861</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296048253293</v>
+        <v>0.1062296237000928</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>36.01196952636552</v>
@@ -1754,7 +1754,7 @@
         <v>38.18603311775468</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>42.05885008185074</v>
+        <v>42.05885079946926</v>
       </c>
       <c r="K13" s="21" t="n">
         <v>35.62858599261265</v>
@@ -1796,22 +1796,22 @@
         <v>133.5</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0374467634999697</v>
+        <v>-0.0374466031122178</v>
       </c>
       <c r="F14" s="16" t="n">
         <v>0.0319463736658787</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.10818310737263</v>
+        <v>0.1081830165120092</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>128.5008570727541</v>
+        <v>128.5008784845189</v>
       </c>
       <c r="I14" s="15" t="n">
         <v>137.7648408843948</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>147.9424448342461</v>
+        <v>147.9424327043532</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>126.5130091330145</v>
@@ -1853,22 +1853,22 @@
         <v>189.6000061035156</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>-0.0452929246956146</v>
+        <v>-0.0452929265798762</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>-0.0056061959533879</v>
+        <v>-0.005606274347556</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1633018392220254</v>
+        <v>0.1633017563777966</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>181.012467304781</v>
+        <v>181.012466947525</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>188.5370713165358</v>
+        <v>188.537056453001</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>220.5620358167269</v>
+        <v>220.5620201094607</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>180.1200057983398</v>
@@ -1910,25 +1910,25 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.08933528472534991</v>
+        <v>-0.089335354170837</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.0827585226318214</v>
+        <v>0.0827586281845227</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>40.80921186599804</v>
+        <v>40.80921775520021</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>43.41861510537765</v>
+        <v>43.41861933804081</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1970,19 +1970,19 @@
         <v>-0.036339177299891</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0165181297928999</v>
+        <v>0.0165180940172871</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>0.0625387106897197</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>103.3044372525923</v>
+        <v>103.3044372525922</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>108.9707404116317</v>
+        <v>108.9707365764861</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>113.9041465433272</v>
+        <v>113.9041465433271</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>101.8399971008301</v>
@@ -2024,25 +2024,25 @@
         <v>248.1999969482422</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0501087082729111</v>
+        <v>-0.0501087049018857</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.0049330944485646</v>
+        <v>-0.004933032871861</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0825054415792305</v>
+        <v>0.082505387163645</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>235.7630157078253</v>
+        <v>235.7630165445138</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>246.9756029211631</v>
+        <v>246.9756182045007</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>268.6778472964206</v>
+        <v>268.6778337904724</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>235.7630157078253</v>
+        <v>235.7630165445138</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
         <v>94.5</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.1036949211912278</v>
+        <v>-0.1036948476951217</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0265262577132464</v>
+        <v>-0.0265261865666126</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0283369659971981</v>
+        <v>0.0283370297099155</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>84.70082994742897</v>
+        <v>84.700836892811</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>91.99326864609822</v>
+        <v>91.99327536945511</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>97.17784328673523</v>
+        <v>97.17784930758701</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>84.70082994742897</v>
+        <v>84.700836892811</v>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0329578488985884</v>
+        <v>0.0329578488985883</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
     </row>
     <row r="5">
@@ -2322,7 +2322,7 @@
         <v>0.0224280868678007</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
     </row>
     <row r="6">
@@ -2365,7 +2365,7 @@
         <v>0.0278732141834907</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
     </row>
     <row r="7">
@@ -2408,7 +2408,7 @@
         <v>0.0199673156767437</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.0036970289786339</v>
+        <v>-0.0036968005684216</v>
       </c>
     </row>
     <row r="8">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.0317317702632586</v>
+        <v>0.0317317702632585</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>-0.0525384894872815</v>
+        <v>-0.0525383720373842</v>
       </c>
     </row>
     <row r="9">
@@ -2520,7 +2520,7 @@
         <v>0.0308880308880308</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0578435654166078</v>
+        <v>0.057843565416608</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>-0.07217851387470781</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.026168505119796</v>
+        <v>0.0261685051197959</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0319463736658787</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0083681530871556</v>
+        <v>-0.0083681530871555</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0181253230935878</v>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.0216342637490465</v>
+        <v>0.0216342637490466</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>-0.0056061959533879</v>
+        <v>-0.005606274347556</v>
       </c>
     </row>
     <row r="12">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4413204787850315</v>
+        <v>0.4413204787850318</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.6781684227851834</v>
+        <v>0.6781684227851839</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>-0.2000140581789575</v>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.0276553695056337</v>
+        <v>0.0276553695056338</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
     </row>
     <row r="13">
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0064875307482624</v>
+        <v>-0.0064875307482625</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0028063182233974</v>
+        <v>0.0028063182233972</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1166666348775229</v>
+        <v>0.1166666348775227</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>-0.0013946075335394</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="J13" s="22" t="n">
-        <v>0.0234179516127443</v>
+        <v>0.0234179516127442</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0165181297928999</v>
+        <v>0.0165180940172871</v>
       </c>
     </row>
     <row r="14">
@@ -2709,7 +2709,7 @@
         <v>0.0227948736710902</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>-0.0049330944485646</v>
+        <v>-0.004933032871861</v>
       </c>
     </row>
     <row r="15">
@@ -2752,7 +2752,7 @@
         <v>0.0257945186668304</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>-0.0265262577132464</v>
+        <v>-0.0265261865666126</v>
       </c>
     </row>
     <row r="16">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0262733290323233</v>
+        <v>0.0262733290323232</v>
       </c>
       <c r="K16" s="27" t="n">
-        <v>0.0121672257670984</v>
+        <v>0.0121672262735507</v>
       </c>
     </row>
     <row r="17">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0218716122937668</v>
+        <v>0.0218716122937669</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>0.0270714525721503</v>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0502369957512587</v>
+        <v>-0.0502369957512588</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.09566792248700599</v>
+        <v>-0.0956679224870062</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.0448046187728339</v>
+        <v>-0.044804618772834</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>-0.0867375485681951</v>
@@ -2881,7 +2881,7 @@
         <v>0.0183815906397974</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0759494774088542</v>
+        <v>0.0759492964836558</v>
       </c>
     </row>
     <row r="19">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0273718387332981</v>
+        <v>0.027371838733298</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -2950,7 +2950,7 @@
         <v>-0.0547403900411772</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.1683217225612644</v>
+        <v>-0.1683217225612643</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>-0.09388789028605229</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.021719891686954</v>
+        <v>0.0217198916869541</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14417.900390625</v>
+        <v>14424.5</v>
       </c>
     </row>
     <row r="5">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12639.74602539062</v>
+        <v>12656.86702636719</v>
       </c>
     </row>
     <row r="6">
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3716,13 +3716,13 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.005949471431804354</v>
+        <v>-0.005949471431804132</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4231.310311300214</v>
+        <v>-4231.310311300098</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -86,22 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -162,10 +157,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,15 +197,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -643,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -694,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 69.53/100</t>
+          <t>Güven Puanı: 70.01/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -754,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: THYAO.IS, ASELS.IS, TOASO.IS, GARAN.IS, EREGL.IS</t>
+          <t>AL: THYAO.IS, ASELS.IS, BIMAS.IS, EREGL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -771,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: YKBNK.IS, TCELL.IS</t>
+          <t>AZALT: TOASO.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -788,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: BIMAS.IS, AKBNK.IS, KCHOL.IS, TUPRS.IS, SAHOL.IS</t>
+          <t>ÇIK: YKBNK.IS, AKBNK.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -974,29 +960,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1380396116533548</v>
+        <v>0.1242468596386035</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13803.96116533548</v>
+        <v>12424.68596386035</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.2119663640262494</v>
+        <v>0.0769231154335685</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2925.97545737571</v>
+        <v>955.7455526238678</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.7967655847673</v>
+        <v>373.6923210554483</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>317.3</v>
+        <v>329.65</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.239327280524994</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
+        <v>1.53846230867137</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1017,29 +1003,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1275711214916294</v>
+        <v>0.1194002080246505</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>12757.11214916294</v>
+        <v>11940.02080246505</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.0618301731244848</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.609020640185</v>
+        <v>738.2535533263639</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647807</v>
+        <v>426.5902720527617</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>373.1666787300279</v>
+        <v>370.7584981174186</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.910596481506187</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
+        <v>0.8015188210908575</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1035,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1058,29 +1044,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567503448248</v>
+        <v>0.1016778383026421</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67503448248</v>
+        <v>10167.78383026421</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1047500099709655</v>
+        <v>0.0485934285285993</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1108.84956541144</v>
+        <v>494.0874768501916</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>333.6345030112316</v>
+        <v>389.0281619841104</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>285.1645786331716</v>
+        <v>352.45</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.879044326954746</v>
+        <v>0.9718685705719885</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1099,29 +1085,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830345552337</v>
+        <v>0.0787158522321887</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830345552337</v>
+        <v>7871.58522321887</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0319463736658787</v>
+        <v>0.0417777788571567</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>222.0857698808096</v>
+        <v>328.8573467109004</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>137.7648408843948</v>
+        <v>43.25461385503717</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>126.5130091330145</v>
+        <v>39.13987304298741</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.6103973750054204</v>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.7287901422859572</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1140,25 +1126,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901421305466755</v>
+        <v>0.07595924180191518</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5901.421305466755</v>
+        <v>7595.924180191519</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0176862670340702</v>
+        <v>0.0265060621964958</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>104.3741130890362</v>
+        <v>201.3380387600228</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>40.80921775520021</v>
+        <v>137.2438573830236</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765090818546</v>
+        <v>126.7051807848712</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1979761226473516</v>
+        <v>0.5066409683987393</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1213,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1236,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1257,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1299,7 +1285,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1451,36 +1437,36 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>399.5</v>
+        <v>401.75</v>
       </c>
       <c r="E8" s="16" t="n">
+        <v>-0.0771412616865747</v>
+      </c>
+      <c r="F8" s="16" t="n">
         <v>0.0618301731244848</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.1259383002873109</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.2830390713974848</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>424.2011541632316</v>
+        <v>370.7584981174186</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647807</v>
+        <v>426.5902720527617</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232953</v>
+        <v>515.4609469339396</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>373.1666787300279</v>
+        <v>370.7584981174186</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>69.53</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1489,7 +1475,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>volatilite yüksek</t>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1508,36 +1494,36 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0457252439987692</v>
+        <v>-0.0478683703056284</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.2119663640262494</v>
+        <v>0.0769231154335685</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.3728564122007715</v>
+        <v>0.3470096126189304</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>349.2722314955889</v>
+        <v>330.3896755039469</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>404.7967655847673</v>
+        <v>373.6923210554483</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>458.5340416750577</v>
+        <v>467.4123355787688</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>317.3</v>
+        <v>329.65</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="M9" s="14" t="n">
-        <v>69.53</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
@@ -1556,7 +1542,7 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1565,36 +1551,36 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-0.0194805194805194</v>
+        <v>-0.0037105180381591</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.1047500099709655</v>
+        <v>0.0485934285285993</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1307690576798095</v>
+        <v>0.1185390749796542</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>296.1168831168831</v>
+        <v>369.6233978078429</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>333.6345030112316</v>
+        <v>389.0281619841104</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>341.4922554193025</v>
+        <v>414.9779968174517</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>285.1645786331716</v>
+        <v>352.45</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>69.53</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
@@ -1603,7 +1589,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1613,109 +1599,109 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.0984893878053735</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.008160641694665301</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.108285628230232</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>271.8054495766799</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>303.9604334709416</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>334.1481169114149</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>271.8054495766799</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>357</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.0174048288175393</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>-0.0036968005684216</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.1185386588107133</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>350.7864761121385</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>355.6802421970735</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>399.3183011954247</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>339.15</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="D12" s="21" t="n">
+        <v>37.45999908447266</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.0597383648825704</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>-0.0089743807627755</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.1046024808035823</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>35.22219999066368</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>37.12381878931538</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>41.37840791960842</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>35.09963061790675</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.1195457879117688</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>-0.0525383720373842</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.0515933378844173</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>64.93349814150704</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>69.87529506224291</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>77.55500866897577</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>64.93349814150704</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="M12" s="20" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
@@ -1727,37 +1713,37 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>38.02000045776367</v>
+        <v>73.5</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0528151211788878</v>
+        <v>-0.0950764079143317</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.004366982061861</v>
+        <v>-0.0301236938145638</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296237000928</v>
+        <v>0.05159344410234</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>36.01196952636552</v>
+        <v>66.51188401829663</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>38.18603311775468</v>
+        <v>71.28590850462956</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>42.05885079946926</v>
+        <v>77.292118141522</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>35.62858599261265</v>
+        <v>66.51188401829663</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1765,11 +1751,11 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>69.53</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -1793,28 +1779,28 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>133.5</v>
+        <v>133.6999969482422</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0374466031122178</v>
+        <v>-0.0371959299442395</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.0319463736658787</v>
+        <v>0.0265060621964958</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1081830165120092</v>
+        <v>0.106493257751661</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>128.5008784845189</v>
+        <v>128.7269012282104</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>137.7648408843948</v>
+        <v>137.2438573830236</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>147.9424327043532</v>
+        <v>147.9381451846477</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>126.5130091330145</v>
+        <v>126.7051807848712</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1822,7 +1808,7 @@
         </is>
       </c>
       <c r="M14" s="14" t="n">
-        <v>69.53</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
@@ -1836,292 +1822,178 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>41.52000045776367</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0573248407643312</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.0831932668372119</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>39.13987304298741</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>43.25461385503717</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>44.97418493492756</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>39.13987304298741</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>108.5999984741211</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>-0.0476952027399054</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.0232805184548855</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>0.0289375192237391</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>103.4202995293445</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>106.0717342054438</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>111.742613017664</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>103.169998550415</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>189.6000061035156</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0452929265798762</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>-0.005606274347556</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1633017563777966</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>181.012466947525</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>188.537056453001</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>220.5620201094607</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>180.1200057983398</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>188</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0567376780722056</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.0086283261623434</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.1410512655708424</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>177.3333165224253</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>189.6221253185206</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>214.5176379273184</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>177.3333165224253</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M15" s="17" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="M17" s="17" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>40.09999847412109</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>-0.089335354170837</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>0.0176862670340702</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>0.0827586281845227</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>36.51765090818546</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>40.80921775520021</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>43.41861933804081</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>36.51765090818546</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>107.1999969482422</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-0.036339177299891</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>0.0165180940172871</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>0.0625387106897197</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>103.3044372525922</v>
-      </c>
-      <c r="I17" s="21" t="n">
-        <v>108.9707365764861</v>
-      </c>
-      <c r="J17" s="21" t="n">
-        <v>113.9041465433271</v>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>101.8399971008301</v>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>248.1999969482422</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0501087049018857</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.004933032871861</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.082505387163645</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>235.7630165445138</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>246.9756182045007</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>268.6778337904724</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>235.7630165445138</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.1036948476951217</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.0265261865666126</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0.0283370297099155</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>84.700836892811</v>
-      </c>
-      <c r="I19" s="24" t="n">
-        <v>91.99327536945511</v>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>97.17784930758701</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>84.700836892811</v>
-      </c>
-      <c r="L19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="23" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="N19" s="23" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O19" s="23" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O19"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2151,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2168,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2250,7 +2122,7 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
@@ -2259,16 +2131,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.1028295376121464</v>
+        <v>0.1067493112947659</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.1872213967310549</v>
+        <v>0.2155824508320727</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.7354474600180945</v>
+        <v>0.6739583333333334</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.1479301578856047</v>
+        <v>0.1733392396294026</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2276,10 +2148,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0329578488985883</v>
+        <v>0.0328480978204836</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.0618301731244848</v>
       </c>
     </row>
     <row r="5">
@@ -2293,7 +2165,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -2302,16 +2174,16 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.1142618849040868</v>
+        <v>0.1683501683501682</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.1142618849040868</v>
+        <v>0.1722972972972973</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.2178669097538741</v>
+        <v>0.2493249324932493</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>0.0518244165888697</v>
+        <v>0.09241424947943019</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -2319,10 +2191,10 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0224280868678007</v>
+        <v>0.0228253194034348</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.2119663640262494</v>
+        <v>0.0769231154335685</v>
       </c>
     </row>
     <row r="6">
@@ -2331,7 +2203,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -2345,16 +2217,16 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.015126050420168</v>
+        <v>-0.011445169685299</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.1205936920222634</v>
+        <v>0.08805921110630691</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.2475735288045928</v>
+        <v>0.27063811454039</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>0.1072235894432254</v>
+        <v>0.1638890498086234</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
@@ -2362,10 +2234,10 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0278732141834907</v>
+        <v>0.0205108171107322</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.1047500099709655</v>
+        <v>0.0485934285285993</v>
       </c>
     </row>
     <row r="7">
@@ -2374,7 +2246,7 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2384,74 +2256,74 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0.0255102040816326</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.140964995269631</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.1936118332407577</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.122078307634617</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.0277398977566513</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.008160641694665301</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.0379105092590879</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.038666804466857</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.2514712161136745</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.146071376548857</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0199673156767437</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>-0.0036968005684216</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.0982873912754496</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.06498194945848371</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.0355607634123917</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.0031833671194287</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="E8" s="22" t="n">
+        <v>0.1148809757632745</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0.0883207750507701</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>-0.0203975564790146</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>-0.0042298975348272</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J8" s="19" t="n">
-        <v>0.0317317702632585</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>-0.0525383720373842</v>
+      <c r="J8" s="22" t="n">
+        <v>0.0315051858549603</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>-0.0089743807627755</v>
       </c>
     </row>
     <row r="9">
@@ -2460,7 +2332,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2470,20 +2342,20 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>0.08011362595745369</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>0.0982091747769389</v>
+        <v>0.06909090909090899</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>-0.0026232549035423</v>
+        <v>0.0362801622500823</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>-0.0046509123633177</v>
+        <v>-0.0183698889398818</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
@@ -2491,10 +2363,10 @@
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.0314494270957156</v>
+        <v>0.0317184743548069</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0.004366982061861</v>
+        <v>-0.0301236938145638</v>
       </c>
     </row>
     <row r="10">
@@ -2517,16 +2389,16 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.0308880308880308</v>
+        <v>0.0695999755859375</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.057843565416608</v>
+        <v>0.0522159349026454</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>-0.07217851387470781</v>
+        <v>-0.0620165519633377</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>0.0324754297631857</v>
+        <v>0.0218837942188241</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -2534,139 +2406,139 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0261685051197959</v>
+        <v>0.0261586249926347</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>0.0319463736658787</v>
+        <v>0.0265060621964958</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0602655929404332</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.4412516072896149</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.7163355302217362</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>-0.1939045391077194</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0.0276545256391398</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>0.0333016179906207</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0102325439453125</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.1219007753135499</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>0.0002736480868266</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>0.0234638800871573</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>-0.0232805184548855</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.0083681530871555</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>-0.0181253230935878</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.1252238109088959</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.0419370262581584</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.0052910052910053</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.0172504077319066</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.0847012600238372</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0.06328416996789429</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J11" s="19" t="n">
-        <v>0.0216342637490466</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>-0.005606274347556</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.4413204787850318</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.6781684227851839</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>-0.2000140581789575</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>0.0276553695056338</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>0.0176862670340702</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0064875307482625</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>0.0028063182233972</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.1166666348775227</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>-0.0013946075335394</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>0.0234179516127442</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>0.0165180940172871</v>
+      <c r="J13" s="19" t="n">
+        <v>0.0216284538786151</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>0.0086283261623434</v>
       </c>
     </row>
     <row r="14">
@@ -2685,31 +2557,31 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>0.0689061163233626</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.0304687619209289</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.3817014734464747</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.1543428661897617</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0.027408599506155</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>-0.0307541864976126</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.3351236975145872</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>-0.1533211302579805</v>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0227948736710902</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>-0.004933032871861</v>
+      <c r="J14" s="24" t="n">
+        <v>0.0227954635167686</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.0324555250908626</v>
       </c>
     </row>
     <row r="15">
@@ -2728,246 +2600,246 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>0.0271739130434782</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>0.0488346459533259</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.09235721479558261</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>-0.1459904557577096</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>0.03999998304579</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>0.0516853761137201</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0.0491312154261469</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.1368626562825304</v>
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0257945186668304</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>-0.0265261865666126</v>
+      <c r="J15" s="24" t="n">
+        <v>0.0257744191435242</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0027831487746044</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>0.0367734088006828</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>-0.0101925424096686</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>-0.1198388837881133</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.0634197646078955</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>0.0218173629922759</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.0118473493714823</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
-        <v>-0.0250659498927598</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>0.0052882985421611</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0.147580014167697</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-0.1342950651390403</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="E17" s="24" t="n">
+        <v>-0.0294642794041</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>0.001024999231536</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>0.1156307329762629</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.1258789211011524</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
-        <v>0.0262733290323232</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.0121672262735507</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="J17" s="24" t="n">
+        <v>0.0263186581136348</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0191753146075474</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
-        <v>0.0169393061154679</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.0268305643193377</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.107179455879407</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.0827674871750347</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="E18" s="24" t="n">
+        <v>-0.09596928912458</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.0523138356178183</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.1274686525922364</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.1254307475911468</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0218716122937669</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>0.0270714525721503</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="J18" s="24" t="n">
+        <v>0.0273682527266637</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.0759492964836558</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
-        <v>-0.0502369957512588</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>-0.0956679224870062</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>-0.044804618772834</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-0.0867375485681951</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="E19" s="24" t="n">
+        <v>-0.0358180490641695</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.09124087718268729</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-0.0691588927652234</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.0852352006628922</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0183815906397974</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>0.0759492964836558</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="J19" s="24" t="n">
+        <v>0.0183517441559908</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.09498274421764449</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E19" s="27" t="n">
-        <v>-0.09942912022230491</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>-0.0534999847412109</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>0.1417370562293971</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-0.1125146473289018</v>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="E20" s="24" t="n">
+        <v>-0.0487238642335918</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.1767068146963282</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>-0.1183548623844481</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.0791441781158497</v>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="27" t="n">
-        <v>0.027371838733298</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>0.09098899757469089</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>-0.0547403900411772</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>-0.1683217225612643</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>-0.09388789028605229</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-0.0589861050729501</v>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>0.0217198916869541</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>0.09098899757469089</v>
+      <c r="J20" s="24" t="n">
+        <v>0.021816982577849</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0.0937362922905394</v>
       </c>
     </row>
   </sheetData>
@@ -2992,7 +2864,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3000,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3025,7 +2897,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, THYAO.IS, TOASO.IS, GARAN.IS, EREGL.IS</t>
+          <t>ASELS.IS, THYAO.IS, BIMAS.IS, GARAN.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -3037,7 +2909,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, TCELL.IS</t>
+          <t>TOASO.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -3049,7 +2921,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, AKBNK.IS, KCHOL.IS, TUPRS.IS, SAHOL.IS</t>
+          <t>YKBNK.IS, AKBNK.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -3061,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS, PGSUS.IS, ARCLK.IS, PETKM.IS, FROTO.IS</t>
+          <t>TUPRS.IS, SAHOL.IS, PGSUS.IS, SISE.IS, PETKM.IS, ARCLK.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -3073,7 +2945,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.71 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.76 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3111,7 +2983,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3119,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3180,7 +3052,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3136,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3184,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3234,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3370,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3394,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14424.5</v>
+        <v>14497.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3404,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12656.86702636719</v>
+        <v>12673.43902832031</v>
       </c>
     </row>
     <row r="6">
@@ -3438,7 +3310,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>69.53</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3472,8 +3344,8 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3481,7 +3353,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-03</t>
+          <t>Rapor Tarihi: 2026-07-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3495,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-07 05:56</t>
+          <t>Son Güncelleme: 2026-07-08 04:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3559,23 +3431,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>174.1000061035156</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.033848054712728</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>338.4805471272794</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="D4" s="25" t="n">
+        <v>174.8000030517578</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.03800480633750802</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>380.0480633750813</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="5">
@@ -3589,23 +3461,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0.08448417266280694</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>844.8417266280685</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="D5" s="25" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.08610884326167967</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>861.0884326167961</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="6">
@@ -3619,23 +3491,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>85.19999694824219</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>83.75</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.01701874413355953</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-170.1874413355963</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="D6" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.03755865097255984</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-375.5865097255974</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="7">
@@ -3649,29 +3521,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>45.5</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>44.34000015258789</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.02549450214092552</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-764.8350642277655</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="D7" s="25" t="n">
+        <v>43.47999954223633</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.04439561445634443</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-1331.868433690335</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3679,59 +3551,59 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
-        <v>43.84000015258789</v>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>38.02000045776367</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.1327554670293646</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-94416.71969714283</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="C8" s="25" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>41.52000045776367</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.02925137086545315</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>20803.80225056759</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>40.09999847412109</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>-0.005949471431804132</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-4231.310311300098</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>0.0520943075470665</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>347</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.04126031507876959</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>1356.723306920569</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3739,83 +3611,83 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>334</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>0.002250562640660148</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>74.00308946839505</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="C10" s="25" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.01551020408163262</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>-510.0071420315689</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>302</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>-0.01387755102040822</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>-456.3221797124534</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>0.0520943075470665</v>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.005632040050062681</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>3967.658124213223</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="E12" s="29" t="n">
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>371</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>371</v>
+      </c>
+      <c r="E12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="28" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>4267316.540047753</v>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>0.0520943075470665</v>
+      <c r="F12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>4287748.934738215</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>0.0525758902510216</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -181,15 +190,6 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -197,6 +197,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +689,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 70.01/100</t>
+          <t>Güven Puanı: 69.55/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +749,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: THYAO.IS, ASELS.IS, BIMAS.IS, EREGL.IS, GARAN.IS</t>
+          <t>AL: TOASO.IS, BIMAS.IS, EREGL.IS, YKBNK.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +766,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TOASO.IS, KCHOL.IS</t>
+          <t>AZALT: THYAO.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +783,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: YKBNK.IS, AKBNK.IS, TCELL.IS</t>
+          <t>ÇIK: AKBNK.IS, TCELL.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -951,7 +960,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -960,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1242468596386035</v>
+        <v>0.1220825652377705</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12424.68596386035</v>
+        <v>12208.25652377705</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0769231154335685</v>
+        <v>0.07579908675799089</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>955.7455526238678</v>
+        <v>925.3746954095852</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>373.6923210554483</v>
+        <v>321.6639269406393</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>329.65</v>
+        <v>282.3950382783036</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.53846230867137</v>
+        <v>1.364888839883686</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -994,7 +1003,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +1012,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1194002080246505</v>
+        <v>0.1156010339188141</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11940.02080246505</v>
+        <v>11560.10339188141</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0618301731244848</v>
+        <v>0.0485934335110049</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>738.2535533263639</v>
+        <v>561.7451155537316</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>426.5902720527617</v>
+        <v>392.4360924914936</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>370.7584981174186</v>
+        <v>355.5375</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.8015188210908575</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.9718686702200992</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1044,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,25 +1053,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1016778383026421</v>
+        <v>0.09098426890552622</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10167.78383026421</v>
+        <v>9098.426890552622</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485934285285993</v>
+        <v>0.0417778692166073</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>494.0874768501916</v>
+        <v>380.1128887103704</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>389.0281619841104</v>
+        <v>42.98375313528766</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>352.45</v>
+        <v>38.89477223461847</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718685705719885</v>
+        <v>0.7287907161564283</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,29 +1094,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.0787158522321887</v>
+        <v>0.08707323101637048</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>7871.58522321887</v>
+        <v>8707.323101637048</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0417777788571567</v>
+        <v>0.0177083448864976</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>328.8573467109004</v>
+        <v>154.1922805219568</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>43.25461385503717</v>
+        <v>38.26583221483261</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>39.13987304298741</v>
+        <v>35.23785181247381</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.7287901422859572</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.2818765453992548</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1135,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07595924180191518</v>
+        <v>0.08425890092151866</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7595.924180191519</v>
+        <v>8425.890092151867</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0265060621964958</v>
+        <v>0.0265059178623019</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>201.3380387600228</v>
+        <v>223.3359506993608</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>137.2438573830236</v>
+        <v>137.9623890953985</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>126.7051807848712</v>
+        <v>127.4179475839125</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5066409683987393</v>
+        <v>0.5102222241779831</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1199,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1222,7 +1231,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1285,7 +1294,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1428,45 +1437,45 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>401.75</v>
+        <v>348.25</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0771412616865747</v>
+        <v>-0.0628859824625369</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0618301731244848</v>
+        <v>0.014527377775034</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974848</v>
+        <v>0.1444448294649761</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>370.7584981174186</v>
+        <v>326.3499566074215</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>426.5902720527617</v>
+        <v>353.3091593101556</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>515.4609469339396</v>
+        <v>398.5529118611779</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>370.7584981174186</v>
+        <v>326.3499566074215</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>70.01000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1475,7 +1484,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1485,109 +1494,109 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>383</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.0563155286172766</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.0062282699504712</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.1235737562936812</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>361.4311525395831</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>385.3854273910305</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>430.3287486604799</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>357.4274084909891</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>347</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0478683703056284</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.0769231154335685</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.3470096126189304</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>330.3896755039469</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>373.6923210554483</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>467.4123355787688</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>329.65</v>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="D10" s="18" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0037105176120389</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0485934335110049</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.1185389470069964</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>372.8613387836945</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>392.4360924914936</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>418.6132009173684</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>355.5375</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>371</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.0037105180381591</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0485934285285993</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.1185390749796542</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>369.6233978078429</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>389.0281619841104</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>414.9779968174517</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>352.45</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
@@ -1604,106 +1613,106 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>301.5</v>
+        <v>299</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0984893878053735</v>
+        <v>-0.0392112770744697</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.008160641694665301</v>
+        <v>0.07579908675799089</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.108285628230232</v>
+        <v>0.1261890277639881</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>271.8054495766799</v>
+        <v>287.2758281547336</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>303.9604334709416</v>
+        <v>321.6639269406393</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>334.1481169114149</v>
+        <v>336.7305193014324</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>271.8054495766799</v>
+        <v>282.3950382783036</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>37.59999847412109</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.0405829171313108</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.0177083448864976</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.1078568727156155</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>36.07408085190843</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>38.26583221483261</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>41.65541672365171</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>35.23785181247381</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>37.45999908447266</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.0597383648825704</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.1046024808035823</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>35.22219999066368</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>37.12381878931538</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>41.37840791960842</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>35.09963061790675</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="M12" s="17" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
@@ -1722,28 +1731,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>73.5</v>
+        <v>73.59999847412109</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0950764079143317</v>
+        <v>-0.0627803164760323</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.0301236938145638</v>
+        <v>-0.0102639194615808</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0779923584675126</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>66.51188401829663</v>
+        <v>68.97936727728028</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>71.28590850462956</v>
+        <v>72.84457401741025</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>77.292118141522</v>
+        <v>79.34023593832313</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>66.51188401829663</v>
+        <v>68.94782763184115</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1751,7 +1760,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>70.01000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1765,116 +1774,116 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>41.2599983215332</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.0573249196105843</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.09721904629672171</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>38.89477223461847</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>42.98375313528766</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>45.271256008557</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>38.89477223461847</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
-        <v>133.6999969482422</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>-0.0371959299442395</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0.0265060621964958</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>0.106493257751661</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>128.7269012282104</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>137.2438573830236</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>147.9381451846477</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>126.7051807848712</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="D15" s="18" t="n">
+        <v>134.3999938964844</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0373630453895584</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.0265059178623019</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1353648461994133</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>129.3784008241737</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>137.9623890953985</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>152.5930283994841</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>127.4179475839125</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="14" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N14" s="14" t="inlineStr">
+      <c r="M15" s="17" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O14" s="14" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>41.52000045776367</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0573248407643312</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.0831932668372119</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>39.13987304298741</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>43.25461385503717</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>44.97418493492756</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>39.13987304298741</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1893,28 +1902,28 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>108.5999984741211</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.0476952027399054</v>
+        <v>-0.0418361433163467</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.0232805184548855</v>
+        <v>-0.0045423790022753</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.0289375192237391</v>
+        <v>0.0584662245874291</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>103.4202995293445</v>
+        <v>103.6733263690872</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>106.0717342054438</v>
+        <v>107.7085115540582</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>111.742613017664</v>
+        <v>114.5260422701772</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>103.169998550415</v>
+        <v>102.7899971008301</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
@@ -1922,11 +1931,11 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>70.01000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -1936,64 +1945,121 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>188</v>
-      </c>
-      <c r="E17" s="19" t="n">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>189.1999969482422</v>
+      </c>
+      <c r="E17" s="22" t="n">
         <v>-0.0567376780722056</v>
       </c>
-      <c r="F17" s="19" t="n">
-        <v>0.0086283261623434</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.1410512655708424</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>177.3333165224253</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>189.6221253185206</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>214.5176379273184</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>177.3333165224253</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="F17" s="22" t="n">
+        <v>-0.0048223569488908</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>0.0915686225707039</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>178.4652284301305</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>188.2876070282287</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>206.5247800591741</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>178.4652284301305</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="17" t="n">
-        <v>70.01000000000001</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="M17" s="20" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>83</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.035516201414184</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0011987972727639</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0637570370071823</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>80.05215528262273</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>82.90049982636059</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>88.29183407159613</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M18" s="23" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2023,7 +2089,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2117,7 +2183,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2127,20 +2193,20 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.1067493112947659</v>
+        <v>0.1715727502102606</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.2155824508320727</v>
+        <v>0.1715727502102606</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.6739583333333334</v>
+        <v>0.207105719237435</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.1733392396294026</v>
+        <v>0.1053862515297376</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2148,10 +2214,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0328480978204836</v>
+        <v>0.022824820174067</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0618301731244848</v>
+        <v>0.014527377775034</v>
       </c>
     </row>
     <row r="5">
@@ -2160,7 +2226,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -2170,74 +2236,74 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.0407608695652172</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.1364985163204748</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.490272373540856</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.2084925376808879</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>0.0333845842154189</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0.0062282699504712</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
-        <v>0.1683501683501682</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.1722972972972973</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0.2493249324932493</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.09241424947943019</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>0.0228253194034348</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>0.0769231154335685</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-0.011445169685299</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.08805921110630691</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.27063811454039</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.1638890498086234</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="E6" s="19" t="n">
+        <v>-0.0027853227890113</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.0356482758399372</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.2709433611854073</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.1962294384679235</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.0205108171107322</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0485934285285993</v>
+      <c r="J6" s="19" t="n">
+        <v>0.0191340474780803</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.0485934335110049</v>
       </c>
     </row>
     <row r="7">
@@ -2251,79 +2317,79 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0.0274914089347078</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.1240601503759397</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.1527607763296543</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.1303337893963583</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.027767494517887</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.07579908675799089</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>0.0255102040816326</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.140964995269631</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.1936118332407577</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.122078307634617</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0277398977566513</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.008160641694665301</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0.1148809757632745</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.0883207750507701</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>-0.0203975564790146</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-0.0042298975348272</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>0.07613050806987549</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.0700056666818647</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.0279214535298276</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.0159354616706395</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0315051858549603</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>-0.0089743807627755</v>
+      <c r="J8" s="19" t="n">
+        <v>0.031411526030687</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.0177083448864976</v>
       </c>
     </row>
     <row r="9">
@@ -2346,16 +2412,16 @@
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>0.1395348837209302</v>
+        <v>0.1001494289301387</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>0.06909090909090899</v>
+        <v>0.0469416113671246</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>0.0362801622500823</v>
+        <v>0.0209529855064856</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>-0.0183698889398818</v>
+        <v>-0.0447680981446837</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
@@ -2363,96 +2429,96 @@
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.0317184743548069</v>
+        <v>0.0316044221381045</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>-0.0301236938145638</v>
+        <v>-0.0102639194615808</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0.0574064028060217</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.3912512579041269</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.664849108892847</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>-0.1760931619255558</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0.0275358386591078</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E10" s="16" t="n">
-        <v>0.0695999755859375</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0522159349026454</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>-0.0620165519633377</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>0.0218837942188241</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="E11" s="19" t="n">
+        <v>0.039443083715049</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.0312037296445557</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>-0.0696524974832244</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.0134026473895743</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="16" t="n">
-        <v>0.0261586249926347</v>
-      </c>
-      <c r="K10" s="16" t="n">
-        <v>0.0265060621964958</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0602655929404332</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.4412516072896149</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.7163355302217362</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>-0.1939045391077194</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0276545256391398</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.0417777788571567</v>
+      <c r="J11" s="19" t="n">
+        <v>0.0259748758543451</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>0.0265059178623019</v>
       </c>
     </row>
     <row r="12">
@@ -2475,16 +2541,16 @@
         </is>
       </c>
       <c r="E12" s="22" t="n">
-        <v>0.0333016179906207</v>
+        <v>0.0074487468435511</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0102325439453125</v>
+        <v>-0.0036832553545037</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.1219007753135499</v>
+        <v>0.0918264239579929</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0.0002736480868266</v>
+        <v>-0.0029473548475476</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -2492,311 +2558,311 @@
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.0234638800871573</v>
+        <v>0.0234356151634331</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>-0.0232805184548855</v>
+        <v>-0.0045423790022753</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.0052910052910053</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0172504077319066</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.0847012600238372</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>0.06328416996789429</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0089051702597958</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.0267489563349015</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.0603681738976948</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>0.07210575195353749</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0216284538786151</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>0.0086283261623434</v>
+      <c r="J13" s="22" t="n">
+        <v>0.02154465758949</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>-0.0048223569488908</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>0.08040199624319409</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>0.0058479532163742</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>0.3429002625234754</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-0.1377224091460074</v>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>0.0234260282216593</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>0.1009765961097133</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n">
-        <v>0.027408599506155</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>-0.0307541864976126</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.3351236975145872</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>-0.1533211302579805</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0227954635167686</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.0324555250908626</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="E15" s="27" t="n">
+        <v>0.0241176829618565</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.0241030714130169</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.1581237740120248</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-0.0356903702952183</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0217844133924391</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>0.0055698143989002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n">
-        <v>0.03999998304579</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>0.0516853761137201</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>0.0491312154261469</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.1368626562825304</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="E16" s="27" t="n">
+        <v>0.0142076836257685</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0.0114441749510387</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0.0249009981329559</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-0.1177832331507001</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0257744191435242</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0027831487746044</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="J16" s="27" t="n">
+        <v>0.025517260122021</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0461441638796008</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="24" t="n">
-        <v>0.0367734088006828</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>-0.0101925424096686</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>-0.1198388837881133</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.0634197646078955</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
+      <c r="E17" s="27" t="n">
+        <v>-0.0413149842611964</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.0240860857244836</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.0865044675889137</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.1111132863407173</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0262362144212885</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0191753146075474</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.0867492723801184</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.081495719712292</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>0.1270588145536535</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.1020873634098058</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0218173629922759</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0118473493714823</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="J18" s="27" t="n">
+        <v>0.0267153449343472</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.0531914626506075</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.0294642794041</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>0.001024999231536</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>0.1156307329762629</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.1258789211011524</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0263186581136348</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0191753146075474</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.09596928912458</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0523138356178183</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.1274686525922364</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.1254307475911468</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="E19" s="27" t="n">
+        <v>-0.0426356010329254</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.1050724484945041</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>-0.1026339289643072</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-0.0922446127363859</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0273682527266637</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0759492964836558</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0358180490641695</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.09124087718268729</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.0691588927652234</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.0852352006628922</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0183517441559908</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.09498274421764449</v>
+      <c r="J19" s="27" t="n">
+        <v>0.018336817608693</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.0629610288629467</v>
       </c>
     </row>
     <row r="20">
@@ -2815,31 +2881,31 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.0487238642335918</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1767068146963282</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>-0.1183548623844481</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.0791441781158497</v>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>-0.0470723139603644</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1733067854724476</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1262230915835717</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.1070771803391674</v>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="24" t="n">
-        <v>0.021816982577849</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.0937362922905394</v>
+      <c r="J20" s="25" t="n">
+        <v>0.021856735996145</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>-0.0011987972727639</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +2963,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, THYAO.IS, BIMAS.IS, GARAN.IS, EREGL.IS</t>
+          <t>BIMAS.IS, TOASO.IS, YKBNK.IS, EREGL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2975,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, KCHOL.IS</t>
+          <t>THYAO.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2987,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, AKBNK.IS, TCELL.IS</t>
+          <t>AKBNK.IS, TCELL.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2999,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, SAHOL.IS, PGSUS.IS, SISE.IS, PETKM.IS, ARCLK.IS, FROTO.IS</t>
+          <t>TUPRS.IS, PGSUS.IS, SAHOL.IS, SISE.IS, PETKM.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3011,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.76 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.61 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3040,7 +3106,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3238,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3250,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3274,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3300,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3332,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14497.400390625</v>
+        <v>14190</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3342,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12673.43902832031</v>
+        <v>12688.55952636719</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +3376,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>70.01000000000001</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="9">
@@ -3344,7 +3410,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -3353,7 +3419,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-06</t>
+          <t>Rapor Tarihi: 2026-07-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-08 04:55</t>
+          <t>Son Güncelleme: 2026-07-09 05:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3431,23 +3497,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="28" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>174.8000030517578</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.03800480633750802</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>380.0480633750813</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.0525758902510216</v>
+      <c r="D4" s="28" t="n">
+        <v>174.1000061035156</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.033848054712728</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>338.4805471272794</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="5">
@@ -3461,29 +3527,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="28" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>133.6999969482422</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>0.08610884326167967</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>861.0884326167961</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.0525758902510216</v>
+      <c r="D5" s="28" t="n">
+        <v>134.3999938964844</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>0.09179525233494501</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>917.9525233494496</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3491,89 +3557,89 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
-        <v>85.19999694824219</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>82</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.03755865097255984</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-375.5865097255974</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.0525758902510216</v>
+      <c r="C6" s="28" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>43.15999984741211</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.05142857478215146</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-1542.857243464547</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>43.47999954223633</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.04439561445634443</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-1331.868433690335</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.0525758902510216</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>41.2599983215332</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>0.02280610226736179</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>16219.87714212621</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>41.52000045776367</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>0.02925137086545315</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>20803.80225056759</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.0525758902510216</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>348.25</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>0.0450112528132034</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>1480.061789367894</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3581,113 +3647,113 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>347</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>0.04126031507876959</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>1356.723306920569</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.0525758902510216</v>
+      <c r="C9" s="28" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>299</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>-0.02367346938775505</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>-778.4319536271323</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>301.5</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>-0.01551020408163262</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>-510.0071420315689</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.0525758902510216</v>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>383</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-0.04130162703379225</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-29096.15957756399</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>401.75</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>0.005632040050062681</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>3967.658124213223</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.0525758902510216</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>371</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>0.00876010781671166</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>23837.52783386968</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>371</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>371</v>
-      </c>
-      <c r="E12" s="26" t="n">
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>37.59999847412109</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>37.59999847412109</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="F12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>4287748.934738215</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>0.0525758902510216</v>
+      <c r="G12" s="28" t="n">
+        <v>4273715.312093651</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>0.0578955334665061</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -101,7 +101,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,10 +157,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,15 +197,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -638,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 69.55/100</t>
+          <t>Güven Puanı: 67.95/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -749,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, BIMAS.IS, EREGL.IS, YKBNK.IS, GARAN.IS</t>
+          <t>AL: THYAO.IS, TOASO.IS, BIMAS.IS, EREGL.IS, AKBNK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -766,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: THYAO.IS, ASELS.IS</t>
+          <t>AZALT: ASELS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -783,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: AKBNK.IS, TCELL.IS, KCHOL.IS, FROTO.IS</t>
+          <t>ÇIK: TUPRS.IS, YKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -960,7 +951,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -969,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1220825652377705</v>
+        <v>0.1202194935753623</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12208.25652377705</v>
+        <v>12021.94935753622</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.07579908675799089</v>
+        <v>0.0769231988729672</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>925.3746954095852</v>
+        <v>924.7668012704993</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>321.6639269406393</v>
+        <v>357.5385020258252</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>282.3950382783036</v>
+        <v>315.4</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.364888839883686</v>
+        <v>1.538463977459344</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1003,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1012,29 +1003,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1156010339188141</v>
+        <v>0.1198309234647827</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11560.10339188141</v>
+        <v>11983.09234647827</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0485934335110049</v>
+        <v>0.1075944977861207</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>561.7451155537316</v>
+        <v>1289.314802944036</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>392.4360924914936</v>
+        <v>329.7862617158174</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>355.5375</v>
+        <v>281.7427966679223</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9718686702200992</v>
+        <v>2.001365326047824</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1035,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1053,27 +1044,27 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09098426890552622</v>
+        <v>0.1013334179194917</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9098.426890552622</v>
+        <v>10133.34179194917</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0417778692166073</v>
+        <v>0.0485933309785036</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>380.1128887103704</v>
+        <v>492.4128316144886</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>42.98375313528766</v>
+        <v>394.0089441151727</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>38.89477223461847</v>
+        <v>356.9625</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.7287907161564283</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+        <v>0.9718666195700699</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1094,29 +1085,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08707323101637048</v>
+        <v>0.08156721901598346</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8707.323101637048</v>
+        <v>8156.721901598346</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0177083448864976</v>
+        <v>0.0521950351766851</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>154.1922805219568</v>
+        <v>425.7403865803635</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>38.26583221483261</v>
+        <v>42.02466825998682</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>35.23785181247381</v>
+        <v>37.75738124191095</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.2818765453992548</v>
+        <v>0.9551237187963362</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1135,29 +1126,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08425890092151866</v>
+        <v>0.07704894602437998</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8425.890092151867</v>
+        <v>7704.894602437997</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0265059178623019</v>
+        <v>0.0669740990092095</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>223.3359506993608</v>
+        <v>516.0283739592063</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>137.9623890953985</v>
+        <v>75.38172172307392</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>127.4179475839125</v>
+        <v>66.13286755390935</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5102222241779831</v>
+        <v>1.047504950386029</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1176,10 +1167,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000</v>
+        <v>49999.99999999999</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1208,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1252,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1294,7 +1285,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 11</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1437,111 +1428,111 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>377</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0771413085746594</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0062283411144734</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.2830390713974848</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>347.9177266673534</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>379.3480846001565</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>483.7057299168518</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>347.9177266673534</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>348.25</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0628859824625369</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.014527377775034</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.1444448294649761</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>326.3499566074215</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>353.3091593101556</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>398.5529118611779</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>326.3499566074215</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>332</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0478684433228991</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0769231988729672</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.3470097212410028</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>316.1076768167975</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>357.5385020258252</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>447.2072274520129</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>383</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0563155286172766</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.0062282699504712</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.1235737562936812</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>361.4311525395831</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>385.3854273910305</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>430.3287486604799</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>357.4274084909891</v>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1542,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -1560,36 +1551,36 @@
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>374.25</v>
+        <v>297.75</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.0037105176120389</v>
+        <v>-0.0280674049032044</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0485934335110049</v>
+        <v>0.1075944977861207</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.1185389470069964</v>
+        <v>0.1296241685699918</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>372.8613387836945</v>
+        <v>289.3929301900709</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>392.4360924914936</v>
+        <v>329.7862617158174</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>418.6132009173684</v>
+        <v>336.345596191715</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>355.5375</v>
+        <v>281.7427966679223</v>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
       <c r="M10" s="17" t="n">
-        <v>69.55</v>
+        <v>67.95</v>
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
@@ -1598,7 +1589,7 @@
       </c>
       <c r="O10" s="17" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1599,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1617,36 +1608,36 @@
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>299</v>
+        <v>375.75</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0392112770744697</v>
+        <v>0.0079654248712648</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.07579908675799089</v>
+        <v>0.0485933309785036</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1261890277639881</v>
+        <v>0.0892148819792251</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>287.2758281547336</v>
+        <v>378.7430083953778</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>321.6639269406393</v>
+        <v>394.0089441151727</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>336.7305193014324</v>
+        <v>409.2724919036938</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>282.3950382783036</v>
+        <v>356.9625</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M11" s="17" t="n">
-        <v>69.55</v>
+        <v>67.95</v>
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
@@ -1655,7 +1646,7 @@
       </c>
       <c r="O11" s="17" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1656,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -1674,45 +1665,45 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>37.59999847412109</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0405829171313108</v>
+        <v>-0.0535298595992588</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>0.0177083448864976</v>
+        <v>0.0521950351766851</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.1078568727156155</v>
+        <v>0.1392961182157173</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>36.07408085190843</v>
+        <v>37.80201610782666</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>38.26583221483261</v>
+        <v>42.02466825998682</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>41.65541672365171</v>
+        <v>45.50348539695062</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>35.23785181247381</v>
+        <v>37.75738124191095</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M12" s="17" t="n">
-        <v>69.55</v>
+        <v>67.95</v>
       </c>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O12" s="17" t="inlineStr">
         <is>
-          <t>volatilite yüksek</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1722,344 +1713,287 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0604839867778684</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.0037500012947557</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.09570146715044869</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>240.9858573914768</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>255.5381246678952</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>281.0474263240901</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>240.9858573914768</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>184</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.0258854768792181</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.0143885670157133</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>0.1169949073027232</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>179.2370722542239</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>186.6474963308912</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>205.5270629437011</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>36.22000122070312</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-0.104751646118041</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.043269249898777</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>0.1046024808035823</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>32.42589647043702</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>34.65278893655051</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>40.00870320309745</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>32.42589647043702</v>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>130.3999938964844</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.0375303774291616</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.0292262169872642</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>0.1489898479630693</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>125.506032908789</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>134.2110924132409</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>149.8282691615068</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>123.603265045301</v>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>73.59999847412109</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0627803164760323</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.0102639194615808</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.0779923584675126</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>68.97936727728028</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>72.84457401741025</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>79.34023593832313</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>68.94782763184115</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="20" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>70.65000152587891</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>0.0300643724938871</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.0669740990092095</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.1197718415174995</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>72.77404948844662</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>75.38172172307392</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>79.11188231184758</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>66.13286755390935</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>41.2599983215332</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.0573249196105843</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.09721904629672171</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>38.89477223461847</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>42.98375313528766</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>45.271256008557</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>38.89477223461847</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>134.3999938964844</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0373630453895584</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>0.0265059178623019</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1353648461994133</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>129.3784008241737</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>137.9623890953985</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>152.5930283994841</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>127.4179475839125</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>108.1999969482422</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.0418361433163467</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.0045423790022753</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>0.0584662245874291</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>103.6733263690872</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>107.7085115540582</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>114.5260422701772</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>102.7899971008301</v>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>189.1999969482422</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-0.0567376780722056</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>-0.0048223569488908</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>0.0915686225707039</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>178.4652284301305</v>
-      </c>
-      <c r="I17" s="21" t="n">
-        <v>188.2876070282287</v>
-      </c>
-      <c r="J17" s="21" t="n">
-        <v>206.5247800591741</v>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>178.4652284301305</v>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>83</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.035516201414184</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0011987972727639</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0637570370071823</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>80.05215528262273</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>82.90049982636059</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>88.29183407159613</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>78.84999999999999</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O18"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2089,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2106,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2183,84 +2117,84 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.0552834149755072</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.1023391812865497</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.430740037950664</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>0.2388378291931963</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.0334250675175611</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.0062283411144734</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>0.1715727502102606</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.1715727502102606</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.207105719237435</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.1053862515297376</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>0.1187868576242627</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.1369863013698631</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.1418744625967325</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.1403751820277814</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.022824820174067</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.014527377775034</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.0407608695652172</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.1364985163204748</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0.490272373540856</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.2084925376808879</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>0.0333845842154189</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>0.0062282699504712</v>
+      <c r="J5" s="19" t="n">
+        <v>0.0235251946764696</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0769231988729672</v>
       </c>
     </row>
     <row r="6">
@@ -2269,12 +2203,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -2283,16 +2217,16 @@
         </is>
       </c>
       <c r="E6" s="19" t="n">
-        <v>-0.0027853227890113</v>
+        <v>0.009322033898305101</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>0.0356482758399372</v>
+        <v>0.181547619047619</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.2709433611854073</v>
+        <v>0.1336305713390384</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.1962294384679235</v>
+        <v>0.151053196090058</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -2300,10 +2234,10 @@
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0.0191340474780803</v>
+        <v>0.0268802742772085</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0485934335110049</v>
+        <v>0.1075944977861207</v>
       </c>
     </row>
     <row r="7">
@@ -2312,7 +2246,7 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2326,16 +2260,16 @@
         </is>
       </c>
       <c r="E7" s="19" t="n">
-        <v>0.0274914089347078</v>
+        <v>-0.0157471490217966</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.1240601503759397</v>
+        <v>0.0222112153873117</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.1527607763296543</v>
+        <v>0.2496510894200649</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.1303337893963583</v>
+        <v>0.2057401190119081</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -2343,10 +2277,10 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.027767494517887</v>
+        <v>0.0190227382797683</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>0.07579908675799089</v>
+        <v>0.0485933309785036</v>
       </c>
     </row>
     <row r="8">
@@ -2355,7 +2289,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -2369,16 +2303,16 @@
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>0.07613050806987549</v>
+        <v>0.0336438731261681</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.0700056666818647</v>
+        <v>0.4037122918511659</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.0279214535298276</v>
+        <v>0.6564265163831884</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>-0.0159354616706395</v>
+        <v>-0.1675138680220886</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -2386,10 +2320,10 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.031411526030687</v>
+        <v>0.027323703803766</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0.0177083448864976</v>
+        <v>0.0521950351766851</v>
       </c>
     </row>
     <row r="9">
@@ -2398,471 +2332,471 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>-0.0134615384615384</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>0.3411276780294834</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.0948128264481293</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0.0233763163900396</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>-0.0037500012947557</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.0144616871578776</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>-0.0320884056163258</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.0430585828994471</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.07462818516432621</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0.0216430600177423</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>0.0143885670157133</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>0.0191333789436873</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>0.0547466819965507</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>-0.0377257755571546</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>0.0070570038590382</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>0.0316338726159951</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>-0.043269249898777</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.0259637723208563</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>-0.07202745946720721</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.0135318505684387</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>0.0260610781031892</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>0.0292262169872642</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>0.1001494289301387</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0.0469416113671246</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0.0209529855064856</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>-0.0447680981446837</v>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>0.0316044221381045</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>-0.0102639194615808</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0.0521221134842586</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.0202166285325473</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.0084972979825233</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-0.0430325934202913</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.0319683926002107</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>0.0669740990092095</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.0574064028060217</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.3912512579041269</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.664849108892847</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.1760931619255558</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0275358386591078</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>-0.0009478528352709</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0.0047664441632695</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.0668016019256962</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>-0.0132006345431</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>0.0232644411966896</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.0120847040538301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.039443083715049</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0312037296445557</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>-0.0696524974832244</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.0134026473895743</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0.0259748758543451</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>0.0265059178623019</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-0.0494559858535474</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.1231752168586647</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0.1454111160228304</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.0603354216117736</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>0.0258864327014241</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0020367065565403</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>0.0074487468435511</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>-0.0036832553545037</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.0918264239579929</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>-0.0029473548475476</v>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>0.0234356151634331</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>-0.0045423790022753</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>-0.013157861714877</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>0.0078387113585705</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0.0110106198075969</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.1134677941121327</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>0.0255805749052704</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.1168632615698388</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0089051702597958</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.0267489563349015</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.0603681738976948</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>0.07210575195353749</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>0.02154465758949</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>-0.0048223569488908</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
-        <v>0.08040199624319409</v>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>0.0058479532163742</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>0.3429002625234754</v>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-0.1377224091460074</v>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J14" s="27" t="n">
-        <v>0.0234260282216593</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>0.1009765961097133</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="E17" s="24" t="n">
+        <v>-0.0171698875149854</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.0514285714285713</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-0.1906387369085769</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.015601392306086</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0224339856142938</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0270714525721503</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>0.0241176829618565</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.0241030714130169</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.1581237740120248</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-0.0356903702952183</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="E18" s="24" t="n">
+        <v>-0.055609726324314</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.0944808075767523</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>-0.1191992565262735</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.08424939661012459</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0217844133924391</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>0.0055698143989002</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="J18" s="24" t="n">
+        <v>0.0180884894343277</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.0591899347447655</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
-        <v>0.0142076836257685</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>0.0114441749510387</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0.0249009981329559</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-0.1177832331507001</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="27" t="n">
-        <v>0.025517260122021</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.0461441638796008</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.0413149842611964</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.0240860857244836</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>0.0865044675889137</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.1111132863407173</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0262362144212885</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>0.0191753146075474</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>-0.0867492723801184</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>-0.081495719712292</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0.1270588145536535</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-0.1020873634098058</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="E19" s="24" t="n">
+        <v>-0.0613441860925292</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.0374217230384893</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>0.0571947776456849</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.1007235450967398</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0267153449343472</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>0.0531914626506075</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>-0.0426356010329254</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>-0.1050724484945041</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>-0.1026339289643072</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-0.0922446127363859</v>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>0.018336817608693</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>0.0629610288629467</v>
+      <c r="J19" s="24" t="n">
+        <v>0.0264720590004156</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.0236686907772818</v>
       </c>
     </row>
     <row r="20">
@@ -2881,32 +2815,30 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.0470723139603644</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1733067854724476</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1262230915835717</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.1070771803391674</v>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>-0.0637311680823627</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.1644260020503899</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>-0.1432796189944291</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.1145317080032551</v>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n">
-        <v>0.021856735996145</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>-0.0011987972727639</v>
-      </c>
+      <c r="J20" s="24" t="n">
+        <v>0.0216343395909976</v>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:K20"/>
@@ -2930,7 +2862,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2938,7 +2870,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2963,7 +2895,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TOASO.IS, YKBNK.IS, EREGL.IS, GARAN.IS</t>
+          <t>THYAO.IS, TOASO.IS, BIMAS.IS, EREGL.IS, AKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2907,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ASELS.IS</t>
+          <t>ASELS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2919,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, TCELL.IS, KCHOL.IS, FROTO.IS</t>
+          <t>TUPRS.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2931,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, PGSUS.IS, SAHOL.IS, SISE.IS, PETKM.IS, ARCLK.IS</t>
+          <t>TCELL.IS, PETKM.IS, SAHOL.IS, PGSUS.IS, ARCLK.IS, SISE.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -3011,7 +2943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.61 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.89 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3049,7 +2981,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3057,7 +2989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3082,7 +3014,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3086,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3170,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3206,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3232,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3308,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3332,7 +3264,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14190</v>
+        <v>14105.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3342,7 +3274,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12688.55952636719</v>
+        <v>12703.84603027344</v>
       </c>
     </row>
     <row r="6">
@@ -3376,7 +3308,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>69.55</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="9">
@@ -3419,7 +3351,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-07</t>
+          <t>Rapor Tarihi: 2026-07-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3433,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-09 05:53</t>
+          <t>Son Güncelleme: 2026-07-10 05:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3497,23 +3429,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>174.1000061035156</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.033848054712728</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>338.4805471272794</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D4" s="25" t="n">
+        <v>166</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>-0.01425174574507204</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>-142.51745745072</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="5">
@@ -3527,23 +3459,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>134.3999938964844</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0.09179525233494501</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>917.9525233494496</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D5" s="25" t="n">
+        <v>130.3999938964844</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.05930134453980473</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>593.0134453980463</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="6">
@@ -3557,23 +3489,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>45.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>43.15999984741211</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.05142857478215146</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-1542.857243464547</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D6" s="25" t="n">
+        <v>41.61999893188477</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.08527474874978536</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-2558.242462493563</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="7">
@@ -3587,23 +3519,23 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>40.34000015258789</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>41.2599983215332</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0.02280610226736179</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>16219.87714212621</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D7" s="25" t="n">
+        <v>39.93999862670898</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.009915754198460136</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-7052.161434034933</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="8">
@@ -3617,23 +3549,23 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="25" t="n">
         <v>333.25</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>348.25</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>0.0450112528132034</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>1480.061789367894</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D8" s="25" t="n">
+        <v>332</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.003750937734433579</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-123.3384824473214</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="9">
@@ -3647,23 +3579,23 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="25" t="n">
         <v>306.25</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>299</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>-0.02367346938775505</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-778.4319536271323</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D9" s="25" t="n">
+        <v>297.75</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>-0.02775510204081633</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>-912.644359424914</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="10">
@@ -3677,23 +3609,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="25" t="n">
         <v>399.5</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>383</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-0.04130162703379225</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-29096.15957756399</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D10" s="25" t="n">
+        <v>377</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.05632040050062581</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>-39676.5812421327</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="11">
@@ -3707,53 +3639,53 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="25" t="n">
         <v>371</v>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>374.25</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0.00876010781671166</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>23837.52783386968</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="D11" s="25" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.01280323450134779</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>34839.46375719411</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>37.59999847412109</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>37.59999847412109</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="F12" s="28" t="n">
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>70.65000152587891</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>70.65000152587891</v>
+      </c>
+      <c r="E12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="28" t="n">
-        <v>4273715.312093651</v>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>0.0578955334665061</v>
+      <c r="F12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>4246948.309279991</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>0.0354640980735552</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,6 +102,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,7 +165,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +688,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 67.95/100</t>
+          <t>Güven Puanı: 69.81/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +748,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: THYAO.IS, TOASO.IS, BIMAS.IS, EREGL.IS, AKBNK.IS</t>
+          <t>AL: TOASO.IS, BIMAS.IS, ASELS.IS, EREGL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +765,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: ASELS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>AZALT: KCHOL.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +782,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, YKBNK.IS</t>
+          <t>ÇIK: THYAO.IS, TUPRS.IS, YKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -951,7 +959,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -960,29 +968,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1202194935753623</v>
+        <v>0.1298803383942314</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12021.94935753622</v>
+        <v>12988.03383942314</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0769231988729672</v>
+        <v>0.1075944148219777</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>924.7668012704993</v>
+        <v>1397.439900640777</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>357.5385020258252</v>
+        <v>326.7403523724834</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>315.4</v>
+        <v>280.1182279728189</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.538463977459344</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>2.132834202439777</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -994,7 +1002,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +1011,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1198309234647827</v>
+        <v>0.1103018119945178</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11983.09234647827</v>
+        <v>11030.18119945178</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1075944977861207</v>
+        <v>0.0485933259961082</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1289.314802944036</v>
+        <v>535.9931908211042</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>329.7862617158174</v>
+        <v>382.7365639885795</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>281.7427966679223</v>
+        <v>346.75</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.001365326047824</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
+        <v>0.9718665199221654</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1043,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,25 +1052,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1013334179194917</v>
+        <v>0.1010801374353509</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10133.34179194917</v>
+        <v>10108.01374353509</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485933309785036</v>
+        <v>0.0439164979259993</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>492.4128316144886</v>
+        <v>443.908564603931</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>394.0089441151727</v>
+        <v>374.5050436309523</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>356.9625</v>
+        <v>334.9231316263845</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718666195700699</v>
+        <v>0.661230145057524</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1085,25 +1093,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08156721901598346</v>
+        <v>0.08498979102386779</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8156.721901598346</v>
+        <v>8498.979102386778</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0521950351766851</v>
+        <v>0.0417778692166073</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>425.7403865803635</v>
+        <v>355.0692374141933</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>42.02466825998682</v>
+        <v>41.73362287148148</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>37.75738124191095</v>
+        <v>37.71751722939798</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.9551237187963362</v>
+        <v>0.7144643871138553</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1117,7 +1125,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1126,62 +1134,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07704894602437998</v>
+        <v>0.0737479211520321</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7704.894602437997</v>
+        <v>7374.79211520321</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0669740990092095</v>
+        <v>0.0233118283326481</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>516.0283739592063</v>
+        <v>171.919887778584</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>75.38172172307392</v>
+        <v>133.1328751118772</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>66.13286755390935</v>
+        <v>122.850931549045</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.047504950386029</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.4183801650227493</v>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>49999.99999999999</v>
-      </c>
-      <c r="F25" s="12" t="n">
+      <c r="D25" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1222,7 +1230,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1423,572 +1431,572 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.1079385998814506</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>-0.0478684433228991</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.3470097212410028</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>301.7397685900993</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>322.0584990460294</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>455.6260382097692</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>301.7397685900993</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>295</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>-0.0347638056112084</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.1075944148219777</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.1296240822210881</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>284.7446773446935</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>326.7403523724834</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>333.239104255221</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>280.1182279728189</v>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>365</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-0.0006844626967830001</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.0485933259961082</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.08921495188780421</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>364.7501711156742</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>382.7365639885795</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>397.5634574390485</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>-0.065000031562885</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0.0439164979259993</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.1382006391848767</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>335.431238676815</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>374.5050436309523</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>408.3294793075745</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>334.9231316263845</v>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0378433523870624</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>-0.008302551330894799</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.1756284887830799</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>254.2498941317188</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>262.0560508108111</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>310.6598281609288</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>251.0375</v>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>40.06000137329102</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-0.0584743900047599</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.1392961182157173</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>37.71751722939798</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>41.73362287148148</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>45.64020406030676</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>37.71751722939798</v>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>377</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0771413085746594</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0062283411144734</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.2830390713974848</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>347.9177266673534</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>379.3480846001565</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>483.7057299168518</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>347.9177266673534</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="D14" s="22" t="n">
+        <v>185.1000061035156</v>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>-0.0245806465802865</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0.0143885670157133</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>0.0729758361499268</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>180.5501282714762</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>187.763329945945</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>198.6078338202763</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>175.8450057983398</v>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>332</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0478684433228991</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0769231988729672</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.3470097212410028</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>316.1076768167975</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>357.5385020258252</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>447.2072274520129</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>297.75</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0280674049032044</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.1075944977861207</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1296241685699918</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>289.3929301900709</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>329.7862617158174</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>336.345596191715</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>281.7427966679223</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>375.75</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.0079654248712648</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0485933309785036</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.0892148819792251</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>378.7430083953778</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>394.0089441151727</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>409.2724919036938</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>356.9625</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>39.93999862670898</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.0535298595992588</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.0521950351766851</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.1392961182157173</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>37.80201610782666</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>42.02466825998682</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>45.50348539695062</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>37.75738124191095</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="D15" s="19" t="n">
+        <v>130.1000061035156</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>-0.0557192483811474</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0.0233118283326481</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0.1272216922975995</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>122.850931549045</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>133.1328751118772</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>146.6515490479329</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>122.850931549045</v>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
-        <v>256.5</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0604839867778684</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.0037500012947557</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.09570146715044869</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>240.9858573914768</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>255.5381246678952</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>281.0474263240901</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>240.9858573914768</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="D16" s="16" t="n">
+        <v>35.86000061035156</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.1065088329994344</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>-0.0199168792367259</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.1064815305875086</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>32.04059379398402</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>35.14578130876627</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>39.67842836221079</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>32.04059379398402</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="M16" s="15" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
-        <v>184</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>-0.0258854768792181</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0.0143885670157133</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>0.1169949073027232</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>179.2370722542239</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>186.6474963308912</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>205.5270629437011</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="D17" s="22" t="n">
+        <v>104.9000015258789</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>-0.0388692288111882</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>0.0138761110298257</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>0.0600558756766196</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>100.8226193642755</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <v>106.3556055940809</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>111.1998629759943</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>99.65500144958496</v>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="14" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N14" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>36.22000122070312</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>-0.104751646118041</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>-0.043269249898777</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>0.1046024808035823</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>32.42589647043702</v>
-      </c>
-      <c r="I15" s="21" t="n">
-        <v>34.65278893655051</v>
-      </c>
-      <c r="J15" s="21" t="n">
-        <v>40.00870320309745</v>
-      </c>
-      <c r="K15" s="21" t="n">
-        <v>32.42589647043702</v>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="20" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>130.3999938964844</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>-0.0375303774291616</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>0.0292262169872642</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>0.1489898479630693</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>125.506032908789</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>134.2110924132409</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>149.8282691615068</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>123.603265045301</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
+      <c r="M17" s="21" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
         <is>
           <t>trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>70.65000152587891</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>0.0300643724938871</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>0.0669740990092095</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.1197718415174995</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>72.77404948844662</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>75.38172172307392</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>79.11188231184758</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>66.13286755390935</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>volatilite yüksek</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2031,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2112,733 +2120,733 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0.1446700507614213</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0.0670347003154574</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0.1485568760611204</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.1853275754063696</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0.0210892198914123</v>
+      </c>
+      <c r="K4" s="17" t="n">
+        <v>-0.0478684433228991</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0.0172413793103447</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>0.0875576036866359</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>0.1424902812400867</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>0.1733396213044109</v>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>0.0252233424189511</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>0.1075944148219777</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>-0.0357396440926404</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>-0.0228999651161745</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>0.1854638270743971</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>0.1934621837869401</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>0.0192629012047767</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>0.0485933259961082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>-0.0477770404777704</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>-0.0096618357487923</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>0.3653663177925785</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>0.2545649009680228</v>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>0.033208178917931</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0.0439164979259993</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.1254258797507359</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0.0527888446215139</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.398507081209307</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>-0.0468540909558131</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0.0232520955933264</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>-0.008302551330894799</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>0.0367495343186519</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.3727078620629436</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.6425849369727854</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.1520547593895964</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>0.0272064505069125</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0417778692166073</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.0552834149755072</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.1023391812865497</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.430740037950664</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.2388378291931963</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E10" s="23" t="n">
+        <v>0.0005405735325167</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-0.08093340758166361</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.0492942938098481</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>0.1097622211770279</v>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0334250675175611</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.0062283411144734</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="J10" s="23" t="n">
+        <v>0.0202677224988554</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.0143885670157133</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>0.0148206645905033</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-0.0538181374289772</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>-0.0716222775792807</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>0.0262773593328771</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0.0239053454337624</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.0233118283326481</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.0304598102451152</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>-0.044752271289394</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>-0.0467835824429415</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0.0234335431881171</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0.0293932688107371</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>-0.0199168792367259</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>0.002868098050996</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-0.0566546366480171</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0.0526843945771198</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.0007962847384253</v>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.021978629617714</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.0138761110298257</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>0.1187868576242627</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1369863013698631</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.1418744625967325</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.1403751820277814</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0235251946764696</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0769231988729672</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0.009322033898305101</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.181547619047619</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.1336305713390384</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.151053196090058</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0620272098149334</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.07326736701990511</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.003439722222854</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0395223485312272</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0296749648554729</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.1042944785276074</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>0.0029976018636213</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.1005376180013021</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.1894379457411047</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.0238790800857664</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.0209456735330101</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0132897529262719</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>-0.0466165548676777</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.0855768675282135</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0.1423423960079708</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.0191879445593335</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>0.0251320832478948</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0548521525126809</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>-0.0447963689606201</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.0841814743462546</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>0.0713609493574576</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>-0.0689221375287711</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.0268802742772085</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.1075944977861207</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.0157471490217966</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.0222112153873117</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.2496510894200649</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.2057401190119081</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0190227382797683</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.0485933309785036</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="J17" s="25" t="n">
+        <v>0.0251453845022457</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.0121672787419914</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.0336438731261681</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.4037122918511659</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.6564265163831884</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>-0.1675138680220886</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0.027323703803766</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.0521950351766851</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.0219418537193569</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.07472752529597659</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.0051372417203386</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.0858979091386915</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>0.0235486104790141</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0296295530137169</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>-0.0134615384615384</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0.3411276780294834</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>-0.0948128264481293</v>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>0.0233763163900396</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>-0.0037500012947557</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>-0.053921568627451</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.1376228893287134</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.1345291479820628</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.0740245671883331</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.0170044822584004</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0999999076690971</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.0144616871578776</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>-0.0320884056163258</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.0430585828994471</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>0.07462818516432621</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.0216430600177423</v>
-      </c>
-      <c r="K10" s="16" t="n">
-        <v>0.0143885670157133</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>0.0191333789436873</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0.0547466819965507</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>-0.0377257755571546</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>0.0070570038590382</v>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>-0.0754716832983692</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.2057957165972301</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1475556752513833</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.1252150755485725</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="22" t="n">
-        <v>0.0316338726159951</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>-0.043269249898777</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.0259637723208563</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>-0.07202745946720721</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>0.0135318505684387</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>0.0260610781031892</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>0.0292262169872642</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.0521221134842586</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0.0202166285325473</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.0084972979825233</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.0430325934202913</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0319683926002107</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>0.0669740990092095</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>-0.0009478528352709</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>0.0047664441632695</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.0668016019256962</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>-0.0132006345431</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0232644411966896</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.0120847040538301</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0494559858535474</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.1231752168586647</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>0.1454111160228304</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.0603354216117736</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0258864327014241</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0020367065565403</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>-0.013157861714877</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>0.0078387113585705</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.0110106198075969</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.1134677941121327</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0255805749052704</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.1168632615698388</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.0171698875149854</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.0514285714285713</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.1906387369085769</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.015601392306086</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0224339856142938</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0270714525721503</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.055609726324314</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0944808075767523</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-0.1191992565262735</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.08424939661012459</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0180884894343277</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0591899347447655</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0613441860925292</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.0374217230384893</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.0571947776456849</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.1007235450967398</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0264720590004156</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.0236686907772818</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.0637311680823627</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1644260020503899</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>-0.1432796189944291</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.1145317080032551</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.0216343395909976</v>
-      </c>
-      <c r="K20" s="24" t="inlineStr"/>
+      <c r="J20" s="25" t="n">
+        <v>0.0204472511519311</v>
+      </c>
+      <c r="K20" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:K20"/>
@@ -2862,7 +2870,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2870,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2895,7 +2903,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TOASO.IS, BIMAS.IS, EREGL.IS, AKBNK.IS</t>
+          <t>TOASO.IS, BIMAS.IS, ASELS.IS, EREGL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2915,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>KCHOL.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2927,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, YKBNK.IS</t>
+          <t>THYAO.IS, TUPRS.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2939,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, PETKM.IS, SAHOL.IS, PGSUS.IS, ARCLK.IS, SISE.IS, FROTO.IS</t>
+          <t>AKBNK.IS, PGSUS.IS, PETKM.IS, SISE.IS, SAHOL.IS, ARCLK.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2951,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.89 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.89 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2989,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2989,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3014,7 +3022,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3046,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3094,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3178,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3240,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3264,7 +3272,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14105.400390625</v>
+        <v>14321.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3274,7 +3282,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12703.84603027344</v>
+        <v>12718.97953125</v>
       </c>
     </row>
     <row r="6">
@@ -3308,7 +3316,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>67.95</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="9">
@@ -3335,7 +3343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3351,7 +3359,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-08</t>
+          <t>Rapor Tarihi: 2026-07-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3365,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-10 05:49</t>
+          <t>Son Güncelleme: 2026-07-11 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3429,23 +3437,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="26" t="n">
         <v>168.3999938964844</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>166</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>-0.01425174574507204</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>-142.51745745072</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.0354640980735552</v>
+      <c r="D4" s="26" t="n">
+        <v>167.3000030517578</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>-0.006532012378828944</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>-65.32012378828949</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="5">
@@ -3459,23 +3467,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>130.3999938964844</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>0.05930134453980473</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>593.0134453980463</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.0354640980735552</v>
+      <c r="D5" s="26" t="n">
+        <v>130.1000061035156</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>0.05686440061870601</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>568.6440061870599</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="6">
@@ -3489,23 +3497,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>45.5</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>41.61999893188477</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.08527474874978536</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-2558.242462493563</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.0354640980735552</v>
+      <c r="D6" s="26" t="n">
+        <v>42.22000122070312</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.07208788525927201</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-2162.636557778162</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="7">
@@ -3519,29 +3527,29 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>40.34000015258789</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>39.93999862670898</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.009915754198460136</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-7052.161434034933</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.0354640980735552</v>
+      <c r="D7" s="26" t="n">
+        <v>40.06000137329102</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>-0.006940971200737889</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-4936.472651186981</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3549,147 +3557,117 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>332</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.003750937734433579</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-123.3384824473214</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.0354640980735552</v>
+      <c r="C8" s="26" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>295</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>-0.03673469387755102</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-1207.911652180035</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>297.75</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>-0.02775510204081633</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>-912.644359424914</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.0354640980735552</v>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>-0.1020025031289111</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>-71858.69713852904</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>377</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>-0.05632040050062581</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>-39676.5812421327</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.0354640980735552</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>371</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>365</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>-0.01617250673854442</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>-44007.74369329773</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>371</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>375.75</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>0.01280323450134779</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>34839.46375719411</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.0354640980735552</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>70.65000152587891</v>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>70.65000152587891</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>4246948.309279991</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>0.0354640980735552</v>
+      <c r="D11" s="26" t="n">
+        <v>70.19999694824219</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>-0.006369491407185346</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>-59.77284158069051</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>4138744.760793019</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>0.0292907465429801</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H12"/>
+  <autoFilter ref="A3:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0737479211520321</v>
+        <v>0.07374792115203216</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7374.79211520321</v>
+        <v>7374.792115203216</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>171.919887778584</v>
+        <v>171.9198877785856</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>133.1328751118772</v>
+        <v>133.1328751118773</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>122.850931549045</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4183801650227493</v>
+        <v>0.4183801650227533</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1790,13 +1790,13 @@
         <v>185.1000061035156</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>-0.0245806465802865</v>
+        <v>-0.0245806465802866</v>
       </c>
       <c r="F14" s="23" t="n">
         <v>0.0143885670157133</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>0.0729758361499268</v>
+        <v>0.0729758361499266</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>180.5501282714762</v>
@@ -1805,7 +1805,7 @@
         <v>187.763329945945</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>198.6078338202763</v>
+        <v>198.6078338202762</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>175.8450057983398</v>
@@ -1850,7 +1850,7 @@
         <v>-0.0557192483811474</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>0.1272216922975995</v>
@@ -1859,7 +1859,7 @@
         <v>122.850931549045</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>133.1328751118772</v>
+        <v>133.1328751118773</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>146.6515490479329</v>
@@ -1907,7 +1907,7 @@
         <v>-0.1065088329994344</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>-0.0199168792367259</v>
+        <v>-0.0199168792367256</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>0.1064815305875086</v>
@@ -1916,7 +1916,7 @@
         <v>32.04059379398402</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>35.14578130876627</v>
+        <v>35.14578130876628</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>39.67842836221079</v>
@@ -1964,10 +1964,10 @@
         <v>-0.0388692288111882</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>0.0600558756766196</v>
+        <v>0.0600558756766194</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>100.8226193642755</v>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0210892198914123</v>
+        <v>0.0210892198914124</v>
       </c>
       <c r="K4" s="17" t="n">
         <v>-0.0478684433228991</v>
@@ -2228,7 +2228,7 @@
         <v>-0.0357396440926404</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-0.0228999651161745</v>
+        <v>-0.0228999651161747</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>0.1854638270743971</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="J8" s="17" t="n">
-        <v>0.0232520955933264</v>
+        <v>0.0232520955933265</v>
       </c>
       <c r="K8" s="17" t="n">
         <v>-0.008302551330894799</v>
@@ -2357,7 +2357,7 @@
         <v>0.0367495343186519</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.3727078620629436</v>
+        <v>0.3727078620629434</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.6425849369727854</v>
@@ -2400,10 +2400,10 @@
         <v>0.0005405735325167</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.08093340758166361</v>
+        <v>-0.08093340758166399</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0492942938098481</v>
+        <v>0.0492942938098479</v>
       </c>
       <c r="H10" s="23" t="n">
         <v>0.1097622211770279</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0202677224988554</v>
+        <v>0.0202677224988553</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.0143885670157133</v>
@@ -2460,7 +2460,7 @@
         <v>0.0239053454337624</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
     </row>
     <row r="12">
@@ -2503,7 +2503,7 @@
         <v>0.0293932688107371</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>-0.0199168792367259</v>
+        <v>-0.0199168792367256</v>
       </c>
     </row>
     <row r="13">
@@ -2529,7 +2529,7 @@
         <v>0.002868098050996</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0566546366480171</v>
+        <v>-0.0566546366480172</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>0.0526843945771198</v>
@@ -2546,7 +2546,7 @@
         <v>0.021978629617714</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
     </row>
     <row r="14">
@@ -2618,7 +2618,7 @@
         <v>-0.1005376180013021</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.1894379457411047</v>
+        <v>-0.1894379457411048</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.0238790800857664</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0235486104790141</v>
+        <v>0.0235486104790142</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.0296295530137169</v>
+        <v>0.0296295530137167</v>
       </c>
     </row>
     <row r="19">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0170044822584004</v>
+        <v>0.0170044822584005</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>0.0999999076690971</v>
@@ -2830,7 +2830,7 @@
         <v>-0.0754716832983692</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.2057957165972301</v>
+        <v>-0.20579571659723</v>
       </c>
       <c r="G20" s="25" t="n">
         <v>-0.1475556752513833</v>
@@ -2878,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2997,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3248,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3450,7 +3450,7 @@
         <v>-65.32012378828949</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3480,7 +3480,7 @@
         <v>568.6440061870599</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3510,7 +3510,7 @@
         <v>-2162.636557778162</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3540,7 +3540,7 @@
         <v>-4936.472651186981</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3570,7 +3570,7 @@
         <v>-1207.911652180035</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3600,7 +3600,7 @@
         <v>-71858.69713852904</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3630,7 +3630,7 @@
         <v>-44007.74369329773</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3660,7 +3660,7 @@
         <v>-59.77284158069051</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>0.0292907465429801</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2878,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2997,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3248,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3450,7 +3450,7 @@
         <v>-65.32012378828949</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3480,7 +3480,7 @@
         <v>568.6440061870599</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3510,7 +3510,7 @@
         <v>-2162.636557778162</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3540,7 +3540,7 @@
         <v>-4936.472651186981</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3570,7 +3570,7 @@
         <v>-1207.911652180035</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3600,7 +3600,7 @@
         <v>-71858.69713852904</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3630,7 +3630,7 @@
         <v>-44007.74369329773</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3660,7 +3660,7 @@
         <v>-59.77284158069051</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>0.0292907465429801</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,11 +102,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -165,10 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -198,13 +190,13 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -620,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -637,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -688,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 69.81/100</t>
+          <t>Güven Puanı: 74.04/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -748,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, BIMAS.IS, ASELS.IS, EREGL.IS, GARAN.IS</t>
+          <t>AL: TOASO.IS, TUPRS.IS, ASELS.IS, EREGL.IS, YKBNK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -765,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, TCELL.IS</t>
+          <t>AZALT: THYAO.IS, BIMAS.IS, KCHOL.IS, TCELL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -782,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, TUPRS.IS, YKBNK.IS</t>
+          <t>ÇIK: PGSUS.IS, AKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -968,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1298803383942314</v>
+        <v>0.1283247720742829</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12988.03383942314</v>
+        <v>12832.47720742829</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1075944148219777</v>
+        <v>0.08979282129620381</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1397.439900640777</v>
+        <v>1152.264332674217</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>326.7403523724834</v>
+        <v>329.9347766474257</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>280.1182279728189</v>
+        <v>287.448544354336</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.132834202439777</v>
+        <v>1.776613759954867</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1002,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1011,29 +1003,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1103018119945178</v>
+        <v>0.1098593557874202</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11030.18119945178</v>
+        <v>10985.93557874202</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0485933259961082</v>
+        <v>0.0595174682884491</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>535.9931908211042</v>
+        <v>653.855072426723</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>382.7365639885795</v>
+        <v>282.8911640330159</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>346.75</v>
+        <v>253.65</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9718665199221654</v>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.19034936576898</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1052,25 +1044,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1010801374353509</v>
+        <v>0.09906242784985422</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10108.01374353509</v>
+        <v>9906.242784985423</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0439164979259993</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>443.908564603931</v>
+        <v>435.0474907212578</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>374.5050436309523</v>
+        <v>386.2491042326198</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>334.9231316263845</v>
+        <v>345.5364219872969</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.661230145057524</v>
+        <v>0.6642161757442929</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1093,25 +1085,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08498979102386779</v>
+        <v>0.09105489056605776</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8498.979102386778</v>
+        <v>9105.489056605775</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0417778692166073</v>
+        <v>0.0521949337830571</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>355.0692374141933</v>
+        <v>475.2603983718894</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>41.73362287148148</v>
+        <v>42.50867693035757</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>37.71751722939798</v>
+        <v>38.08408125062427</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.7144643871138553</v>
+        <v>0.9105129511622817</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1125,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1134,62 +1126,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07374792115203216</v>
+        <v>0.07169855372238489</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7374.792115203216</v>
+        <v>7169.855372238489</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326483</v>
+        <v>0.0516510593235407</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>171.9198877785856</v>
+        <v>370.3306251726972</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>133.1328751118773</v>
+        <v>36.95501758275235</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>122.850931549045</v>
+        <v>33.06703733795143</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4183801650227533</v>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.8755674960948088</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1207,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1230,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1251,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1293,7 +1285,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1431,577 +1423,691 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.07977534060717011</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0313901161462761</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.1259383002873109</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>317.0173951608299</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>355.3138950123922</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>387.8857444489786</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>317.0173951608299</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>302.75</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0170454545454545</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.08979282129620381</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.1171875590725464</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>297.5894886363637</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>329.9347766474257</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>338.2285335092134</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>287.448544354336</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>267</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0322755583889851</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0595174682884491</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.2064285544041462</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>258.382425910141</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>282.8911640330159</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>322.116424025907</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>253.65</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0156773487587726</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0209217743478541</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.085651551868344</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>366.6601875873572</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>380.2933609445756</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>404.4052030709582</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>353.875</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>370</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.0654499587490297</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.0439164979259993</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.1431977512695257</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>345.783515262859</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>386.2491042326198</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>422.9831679697245</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>345.5364219872969</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>192.8000030517578</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0136719843632644</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.0259673500152164</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.0466707658152421</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>190.1640444247969</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>197.8065082139376</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>201.7981268433644</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>183.1600028991699</v>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>40.40000152587891</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.0573247571233663</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.0521949337830571</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.1107635436316054</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>38.08408125062427</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>42.50867693035757</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>44.87484885760752</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>38.08408125062427</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>107</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0388691413931725</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.0129803441648973</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.0608834909476494</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>102.8410018709305</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>108.388896825644</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>113.5145335313985</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>35.13999938964844</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>-0.0149376594275444</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>0.0516510593235407</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.0996849765015785</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>34.61509004648175</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>36.95501758275235</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>38.64292940307103</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>33.06703733795143</v>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>129</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>-0.0564308739824556</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0.0210781225826901</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0.1152459111776803</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>121.7204172562632</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>131.719077813167</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>143.8667225419208</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>121.7204172562632</v>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>338.25</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.1079385998814506</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>-0.0478684433228991</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0.3470097212410028</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>301.7397685900993</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>322.0584990460294</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>455.6260382097692</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>301.7397685900993</v>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O8" s="15" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>295</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>-0.0347638056112084</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0.1075944148219777</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.1296240822210881</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>284.7446773446935</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>326.7403523724834</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>333.239104255221</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>280.1182279728189</v>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M9" s="18" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N9" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="18" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>365</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>-0.0006844626967830001</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.0485933259961082</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.08921495188780421</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>364.7501711156742</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>382.7365639885795</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>397.5634574390485</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>346.75</v>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N10" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O10" s="18" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>358.75</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>-0.065000031562885</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0.0439164979259993</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.1382006391848767</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>335.431238676815</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>374.5050436309523</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>408.3294793075745</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>334.9231316263845</v>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="18" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N11" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O11" s="18" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="D18" s="21" t="n">
+        <v>170.1999969482422</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>-0.1133159383854944</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>-0.008556371217490699</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>0.1413512208221863</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>150.9136245808438</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>168.7437025931372</v>
+      </c>
+      <c r="J18" s="21" t="n">
+        <v>194.2579743008086</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <v>150.9136245808438</v>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O18" s="20" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
-        <v>264.25</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0378433523870624</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>-0.008302551330894799</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>0.1756284887830799</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>254.2498941317188</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>262.0560508108111</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>310.6598281609288</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>251.0375</v>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="D19" s="21" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>-0.0897941341967378</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>-0.053711988232548</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>0.0537766399993218</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>62.57665327397428</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>65.05730080901233</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>72.44714399995337</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>62.57665327397428</v>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N12" s="15" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="15" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>40.06000137329102</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>-0.0584743900047599</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.1392961182157173</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>37.71751722939798</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>41.73362287148148</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>45.64020406030676</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>37.71751722939798</v>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="18" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>185.1000061035156</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>-0.0245806465802866</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>0.0143885670157133</v>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>0.0729758361499266</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>180.5501282714762</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>187.763329945945</v>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>198.6078338202762</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>175.8450057983398</v>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>130.1000061035156</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>-0.0557192483811474</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>0.0233118283326483</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>0.1272216922975995</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>122.850931549045</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>133.1328751118773</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>146.6515490479329</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>122.850931549045</v>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="18" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N15" s="18" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="M19" s="20" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>35.86000061035156</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.1065088329994344</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>-0.0199168792367256</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>0.1064815305875086</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>32.04059379398402</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>35.14578130876628</v>
-      </c>
-      <c r="J16" s="16" t="n">
-        <v>39.67842836221079</v>
-      </c>
-      <c r="K16" s="16" t="n">
-        <v>32.04059379398402</v>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N16" s="15" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="15" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>104.9000015258789</v>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>-0.0388692288111882</v>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>0.0138761110298255</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>0.0600558756766194</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>100.8226193642755</v>
-      </c>
-      <c r="I17" s="22" t="n">
-        <v>106.3556055940809</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>111.1998629759943</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>99.65500144958496</v>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="21" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2031,7 +2137,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2048,7 +2154,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2120,733 +2226,733 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.174765558397272</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.0782472613458529</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>0.1958533597911065</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.0211849790475223</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.0313901161462761</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>0.06978798586572441</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.09099099099099089</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.1725048564252078</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.1720078095669028</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0252707772843336</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.08979282129620381</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>0.1313559322033899</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.0470588235294118</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.4087638430007234</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.0117997091274201</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.023205517276111</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.0595174682884491</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-0.0159260751356398</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.0065594159321824</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.1646659498315272</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.189655659873275</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.0194015143236158</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.0209217743478541</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>-0.0205162144275314</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>-0.0179163901791639</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.3214285714285714</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.2926304938465678</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.0330588892063555</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.0439164979259993</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0466884161020486</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>-0.0340681505201518</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.0870041854768803</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.1359221120589444</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.0209428200489323</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0.0259673500152164</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0.0520833312637276</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.3604425406496807</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.6605564421008812</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>-0.121851027724222</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0.0271648980406396</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>0.0521949337830571</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0046511627906976</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>-0.06468532716063739</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.08850454402998741</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.010240362230919</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0.0218163587422981</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.0129803441648973</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.0034265828188519</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-0.0664187045839203</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>-0.0664187045839203</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0.0422189262828736</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>0.0294957610657738</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>0.0516510593235407</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>-0.0563277038781323</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>-0.07757380511345351</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0.024692857219561</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>0.0239169393170869</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>0.0210781225826901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
-        <v>0.1446700507614213</v>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>0.0670347003154574</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>0.1485568760611204</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.1853275754063696</v>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>0.0210892198914124</v>
-      </c>
-      <c r="K4" s="17" t="n">
-        <v>-0.0478684433228991</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>0.0172413793103447</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>0.0875576036866359</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>0.1424902812400867</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>0.1733396213044109</v>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="E14" s="22" t="n">
+        <v>0.0283987731011612</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.08148950812104359</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>-0.1685393283553552</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>0.0430765326232058</v>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>0.0210765814808243</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>-0.008556371217490699</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-0.0050389652192398</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.0520339563514903</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0.1219933871809682</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.0723122926083464</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
-        <v>0.0252233424189511</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>0.1075944148219777</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>-0.0357396440926404</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>-0.0228999651161747</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>0.1854638270743971</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>0.1934621837869401</v>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="J15" s="24" t="n">
+        <v>0.0254182463899903</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0271150177147871</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>-0.0187721435348136</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>-0.09626165900295749</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0.1484560556619598</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.0163309575069274</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
-        <v>0.0192629012047767</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>0.0485933259961082</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>-0.0477770404777704</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>-0.0096618357487923</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>0.3653663177925785</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <v>0.2545649009680228</v>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="n">
-        <v>0.033208178917931</v>
-      </c>
-      <c r="K7" s="20" t="n">
-        <v>0.0439164979259993</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="J16" s="24" t="n">
+        <v>0.0249459444263092</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.0548521525126809</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
-        <v>0.1254258797507359</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0.0527888446215139</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0.398507081209307</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>-0.0468540909558131</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>0.0232520955933265</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>-0.008302551330894799</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="E17" s="22" t="n">
+        <v>0.029191569747853</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>-0.0869854287689156</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>-0.0385710010386531</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>-0.0388066121513535</v>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>0.0297740336139579</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>-0.053711988232548</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>0.0367495343186519</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0.3727078620629434</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.6425849369727854</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>-0.1520547593895964</v>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0272064505069125</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>-0.0120087171664294</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.07227065946904419</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.0071625445398397</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.0635927652447857</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>0.0235757335094399</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.0283622708857007</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>0.0005405735325167</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>-0.08093340758166399</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0.0492942938098479</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>0.1097622211770279</v>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0202677224988553</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.0143885670157133</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>-0.0256157485135083</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.1278659594787656</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-0.0943223050385724</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.0562731000610712</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>0.0172340531422683</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.100972740229551</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0.0148206645905033</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>-0.0538181374289772</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>-0.0716222775792807</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0.0262773593328771</v>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>-0.0548815694109156</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.1996085568066667</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>-0.1406054121782667</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.1304547730263413</v>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
-        <v>0.0239053454337624</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0.0233118283326483</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.0304598102451152</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>-0.044752271289394</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>-0.0467835824429415</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>0.0234335431881171</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>0.0293932688107371</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>-0.0199168792367256</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>0.002868098050996</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>-0.0566546366480172</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>0.0526843945771198</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>0.0007962847384253</v>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>0.021978629617714</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0138761110298255</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>0.0620272098149334</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.07326736701990511</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.003439722222854</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.0395223485312272</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0296749648554729</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.1042944785276074</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>0.0029976018636213</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.1005376180013021</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>-0.1894379457411048</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.0238790800857664</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0209456735330101</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0132897529262719</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.0466165548676777</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.0855768675282135</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0.1423423960079708</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.0191879445593335</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0251320832478948</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0548521525126809</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0447963689606201</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.0841814743462546</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>0.0713609493574576</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.0689221375287711</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0251453845022457</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.0121672787419914</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0219418537193569</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.07472752529597659</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.0051372417203386</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.0858979091386915</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0235486104790142</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0296295530137167</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.053921568627451</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.1376228893287134</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.1345291479820628</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.0740245671883331</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0170044822584005</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0999999076690971</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.0754716832983692</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.20579571659723</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1475556752513833</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.1252150755485725</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0204472511519311</v>
-      </c>
-      <c r="K20" s="25" t="inlineStr"/>
+      <c r="J20" s="24" t="n">
+        <v>0.020516370646107</v>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:K20"/>
@@ -2870,7 +2976,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2878,7 +2984,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2903,7 +3009,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, BIMAS.IS, ASELS.IS, EREGL.IS, GARAN.IS</t>
+          <t>TOASO.IS, TUPRS.IS, ASELS.IS, EREGL.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2915,7 +3021,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TCELL.IS</t>
+          <t>THYAO.IS, BIMAS.IS, KCHOL.IS, TCELL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2927,7 +3033,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TUPRS.IS, YKBNK.IS</t>
+          <t>PGSUS.IS, AKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2939,7 +3045,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, PGSUS.IS, PETKM.IS, SISE.IS, SAHOL.IS, ARCLK.IS, FROTO.IS</t>
+          <t>SISE.IS, PETKM.IS, SAHOL.IS, ARCLK.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3057,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.89 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.77 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3095,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2997,7 +3103,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3058,7 +3164,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3200,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3308,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3320,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3346,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3248,7 +3354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3272,7 +3378,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14321.2001953125</v>
+        <v>14092</v>
       </c>
     </row>
     <row r="5">
@@ -3282,7 +3388,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12718.97953125</v>
+        <v>12732.09903320312</v>
       </c>
     </row>
     <row r="6">
@@ -3316,7 +3422,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>69.81</v>
+        <v>74.04000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3350,7 +3456,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -3359,7 +3465,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-09</t>
+          <t>Rapor Tarihi: 2026-07-10</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3479,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-13 05:21</t>
+          <t>Son Güncelleme: 2026-07-14 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3429,7 +3535,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3437,29 +3543,29 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
-        <v>168.3999938964844</v>
-      </c>
-      <c r="D4" s="26" t="n">
-        <v>167.3000030517578</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>-0.006532012378828944</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>-65.32012378828949</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>0.0292907465429801</v>
+      <c r="C4" s="25" t="n">
+        <v>123.0999984741211</v>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>129</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.04792852639327405</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>479.2852639327393</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3467,203 +3573,203 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
-        <v>123.0999984741211</v>
-      </c>
-      <c r="D5" s="26" t="n">
-        <v>130.1000061035156</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>0.05686440061870601</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>568.6440061870599</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>0.0292907465429801</v>
+      <c r="C5" s="25" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>43.43999862670898</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.04527475545694537</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-1358.242663708363</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>42.22000122070312</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.07208788525927201</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-2162.636557778162</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0.0292907465429801</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>40.40000152587891</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.001487391498861124</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1057.844391423976</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>40.06000137329102</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>-0.006940971200737889</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>-4936.472651186981</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0.0292907465429801</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>302.75</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.01142857142857145</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-375.7947362337836</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="D8" s="26" t="n">
-        <v>295</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>-0.03673469387755102</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>-1207.911652180035</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0.0292907465429801</v>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>370</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.07384230287859828</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-52020.4065174628</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="D9" s="26" t="n">
-        <v>358.75</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>-0.1020025031289111</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>-71858.69713852904</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0.0292907465429801</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>371</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.004043126684636134</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>11001.93592332443</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n">
-        <v>371</v>
-      </c>
-      <c r="D10" s="26" t="n">
-        <v>365</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>-0.01617250673854442</v>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>-44007.74369329773</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>0.0292907465429801</v>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>267</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>267</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>70.65000152587891</v>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>70.19999694824219</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>-0.006369491407185346</v>
-      </c>
-      <c r="F11" s="26" t="n">
-        <v>-59.77284158069051</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>4205495.547493511</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>0.0292907465429801</v>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>35.13999938964844</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>35.13999938964844</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>4287864.596497652</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>0.0450379593777363</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,6 +102,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,7 +165,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,6 +180,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -181,22 +198,22 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +646,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +697,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 74.04/100</t>
+          <t>Güven Puanı: 77.35/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +757,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TOASO.IS, TUPRS.IS, ASELS.IS, EREGL.IS, YKBNK.IS</t>
+          <t>AL: THYAO.IS, TOASO.IS, BIMAS.IS, ASELS.IS, YKBNK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +774,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: THYAO.IS, BIMAS.IS, KCHOL.IS, TCELL.IS, GARAN.IS</t>
+          <t>AZALT: PETKM.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +791,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PGSUS.IS, AKBNK.IS</t>
+          <t>ÇIK: TUPRS.IS, KCHOL.IS, EREGL.IS, TCELL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -951,7 +968,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -960,25 +977,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1283247720742829</v>
+        <v>0.1378322652272047</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12832.47720742829</v>
+        <v>13783.22652272047</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.08979282129620381</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1152.264332674217</v>
+        <v>2921.580410571222</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>329.9347766474257</v>
+        <v>404.1907824027542</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>287.448544354336</v>
+        <v>316.825</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.776613759954867</v>
+        <v>4.239327280524988</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -994,7 +1011,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +1020,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1098593557874202</v>
+        <v>0.1136631628553195</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10985.93557874202</v>
+        <v>11366.31628553195</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0595174682884491</v>
+        <v>0.1012146812708825</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>653.855072426723</v>
+        <v>1150.438080064157</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>282.8911640330159</v>
+        <v>332.0162264031711</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>253.65</v>
+        <v>286.3732915062712</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.19034936576898</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>2.017373866616283</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1052,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,29 +1061,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09906242784985422</v>
+        <v>0.1072078985276552</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9906.242784985423</v>
+        <v>10720.78985276552</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0439164979259993</v>
+        <v>0.0683479782593187</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>435.0474907212578</v>
+        <v>732.7443117795424</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>386.2491042326198</v>
+        <v>399.82923086355</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>345.5364219872969</v>
+        <v>355.5375</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6642161757442929</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.366959565186369</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1093,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,25 +1102,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09105489056605776</v>
+        <v>0.08597095301797182</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9105.489056605775</v>
+        <v>8597.095301797182</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0521949337830571</v>
+        <v>0.0535513188368701</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>475.2603983718894</v>
+        <v>460.3857915774989</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>42.50867693035757</v>
+        <v>371.3768398899967</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>38.08408125062427</v>
+        <v>329.4041014496287</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.9105129511622817</v>
+        <v>0.817324333531646</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1126,62 +1143,62 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07169855372238489</v>
+        <v>0.05532572037184878</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7169.855372238489</v>
+        <v>5532.572037184878</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0516510593235407</v>
+        <v>0.0558805665963408</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>370.3306251726972</v>
+        <v>309.1632601729625</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>36.95501758275235</v>
+        <v>36.00552570978934</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>33.06703733795143</v>
+        <v>32.08809529708159</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.8755674960948088</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.9471267093838054</v>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1199,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1208,7 +1225,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
@@ -1222,7 +1239,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1285,7 +1302,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1423,691 +1440,634 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.0457252439987692</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0.2119663640262494</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.3728564122007715</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>348.7493688735895</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>404.1907824027542</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>457.8476134689573</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>316.825</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.0014379806316145</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.0683479782593187</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.099999524042526</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>374.7881642513817</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>399.82923086355</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>411.6748218729153</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>355.5375</v>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="15" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="15" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>268.25</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-0.0985715365910573</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>-0.0267076945339092</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.1114567611459338</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>241.8081853094489</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>261.0856609412788</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>298.1482761773967</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>241.8081853094489</v>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0124320687288295</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0.1012146812708825</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.1171874493663938</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>297.7517312782579</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>332.0162264031711</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>336.8320159839677</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>286.3732915062712</v>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.08661872847313259</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>-0.0031016652385442</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>0.0914748780728462</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>174.9125134973951</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>190.9060311068188</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>209.0174391509501</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>174.9125134973951</v>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.065000031562885</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0.0535513188368701</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.1516949254631578</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>329.587488874083</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>371.3768398899967</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>405.9724612257631</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>329.4041014496287</v>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O13" s="15" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>40.86000061035156</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>-0.0609999151131662</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>-0.0328176483352647</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>0.06427665049290281</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>38.3675440415962</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>39.51907147934234</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>43.48634458872293</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>38.3675440415962</v>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>-0.0616850558301536</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>-0.0163197883018672</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0.0289374380038223</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>102.2763289145133</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>107.2211430750965</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>112.1541807424166</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>102.2763289145133</v>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.07977534060717011</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0313901161462761</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.1259383002873109</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>317.0173951608299</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>355.3138950123922</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>387.8857444489786</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>317.0173951608299</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="D16" s="22" t="n">
+        <v>19.79999923706055</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>-0.0506568676954056</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>0.0558282141107764</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>18.79699329533964</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>19.79999923706055</v>
+      </c>
+      <c r="J16" s="22" t="n">
+        <v>20.90539783386037</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>18.79699329533964</v>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>302.75</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0170454545454545</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.08979282129620381</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.1171875590725464</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>297.5894886363637</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>329.9347766474257</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>338.2285335092134</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>287.448544354336</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>267</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0322755583889851</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0595174682884491</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.2064285544041462</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>258.382425910141</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>282.8911640330159</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>322.116424025907</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>253.65</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>372.5</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0156773487587726</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0209217743478541</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.085651551868344</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>366.6601875873572</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>380.2933609445756</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>404.4052030709582</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>353.875</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>370</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.0654499587490297</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.0439164979259993</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.1431977512695257</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>345.783515262859</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>386.2491042326198</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>422.9831679697245</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>345.5364219872969</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>192.8000030517578</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0136719843632644</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.0259673500152164</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.0466707658152421</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>190.1640444247969</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>197.8065082139376</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>201.7981268433644</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>183.1600028991699</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>40.40000152587891</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.0573247571233663</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0.0521949337830571</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.1107635436316054</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>38.08408125062427</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>42.50867693035757</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>44.87484885760752</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>38.08408125062427</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>107</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0388691413931725</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.0129803441648973</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.0608834909476494</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>102.8410018709305</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>108.388896825644</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>113.5145335313985</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>101.65</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="D17" s="16" t="n">
+        <v>34.09999847412109</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0449745253424798</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0.0558805665963408</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.1010665940075984</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>32.56636722856821</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>36.00552570978934</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>37.54636917556481</v>
+      </c>
+      <c r="K17" s="16" t="n">
+        <v>32.08809529708159</v>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M15" s="14" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>35.13999938964844</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>-0.0149376594275444</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0.0516510593235407</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.0996849765015785</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>34.61509004648175</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>36.95501758275235</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>38.64292940307103</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>33.06703733795143</v>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="M17" s="15" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>hacim artışı var</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>129</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-0.0564308739824556</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>0.0210781225826901</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0.1152459111776803</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>121.7204172562632</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>131.719077813167</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>143.8667225419208</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>121.7204172562632</v>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>81.55000305175781</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.06983352448881711</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.06983352448881711</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-0.06983352448881711</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>75.85507891657977</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>75.85507891657977</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>75.85507891657977</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>75.85507891657977</v>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M17" s="14" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>170.1999969482422</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>-0.1133159383854944</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>-0.008556371217490699</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>0.1413512208221863</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>150.9136245808438</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>168.7437025931372</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>194.2579743008086</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>150.9136245808438</v>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="20" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>-0.0897941341967378</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>-0.053711988232548</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>0.0537766399993218</v>
-      </c>
-      <c r="H19" s="21" t="n">
-        <v>62.57665327397428</v>
-      </c>
-      <c r="I19" s="21" t="n">
-        <v>65.05730080901233</v>
-      </c>
-      <c r="J19" s="21" t="n">
-        <v>72.44714399995337</v>
-      </c>
-      <c r="K19" s="21" t="n">
-        <v>62.57665327397428</v>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="20" t="n">
-        <v>74.04000000000001</v>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O19" s="20" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M18" s="24" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O18" s="24" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O19"/>
+  <autoFilter ref="A7:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2137,7 +2097,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2154,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2226,733 +2186,735 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0.0836718115353372</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0.0317092034029389</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0.1440823327615781</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.1499005356795786</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0.0215530423622403</v>
+      </c>
+      <c r="K4" s="17" t="n">
+        <v>0.2119663640262494</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>-0.0100020004323775</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.0005298227206975</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.2106169698089695</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.1802665060286667</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>0.0193638014480971</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>0.0683479782593187</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>0.1473481458450443</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>0.0540275049115912</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>0.3756176672493339</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>0.0013963433074857</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>0.0232069565106787</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>-0.0267076945339092</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.0203045685279188</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.0588235294117647</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.1499560657287892</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0.1591141246452383</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>0.0250857520625685</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>0.1012146812708825</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>0.0213333333333334</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>-0.0612745098039215</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>0.0511119296568791</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>0.1017952566767343</v>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>0.0207599355008555</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>-0.0031016652385442</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0505050505050505</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-0.1154328732747804</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.2455830388692579</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.307201563466887</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>0.0327601397877607</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>0.0535513188368701</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>0.0381097555065967</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.323181353615551</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.6646131751833297</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>-0.1024702037092369</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>0.0268143764659159</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>-0.0328176483352647</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>-0.015356793090401</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-0.0707587624537017</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.094927138709669</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>0.0042469551857133</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0.021703344228977</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>-0.0163197883018672</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.174765558397272</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.0782472613458529</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.1958533597911065</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0211849790475223</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.0313901161462761</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="E12" s="23" t="n">
+        <v>0.021144912858068</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>-0.0730337700709148</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.1667648814504663</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>-0.0184730884003817</v>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>0.0251450408743384</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.06978798586572441</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.09099099099099089</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.1725048564252078</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.1720078095669028</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E13" s="17" t="n">
+        <v>-0.1049868808450725</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>-0.1179514069138378</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>-0.08480944685351451</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>0.0352762929210594</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>0.0295000479042009</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>0.0558805665963408</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>-0.0361930069846632</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>-0.0788220310991153</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>0.1063463445953991</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>-0.1029147356555855</v>
+      </c>
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0252707772843336</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.08979282129620381</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0.1313559322033899</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.0470588235294118</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.4087638430007234</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.0117997091274201</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0.023205517276111</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.0595174682884491</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="J14" s="28" t="n">
+        <v>0.025265805511917</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>0.0287515115570934</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0159260751356398</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.0065594159321824</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.1646659498315272</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>0.189655659873275</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>0.0194015143236158</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0209217743478541</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>-0.0205162144275314</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>-0.0179163901791639</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.3214285714285714</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.2926304938465678</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0.0330588892063555</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.0439164979259993</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>-0.0383721285088117</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>-0.1220806833605168</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>-0.190802354034076</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>0.0007877013615595</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>0.021222191247619</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>0.0118473493714823</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0466884161020486</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>-0.0340681505201518</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.0870041854768803</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.1359221120589444</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>0.0209428200489323</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>0.0259673500152164</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>-0.06769681649323581</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>-0.09757833008413851</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>-0.0946424194475531</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>-0.0306021721721768</v>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>0.0237463515835941</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>0.0035923499515197</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.0520833312637276</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.3604425406496807</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.6605564421008812</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.121851027724222</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0271648980406396</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>0.0521949337830571</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>-0.0524781481613567</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>-0.1687979755893203</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>-0.1112123727222917</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>-0.0536024475053498</v>
+      </c>
+      <c r="I17" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n">
+        <v>0.0166552056654442</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>0.0384314524152172</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0046511627906976</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>-0.06468532716063739</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.08850454402998741</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.010240362230919</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0218163587422981</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.0129803441648973</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>-0.07034914241468</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.1254902259976256</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.0264978175843392</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.0792867898740543</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="n">
+        <v>0.022866592480569</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>0.1011980384014693</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>0.0034265828188519</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>-0.0664187045839203</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>-0.0664187045839203</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.0422189262828736</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>-0.0681817775796049</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>-0.1371173442700961</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>-0.0500923766103237</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>-0.07746755525020881</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="19" t="n">
-        <v>0.0294957610657738</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>0.0516510593235407</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="J19" s="28" t="n">
+        <v>0.0293358486966032</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>0.09498274421764449</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>-0.0563277038781323</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>-0.07757380511345351</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>0.024692857219561</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>-0.0594001623732327</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.2255460523427167</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.1462670335506165</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>-0.1539911652398075</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
-        <v>0.0239169393170869</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>0.0210781225826901</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>0.0283987731011612</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.08148950812104359</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>-0.1685393283553552</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>0.0430765326232058</v>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>0.0210765814808243</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>-0.008556371217490699</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0050389652192398</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.0520339563514903</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>0.1219933871809682</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.0723122926083464</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0254182463899903</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0271150177147871</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>-0.0187721435348136</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>-0.09626165900295749</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.1484560556619598</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.0163309575069274</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0249459444263092</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0548521525126809</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>0.029191569747853</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>-0.0869854287689156</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>-0.0385710010386531</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>-0.0388066121513535</v>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>0.0297740336139579</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>-0.053711988232548</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0120087171664294</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.07227065946904419</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.0071625445398397</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.0635927652447857</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0235757335094399</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0283622708857007</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0256157485135083</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.1278659594787656</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.0943223050385724</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.0562731000610712</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0172340531422683</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.100972740229551</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.0548815694109156</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1996085568066667</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>-0.1406054121782667</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.1304547730263413</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.020516370646107</v>
-      </c>
-      <c r="K20" s="24" t="inlineStr"/>
+      <c r="J20" s="26" t="n">
+        <v>0.0200591603836238</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>-0.06983352448881711</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:K20"/>
@@ -2976,7 +2938,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2984,7 +2946,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3009,7 +2971,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS, TUPRS.IS, ASELS.IS, EREGL.IS, YKBNK.IS</t>
+          <t>THYAO.IS, BIMAS.IS, TOASO.IS, ASELS.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -3021,7 +2983,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, BIMAS.IS, KCHOL.IS, TCELL.IS, GARAN.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -3033,7 +2995,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS, AKBNK.IS</t>
+          <t>TUPRS.IS, KCHOL.IS, EREGL.IS, TCELL.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3007,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS, PETKM.IS, SAHOL.IS, ARCLK.IS, FROTO.IS</t>
+          <t>SISE.IS, PGSUS.IS, GARAN.IS, ARCLK.IS, SAHOL.IS, AKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3019,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.77 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.68 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3057,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3103,7 +3065,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3164,7 +3126,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3138,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3162,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3246,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3270,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3308,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3354,7 +3316,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,7 +3384,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>74.04000000000001</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3449,7 +3411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3465,7 +3427,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-10</t>
+          <t>Rapor Tarihi: 2026-07-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3479,7 +3441,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-14 04:38</t>
+          <t>Son Güncelleme: 2026-07-15 04:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3543,23 +3505,23 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="29" t="n">
         <v>123.0999984741211</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>129</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.04792852639327405</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>479.2852639327393</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.0450379593777363</v>
+      <c r="D4" s="29" t="n">
+        <v>126.6999969482422</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.02924450462018413</v>
+      </c>
+      <c r="F4" s="29" t="n">
+        <v>292.4450462018413</v>
+      </c>
+      <c r="G4" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
     <row r="5">
@@ -3573,207 +3535,177 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="29" t="n">
         <v>45.5</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>43.43999862670898</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.04527475545694537</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-1358.242663708363</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.0450379593777363</v>
+      <c r="D5" s="29" t="n">
+        <v>43.13999938964844</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>-0.05186814528245187</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>-1556.044358473559</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>40.34000015258789</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>40.40000152587891</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>0.001487391498861124</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1057.844391423976</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.0450379593777363</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>-0.01551020408163262</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>-510.0071420315689</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>306.25</v>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>302.75</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.01142857142857145</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-375.7947362337836</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.0450379593777363</v>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>-0.1176470588235294</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>-82879.96970578819</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>370</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.07384230287859828</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-52020.4065174628</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.0450379593777363</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>371</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>0.00876010781671166</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>23837.52783386968</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>371</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>372.5</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>0.004043126684636134</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>11001.93592332443</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.0450379593777363</v>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>35.13999938964844</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>34.09999847412109</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>-0.02959592867362737</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>-1766.358089831556</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>267</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>267</v>
-      </c>
-      <c r="E10" s="26" t="n">
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="E10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.0450379593777363</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>35.13999938964844</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>35.13999938964844</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>4287864.596497652</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.0450379593777363</v>
+      <c r="G10" s="29" t="n">
+        <v>4275944.763689951</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>0.0283129013426737</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H11"/>
+  <autoFilter ref="A3:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -646,7 +646,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -697,7 +697,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 77.35/100</t>
+          <t>Güven Puanı: 76.66/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -757,7 +757,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: THYAO.IS, TOASO.IS, BIMAS.IS, ASELS.IS, YKBNK.IS</t>
+          <t>AL: THYAO.IS, TOASO.IS, BIMAS.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -774,7 +774,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: PETKM.IS</t>
+          <t>AZALT: KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -791,7 +791,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, KCHOL.IS, EREGL.IS, TCELL.IS, FROTO.IS</t>
+          <t>ÇIK: TUPRS.IS, TCELL.IS, EREGL.IS, PETKM.IS, PGSUS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -977,25 +977,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1378322652272047</v>
+        <v>0.1411907502446492</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13783.22652272047</v>
+        <v>14119.07502446492</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.2119663640262494</v>
+        <v>0.211966460056985</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2921.580410571222</v>
+        <v>2992.770352214818</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.1907824027542</v>
+        <v>395.1010659785771</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>316.825</v>
+        <v>309.7</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.239327280524988</v>
+        <v>4.239329201139699</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1136631628553195</v>
+        <v>0.1158182162300614</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11366.31628553195</v>
+        <v>11581.82162300614</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1012146812708825</v>
+        <v>0.1111299260656438</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1150.438080064157</v>
+        <v>1287.086980670147</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>332.0162264031711</v>
+        <v>327.7833281893649</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>286.3732915062712</v>
+        <v>280.1065641480559</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.017373866616283</v>
+        <v>2.201193097097575</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1061,29 +1061,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1072078985276552</v>
+        <v>0.1004959051851134</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10720.78985276552</v>
+        <v>10049.59051851134</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0683479782593187</v>
+        <v>0.0285884964496119</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>732.7443117795424</v>
+        <v>287.3026828585149</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>399.82923086355</v>
+        <v>395.4922768848758</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>355.5375</v>
+        <v>347.0838567671177</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.366959565186369</v>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.2937843383926182</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1102,29 +1102,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08597095301797182</v>
+        <v>0.08834742378690429</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8597.095301797182</v>
+        <v>8834.742378690429</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0535513188368701</v>
+        <v>0.0768722084891164</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>460.3857915774989</v>
+        <v>679.1461580823228</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>371.3768398899967</v>
+        <v>375.2899646584571</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>329.4041014496287</v>
+        <v>325.9832118727351</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.817324333531646</v>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.189777356656739</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1143,25 +1143,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05532572037184878</v>
+        <v>0.05414770455327169</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5532.572037184878</v>
+        <v>5414.770455327169</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0558805665963408</v>
+        <v>0.029998132625555</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>309.1632601729625</v>
+        <v>162.4330022558412</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>36.00552570978934</v>
+        <v>44.90791701082177</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>32.08809529708159</v>
+        <v>41.39471417403306</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.9471267093838054</v>
+        <v>0.5930838652632977</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
@@ -1239,7 +1239,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1260,7 +1260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1454,36 +1454,36 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>333.5</v>
+        <v>384.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.0457252439987692</v>
+        <v>-0.0973111657552205</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.2119663640262494</v>
+        <v>0.0285884964496119</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.3728564122007715</v>
+        <v>0.0474812210724069</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>348.7493688735895</v>
+        <v>347.0838567671177</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>404.1907824027542</v>
+        <v>395.4922768848758</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>457.8476134689573</v>
+        <v>402.7565295023405</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>316.825</v>
+        <v>347.0838567671177</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="15" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N8" s="15" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="O8" s="15" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -1511,36 +1511,36 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>374.25</v>
+        <v>326</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0.0014379806316145</v>
+        <v>0.0457252883240006</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>0.0683479782593187</v>
+        <v>0.211966460056985</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.099999524042526</v>
+        <v>0.3728564655733453</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>374.7881642513817</v>
+        <v>340.9064439936242</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>399.82923086355</v>
+        <v>395.1010659785771</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>411.6748218729153</v>
+        <v>447.5512077769106</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>355.5375</v>
+        <v>309.7</v>
       </c>
       <c r="L9" s="15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
       <c r="M9" s="15" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N9" s="15" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
@@ -1568,28 +1568,28 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>268.25</v>
+        <v>270.75</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-0.0985715365910573</v>
+        <v>-0.1075472304912292</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-0.0267076945339092</v>
+        <v>-0.0035847527809796</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.1114567611459338</v>
+        <v>0.08512142993789459</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>241.8081853094489</v>
+        <v>241.6315873444997</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>261.0856609412788</v>
+        <v>269.7794281845498</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>298.1482761773967</v>
+        <v>293.796627155685</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>241.8081853094489</v>
+        <v>241.6315873444997</v>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="M10" s="18" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
@@ -1625,28 +1625,28 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>301.5</v>
+        <v>295</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>-0.0124320687288295</v>
+        <v>0.0081607762661732</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.1012146812708825</v>
+        <v>0.1111299260656438</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.1171874493663938</v>
+        <v>0.1437536984966724</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>297.7517312782579</v>
+        <v>297.4074289985211</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>332.0162264031711</v>
+        <v>327.7833281893649</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>336.8320159839677</v>
+        <v>337.4073410565183</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>286.3732915062712</v>
+        <v>280.1065641480559</v>
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="M11" s="15" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N11" s="15" t="inlineStr">
         <is>
@@ -1663,178 +1663,178 @@
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>191.1000061035156</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>-0.0031018111585281</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0.0259674251026877</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.0466708728798923</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>190.5072499721889</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>196.0623811991318</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>200.0188101957195</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>181.5450057983398</v>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>-0.08661872847313259</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>-0.0031016652385442</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>0.0914748780728462</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>174.9125134973951</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>190.9060311068188</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>209.0174391509501</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>174.9125134973951</v>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="D13" s="19" t="n">
+        <v>110.1999969482422</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-0.0615866518007279</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>-0.0157859170736172</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.0100401434839101</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>103.4131481077495</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>108.4603889349044</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>111.306420729529</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>103.4131481077495</v>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="18" t="n">
-        <v>77.34999999999999</v>
-      </c>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="M13" s="18" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O12" s="18" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
-        <v>352.5</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>-0.065000031562885</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>0.0535513188368701</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>0.1516949254631578</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>329.587488874083</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>371.3768398899967</v>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>405.9724612257631</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>329.4041014496287</v>
-      </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="15" t="n">
-        <v>77.34999999999999</v>
-      </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="D14" s="16" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0161982288834289</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.0768722084891164</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.2234482270298656</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>342.854917234125</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>375.2899646584571</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>426.3717071199082</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>325.9832118727351</v>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>40.86000061035156</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>-0.0609999151131662</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>-0.0328176483352647</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0.06427665049290281</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>38.3675440415962</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>39.51907147934234</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>43.48634458872293</v>
-      </c>
-      <c r="K14" s="19" t="n">
-        <v>38.3675440415962</v>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>77.34999999999999</v>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O14" s="18" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -1853,28 +1853,28 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>109</v>
+        <v>41.88000106811523</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>-0.0616850558301536</v>
+        <v>-0.0609999645366716</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>-0.0163197883018672</v>
+        <v>-0.0254998112759489</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.0289374380038223</v>
+        <v>0.082112718269422</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>102.2763289145133</v>
+        <v>39.32532248816444</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>107.2211430750965</v>
+        <v>40.81206894464176</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>112.1541807424166</v>
+        <v>45.31888179694447</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>102.2763289145133</v>
+        <v>39.32532248816444</v>
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
@@ -1882,71 +1882,71 @@
         </is>
       </c>
       <c r="M15" s="18" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N15" s="18" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O15" s="18" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>19.79999923706055</v>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>-0.0506568676954056</v>
-      </c>
-      <c r="F16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>0.0558282141107764</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>18.79699329533964</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <v>19.79999923706055</v>
-      </c>
-      <c r="J16" s="22" t="n">
-        <v>20.90539783386037</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>18.79699329533964</v>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>19.60000038146973</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>-0.0633746386509592</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>-0.0293355143063753</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>0.0814151454989152</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>18.35785743973542</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>19.02502428987416</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>21.19573726430588</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>18.35785743973542</v>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M16" s="21" t="n">
-        <v>77.34999999999999</v>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="21" t="inlineStr">
+      <c r="M16" s="18" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1967,28 +1967,28 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>34.09999847412109</v>
+        <v>43.59999847412109</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-0.0449745253424798</v>
+        <v>-0.0338140537472411</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>0.0558805665963408</v>
+        <v>0.029998132625555</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.1010665940075984</v>
+        <v>0.111591751941328</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>32.56636722856821</v>
+        <v>42.12570578233753</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>36.00552570978934</v>
+        <v>44.90791701082177</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>37.54636917556481</v>
+        <v>48.4653986884875</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>32.08809529708159</v>
+        <v>41.39471417403306</v>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         </is>
       </c>
       <c r="M17" s="15" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N17" s="15" t="inlineStr">
         <is>
-          <t>hacim artışı var</t>
+          <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
       <c r="O17" s="15" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -2024,28 +2024,28 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>81.55000305175781</v>
+        <v>166</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.06983352448881711</v>
+        <v>-0.08003966001870309</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>-0.06983352448881711</v>
+        <v>-0.0007077205736818</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-0.06983352448881711</v>
+        <v>0.0477932433117227</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>75.85507891657977</v>
+        <v>152.7134164368953</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>75.85507891657977</v>
+        <v>165.8825183847688</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>75.85507891657977</v>
+        <v>173.933678389746</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>75.85507891657977</v>
+        <v>152.7134164368953</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="M18" s="24" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2114,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
@@ -2205,16 +2205,16 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>0.0836718115353372</v>
+        <v>-0.0190288668441804</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>0.0317092034029389</v>
+        <v>0.026567336110163</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.1440823327615781</v>
+        <v>0.2377986270081336</v>
       </c>
       <c r="H4" s="17" t="n">
-        <v>0.1499005356795786</v>
+        <v>0.1605015198941304</v>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0215530423622403</v>
+        <v>0.0196644721393515</v>
       </c>
       <c r="K4" s="17" t="n">
-        <v>0.2119663640262494</v>
+        <v>0.0285884964496119</v>
       </c>
     </row>
     <row r="5">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -2248,27 +2248,27 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>-0.0100020004323775</v>
+        <v>0.0007674597083653</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>0.0005298227206975</v>
+        <v>0.0292028413575375</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.2106169698089695</v>
+        <v>0.1358885017421602</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.1802665060286667</v>
+        <v>0.1491219309923437</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J5" s="17" t="n">
-        <v>0.0193638014480971</v>
+        <v>0.0215922041683922</v>
       </c>
       <c r="K5" s="17" t="n">
-        <v>0.0683479782593187</v>
+        <v>0.211966460056985</v>
       </c>
     </row>
     <row r="6">
@@ -2291,16 +2291,16 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>0.1473481458450443</v>
+        <v>0.1675291381027699</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>0.0540275049115912</v>
+        <v>0.0255681818181818</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>0.3756176672493339</v>
+        <v>0.3524611212261019</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>0.0013963433074857</v>
+        <v>0.008091394995426399</v>
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="J6" s="20" t="n">
-        <v>0.0232069565106787</v>
+        <v>0.0227658524144454</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>-0.0267076945339092</v>
+        <v>-0.0035847527809796</v>
       </c>
     </row>
     <row r="7">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>0.0203045685279188</v>
+        <v>-0.0642347343378271</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.0396475770925111</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.1499560657287892</v>
+        <v>0.1132472898847316</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>0.1591141246452383</v>
+        <v>0.1642141627234943</v>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
@@ -2351,139 +2351,139 @@
         </is>
       </c>
       <c r="J7" s="17" t="n">
-        <v>0.0250857520625685</v>
+        <v>0.0252431116134646</v>
       </c>
       <c r="K7" s="17" t="n">
-        <v>0.1012146812708825</v>
+        <v>0.1111299260656438</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>-0.0289633986781143</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>-0.0636942656111761</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0.0550570318630014</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0.0974944523345975</v>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>0.0207599110986449</v>
+      </c>
+      <c r="K8" s="23" t="n">
+        <v>0.0259674251026877</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
-        <v>0.0213333333333334</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>-0.0612745098039215</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>0.0511119296568791</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>0.1017952566767343</v>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="E9" s="20" t="n">
+        <v>-0.0409051741968701</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>-0.0475367341838427</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.08357915688361189</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>0.0133939105888096</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>0.0216927332752226</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>-0.0157859170736172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.072521623419827</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>-0.1607465382299819</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.2027610008628126</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.3510003411936864</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="20" t="n">
-        <v>0.0207599355008555</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>-0.0031016652385442</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>-0.0505050505050505</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>-0.1154328732747804</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>0.2455830388692579</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0.307201563466887</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>0.0327601397877607</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>0.0535513188368701</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>0.0381097555065967</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.323181353615551</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.6646131751833297</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>-0.1024702037092369</v>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>0.0268143764659159</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>-0.0328176483352647</v>
+      <c r="J10" s="17" t="n">
+        <v>0.0323052914307962</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>0.0768722084891164</v>
       </c>
     </row>
     <row r="11">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -2506,70 +2506,70 @@
         </is>
       </c>
       <c r="E11" s="20" t="n">
-        <v>-0.015356793090401</v>
+        <v>0.0417910515744213</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>-0.0707587624537017</v>
+        <v>0.326545134059877</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.094927138709669</v>
+        <v>0.6885221205176615</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>0.0042469551857133</v>
+        <v>-0.1112733409259896</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0.0268438090323615</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>-0.0254998112759489</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>0.0129198963861214</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>-0.1171171302755156</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>0.1590775019710772</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-0.0327387798328456</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
-        <v>0.021703344228977</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>-0.0163197883018672</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>0.021144912858068</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>-0.0730337700709148</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>0.1667648814504663</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>-0.0184730884003817</v>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0.0251450408743384</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0</v>
+      <c r="J12" s="20" t="n">
+        <v>0.0246359648641499</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>-0.0293355143063753</v>
       </c>
     </row>
     <row r="13">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -2592,70 +2592,70 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>-0.1049868808450725</v>
+        <v>-0.0603448913723883</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>-0.1179514069138378</v>
+        <v>-0.0752373665829406</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>-0.08480944685351451</v>
+        <v>0.1272756251660045</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>0.0352762929210594</v>
+        <v>-0.1060989864928483</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>0.0252899584548952</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>0.029998132625555</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.0838851942838824</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.09635273403531509</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.1753601714684601</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.0243681424048937</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
-        <v>0.0295000479042009</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>0.0558805665963408</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>-0.0361930069846632</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>-0.0788220310991153</v>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>0.1063463445953991</v>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>-0.1029147356555855</v>
-      </c>
-      <c r="I14" s="27" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J14" s="28" t="n">
-        <v>0.025265805511917</v>
-      </c>
-      <c r="K14" s="28" t="n">
-        <v>0.0287515115570934</v>
+      <c r="J14" s="26" t="n">
+        <v>0.0210248897360651</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>-0.0007077205736818</v>
       </c>
     </row>
     <row r="15">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -2678,16 +2678,16 @@
         </is>
       </c>
       <c r="E15" s="28" t="n">
-        <v>-0.0383721285088117</v>
+        <v>-0.08581564612422431</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>-0.1220806833605168</v>
+        <v>-0.0706561158427049</v>
       </c>
       <c r="G15" s="28" t="n">
-        <v>-0.190802354034076</v>
+        <v>-0.09201783893196849</v>
       </c>
       <c r="H15" s="28" t="n">
-        <v>0.0007877013615595</v>
+        <v>-0.0563033927587761</v>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="J15" s="28" t="n">
-        <v>0.021222191247619</v>
+        <v>0.0238212180877457</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0.0118473493714823</v>
+        <v>0.0044790800861671</v>
       </c>
     </row>
     <row r="16">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -2721,16 +2721,16 @@
         </is>
       </c>
       <c r="E16" s="28" t="n">
-        <v>-0.06769681649323581</v>
+        <v>-0.1606524999278733</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>-0.09757833008413851</v>
+        <v>-0.1077247015470571</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>-0.0946424194475531</v>
+        <v>-0.0953649905100008</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>-0.0306021721721768</v>
+        <v>0.0607523005675425</v>
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0237463515835941</v>
+        <v>0.0294479348541073</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>0.0035923499515197</v>
+        <v>0.0024287491670588</v>
       </c>
     </row>
     <row r="17">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -2764,16 +2764,16 @@
         </is>
       </c>
       <c r="E17" s="28" t="n">
-        <v>-0.0524781481613567</v>
+        <v>-0.1161067228688695</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>-0.1687979755893203</v>
+        <v>-0.0973764043840919</v>
       </c>
       <c r="G17" s="28" t="n">
-        <v>-0.1112123727222917</v>
+        <v>-0.0279457946083959</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>-0.0536024475053498</v>
+        <v>-0.0696915663651644</v>
       </c>
       <c r="I17" s="27" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="J17" s="28" t="n">
-        <v>0.0166552056654442</v>
+        <v>0.0226186848606233</v>
       </c>
       <c r="K17" s="28" t="n">
-        <v>0.0384314524152172</v>
+        <v>0.0283622708857007</v>
       </c>
     </row>
     <row r="18">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -2807,16 +2807,16 @@
         </is>
       </c>
       <c r="E18" s="28" t="n">
-        <v>-0.07034914241468</v>
+        <v>-0.076814341593669</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>-0.1254902259976256</v>
+        <v>-0.178271816644651</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>-0.0264978175843392</v>
+        <v>-0.1270053510480354</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>-0.0792867898740543</v>
+        <v>-0.0634664546529962</v>
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="J18" s="28" t="n">
-        <v>0.022866592480569</v>
+        <v>0.0165054412771882</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>0.1011980384014693</v>
+        <v>0.0423503831348128</v>
       </c>
     </row>
     <row r="19">
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="E19" s="28" t="n">
-        <v>-0.0681817775796049</v>
+        <v>-0.0996742869821355</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>-0.1371173442700961</v>
+        <v>-0.107235179433203</v>
       </c>
       <c r="G19" s="28" t="n">
-        <v>-0.0500923766103237</v>
+        <v>-0.0427560154628976</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>-0.07746755525020881</v>
+        <v>-0.0988454169353313</v>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
@@ -2867,54 +2867,52 @@
         </is>
       </c>
       <c r="J19" s="28" t="n">
-        <v>0.0293358486966032</v>
+        <v>0.0294480866932792</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>0.09498274421764449</v>
+        <v>0.06673212298112791</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.0594001623732327</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.2255460523427167</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.1462670335506165</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>-0.1539911652398075</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>-0.1004439020602498</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>-0.2273593720419278</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>-0.1691609831902574</v>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>-0.1730126030376599</v>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0200591603836238</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>-0.06983352448881711</v>
-      </c>
+      <c r="J20" s="28" t="n">
+        <v>0.0200612149228342</v>
+      </c>
+      <c r="K20" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:K20"/>
@@ -2938,7 +2936,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2946,7 +2944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2971,7 +2969,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, BIMAS.IS, TOASO.IS, ASELS.IS, YKBNK.IS</t>
+          <t>BIMAS.IS, THYAO.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2981,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2993,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, KCHOL.IS, EREGL.IS, TCELL.IS, FROTO.IS</t>
+          <t>TUPRS.IS, TCELL.IS, EREGL.IS, PETKM.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3005,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS, PGSUS.IS, GARAN.IS, ARCLK.IS, SAHOL.IS, AKBNK.IS</t>
+          <t>GARAN.IS, YKBNK.IS, SAHOL.IS, ARCLK.IS, AKBNK.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3017,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.68 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.73 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3055,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3065,7 +3063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3222,7 +3220,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3280,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3306,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3316,7 +3314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3340,7 +3338,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14092</v>
+        <v>14080</v>
       </c>
     </row>
     <row r="5">
@@ -3350,7 +3348,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12732.09903320312</v>
+        <v>12745.84003417969</v>
       </c>
     </row>
     <row r="6">
@@ -3384,7 +3382,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>77.34999999999999</v>
+        <v>76.66</v>
       </c>
     </row>
     <row r="9">
@@ -3427,7 +3425,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-13</t>
+          <t>Rapor Tarihi: 2026-07-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3441,7 +3439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-15 04:38</t>
+          <t>Son Güncelleme: 2026-07-16 04:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3509,19 +3507,19 @@
         <v>123.0999984741211</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>126.6999969482422</v>
+        <v>128.8999938964844</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.02924450462018413</v>
+        <v>0.0471161291166271</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>292.4450462018413</v>
+        <v>471.1612911662705</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
     <row r="5">
@@ -3539,19 +3537,19 @@
         <v>45.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>43.13999938964844</v>
+        <v>43.59999847412109</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-0.05186814528245187</v>
+        <v>-0.04175827529404186</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-1556.044358473559</v>
+        <v>-1252.748258821259</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
     <row r="6">
@@ -3569,19 +3567,19 @@
         <v>306.25</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>301.5</v>
+        <v>295</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.01551020408163262</v>
+        <v>-0.03673469387755102</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-510.0071420315689</v>
+        <v>-1207.911652180035</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
     <row r="7">
@@ -3599,19 +3597,19 @@
         <v>399.5</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>352.5</v>
+        <v>348.5</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.1176470588235294</v>
+        <v>-0.1276595744680851</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-82879.96970578819</v>
+        <v>-89933.58414883399</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
     <row r="8">
@@ -3629,19 +3627,19 @@
         <v>371</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>374.25</v>
+        <v>384.5</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>0.00876010781671166</v>
+        <v>0.03638814016172498</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>23837.52783386968</v>
+        <v>99017.42330992036</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
     <row r="9">
@@ -3659,19 +3657,19 @@
         <v>35.13999938964844</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>34.09999847412109</v>
+        <v>33.95999908447266</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-0.02959592867362737</v>
+        <v>-0.03357997511870725</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-1766.358089831556</v>
+        <v>-2004.135817509421</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
     <row r="10">
@@ -3689,19 +3687,19 @@
         <v>333.5</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>333.5</v>
+        <v>326</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>0</v>
+        <v>-0.02248875562218888</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>0</v>
+        <v>-17548.81786383805</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>4275944.763689951</v>
+        <v>4326068.556965909</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>0.0283129013426737</v>
+        <v>0.0274372446001167</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -646,7 +646,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1411907502446492</v>
+        <v>0.1411907281111466</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>14119.07502446492</v>
+        <v>14119.07281111465</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.211966460056985</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2992.770352214818</v>
+        <v>2992.769883058797</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>395.1010659785771</v>
@@ -1020,25 +1020,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1158182162300614</v>
+        <v>0.1158181990764193</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11581.82162300614</v>
+        <v>11581.81990764193</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1287.086980670147</v>
+        <v>1287.086829745878</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>327.7833281893649</v>
+        <v>327.7833292006644</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>280.1065641480559</v>
+        <v>280.1065641480558</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.201193097097575</v>
+        <v>2.201193164999927</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1004959051851134</v>
+        <v>0.1004959604649992</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10049.59051851134</v>
+        <v>10049.59604649992</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>287.3026828585149</v>
+        <v>287.3064164680217</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>395.4922768848758</v>
+        <v>395.492413687158</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2937843383926182</v>
+        <v>0.2937877395757468</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1102,25 +1102,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08834742378690429</v>
+        <v>0.08834739475178791</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8834.742378690429</v>
+        <v>8834.739475178791</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>679.1461580823228</v>
+        <v>679.1454050460652</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>375.2899646584571</v>
+        <v>375.2899437582186</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>325.9832118727351</v>
+        <v>325.983211872735</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.189777356656739</v>
+        <v>1.189776428449815</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05414770455327169</v>
+        <v>0.05414771759564697</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5414.770455327169</v>
+        <v>5414.771759564697</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>162.4330022558412</v>
+        <v>162.4334405493678</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>44.90791701082177</v>
+        <v>44.90792022494814</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>41.39471417403306</v>
+        <v>41.39471417403307</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5930838652632977</v>
+        <v>0.593085322729063</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,25 +1457,25 @@
         <v>384.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.0973111657552205</v>
+        <v>-0.09731125023654159</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.0474812210724069</v>
+        <v>0.0474812157001536</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>395.4922768848758</v>
+        <v>395.492413687158</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>402.7565295023405</v>
+        <v>402.7565274367091</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
         <v>270.75</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-0.1075472304912292</v>
+        <v>-0.1075471744334234</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-0.0035847527809796</v>
+        <v>-0.0035848577601887</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.08512142993789459</v>
+        <v>0.0851215718148548</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>241.6315873444997</v>
+        <v>241.6316025221506</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>269.7794281845498</v>
+        <v>269.7793997614289</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>293.796627155685</v>
+        <v>293.796665568872</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>241.6315873444997</v>
+        <v>241.6316025221506</v>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
@@ -1631,22 +1631,22 @@
         <v>0.0081607762661732</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.1437536984966724</v>
+        <v>0.1437538499105514</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>297.4074289985211</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>327.7833281893649</v>
+        <v>327.7833292006644</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>337.4073410565183</v>
+        <v>337.4073857236127</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>280.1065641480559</v>
+        <v>280.1065641480558</v>
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
@@ -1685,22 +1685,22 @@
         <v>191.1000061035156</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>-0.0031018111585281</v>
+        <v>-0.0031017381985415</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.0259674251026877</v>
+        <v>0.025967427052516</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>0.0466708728798923</v>
+        <v>0.0466707608184535</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>190.5072499721889</v>
+        <v>190.5072639148428</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>196.0623811991318</v>
+        <v>196.0623815717441</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>200.0188101957195</v>
+        <v>200.0187887807778</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>181.5450057983398</v>
@@ -1745,7 +1745,7 @@
         <v>-0.0615866518007279</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>-0.0157859170736172</v>
+        <v>-0.0157857473464384</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>0.0100401434839101</v>
@@ -1754,7 +1754,7 @@
         <v>103.4131481077495</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>108.4603889349044</v>
+        <v>108.4604076388389</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>111.306420729529</v>
@@ -1802,7 +1802,7 @@
         <v>-0.0161982288834289</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>0.2234482270298656</v>
@@ -1811,13 +1811,13 @@
         <v>342.854917234125</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>375.2899646584571</v>
+        <v>375.2899437582186</v>
       </c>
       <c r="J14" s="16" t="n">
         <v>426.3717071199082</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>325.9832118727351</v>
+        <v>325.983211872735</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>-0.0254998112759489</v>
+        <v>-0.0254997257062651</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.082112718269422</v>
+        <v>0.08211272221694969</v>
       </c>
       <c r="H15" s="19" t="n">
         <v>39.32532248816444</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>40.81206894464176</v>
+        <v>40.81207252830021</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>45.31888179694447</v>
+        <v>45.31888196226694</v>
       </c>
       <c r="K15" s="19" t="n">
         <v>39.32532248816444</v>
@@ -1973,7 +1973,7 @@
         <v>-0.0338140537472411</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>0.111591751941328</v>
@@ -1982,13 +1982,13 @@
         <v>42.12570578233753</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>44.90791701082177</v>
+        <v>44.90792022494814</v>
       </c>
       <c r="J17" s="16" t="n">
         <v>48.4653986884875</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>41.39471417403306</v>
+        <v>41.39471417403307</v>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0196644721393515</v>
+        <v>0.0196644721393516</v>
       </c>
       <c r="K4" s="17" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
     </row>
     <row r="5">
@@ -2311,7 +2311,7 @@
         <v>0.0227658524144454</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>-0.0035847527809796</v>
+        <v>-0.0035848577601887</v>
       </c>
     </row>
     <row r="7">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="J7" s="17" t="n">
-        <v>0.0252431116134646</v>
+        <v>0.0252431116134647</v>
       </c>
       <c r="K7" s="17" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
     </row>
     <row r="8">
@@ -2397,7 +2397,7 @@
         <v>0.0207599110986449</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.0259674251026877</v>
+        <v>0.025967427052516</v>
       </c>
     </row>
     <row r="9">
@@ -2440,7 +2440,7 @@
         <v>0.0216927332752226</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>-0.0157859170736172</v>
+        <v>-0.0157857473464384</v>
       </c>
     </row>
     <row r="10">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.0323052914307962</v>
+        <v>0.0323052914307963</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
     </row>
     <row r="11">
@@ -2526,7 +2526,7 @@
         <v>0.0268438090323615</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>-0.0254998112759489</v>
+        <v>-0.0254997257062651</v>
       </c>
     </row>
     <row r="12">
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.0252899584548952</v>
+        <v>0.0252899584548951</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
     </row>
     <row r="14">
@@ -2698,7 +2698,7 @@
         <v>0.0238212180877457</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0.0044790800861671</v>
+        <v>0.0044791569432763</v>
       </c>
     </row>
     <row r="16">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0294479348541073</v>
+        <v>0.0294479348541072</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>0.0024287491670588</v>
+        <v>0.0024286871265271</v>
       </c>
     </row>
     <row r="17">
@@ -2784,7 +2784,7 @@
         <v>0.0226186848606233</v>
       </c>
       <c r="K17" s="28" t="n">
-        <v>0.0283622708857007</v>
+        <v>0.0283623502202803</v>
       </c>
     </row>
     <row r="18">
@@ -2827,7 +2827,7 @@
         <v>0.0165054412771882</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>0.0423503831348128</v>
+        <v>0.0423504428390855</v>
       </c>
     </row>
     <row r="19">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="J19" s="28" t="n">
-        <v>0.0294480866932792</v>
+        <v>0.0294480866932793</v>
       </c>
       <c r="K19" s="28" t="n">
         <v>0.06673212298112791</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="J20" s="28" t="n">
-        <v>0.0200612149228342</v>
+        <v>0.0200612149228341</v>
       </c>
       <c r="K20" s="28" t="inlineStr"/>
     </row>
@@ -2944,7 +2944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3063,7 +3063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3314,7 +3314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14080</v>
+        <v>14251.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12745.84003417969</v>
+        <v>12760.26203125</v>
       </c>
     </row>
     <row r="6">
@@ -3439,7 +3439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -91,17 +91,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -162,10 +162,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,15 +180,6 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -198,13 +189,13 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,10 +207,10 @@
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -629,7 +620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-14</t>
+          <t>Rapor Tarihi: 2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -646,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-17 04:51</t>
+          <t>Son Güncelleme: 2026-07-18 04:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -697,7 +688,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 76.66/100</t>
+          <t>Güven Puanı: 73.20/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -757,7 +748,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: THYAO.IS, TOASO.IS, BIMAS.IS, ASELS.IS, SISE.IS</t>
+          <t>AL: TOASO.IS, THYAO.IS, ASELS.IS, KCHOL.IS, SISE.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -774,7 +765,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -791,7 +782,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, TCELL.IS, EREGL.IS, PETKM.IS, PGSUS.IS</t>
+          <t>ÇIK: BIMAS.IS, TUPRS.IS, TCELL.IS, EREGL.IS, PETKM.IS, SAHOL.IS, PGSUS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -968,7 +959,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -977,25 +968,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1411907281111466</v>
+        <v>0.1300092729005628</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>14119.07281111465</v>
+        <v>13000.92729005628</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.211966460056985</v>
+        <v>0.1047501547505572</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2992.769883058797</v>
+        <v>1361.849145534137</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>395.1010659785771</v>
+        <v>336.9487971989199</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>309.7</v>
+        <v>289.75</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.239329201139699</v>
+        <v>2.095003095011142</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1011,7 +1002,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1020,29 +1011,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1158181990764193</v>
+        <v>0.1102481809043067</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11581.81990764193</v>
+        <v>11024.81809043067</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1111299294937776</v>
+        <v>0.0436044762683809</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1287.086829745878</v>
+        <v>480.7314187874006</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>327.7833292006644</v>
+        <v>344.3894771685657</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>280.1065641480558</v>
+        <v>311.0828020725023</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.201193164999927</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
+        <v>0.760655844682442</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1043,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1061,25 +1052,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1004959604649992</v>
+        <v>0.09676731342591428</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10049.59604649992</v>
+        <v>9676.731342591429</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0285888522422834</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>287.3064164680217</v>
+        <v>743.8711289280222</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>395.492413687158</v>
+        <v>379.5974323522872</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>347.0838242840497</v>
+        <v>329.6993168810639</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2937877395757468</v>
+        <v>1.188448267577676</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1093,7 +1084,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1102,29 +1093,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08834739475178791</v>
+        <v>0.09533883249165311</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8834.739475178791</v>
+        <v>9533.88324916531</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.07687214851712661</v>
+        <v>0.025967427052516</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>679.1454050460652</v>
+        <v>247.5704177999044</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>375.2899437582186</v>
+        <v>202.1155831293457</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>325.983211872735</v>
+        <v>187.15</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.189776428449815</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.5193485410503217</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1143,25 +1134,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05414771759564697</v>
+        <v>0.06763640027756311</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5414.771759564697</v>
+        <v>6763.640027756311</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0299982063440521</v>
+        <v>0.0333833966972141</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>162.4334405493678</v>
+        <v>225.7932781637451</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>44.90792022494814</v>
+        <v>46.50225285137464</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>41.39471417403307</v>
+        <v>42.69473037002698</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.593085322729063</v>
+        <v>0.6516603662506142</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1216,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1239,7 +1230,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-07-14</t>
+          <t>Rapor Tarihi: 2026-07-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1260,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-17 04:51</t>
+          <t>Son Güncelleme: 2026-07-18 04:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1302,7 +1293,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 11</t>
+          <t>Toplam önerilen/satılacak satır: 12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1450,32 +1441,32 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>384.5</v>
+        <v>396.25</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.09731125023654159</v>
+        <v>-0.1071560473935289</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.0285888522422834</v>
+        <v>-0.0343615108855213</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.0474812157001536</v>
+        <v>0.0333114725147823</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>347.0838242840497</v>
+        <v>353.7894162203142</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>395.492413687158</v>
+        <v>382.6342513116122</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>402.7565274367091</v>
+        <v>409.4496709839825</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>347.0838242840497</v>
+        <v>353.7894162203142</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1483,7 +1474,7 @@
         </is>
       </c>
       <c r="M8" s="15" t="n">
-        <v>76.66</v>
+        <v>73.2</v>
       </c>
       <c r="N8" s="15" t="inlineStr">
         <is>
@@ -1492,7 +1483,7 @@
       </c>
       <c r="O8" s="15" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1502,45 +1493,45 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>326</v>
+        <v>286.25</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0.0457252883240006</v>
+        <v>-0.0985715292981395</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>0.211966460056985</v>
+        <v>-0.0267075881338385</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.3728564655733453</v>
+        <v>0.1114566537530277</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>340.9064439936242</v>
+        <v>258.0338997384076</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>395.1010659785771</v>
+        <v>278.6049528966887</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>447.5512077769106</v>
+        <v>318.1544671368042</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>309.7</v>
+        <v>258.0338997384076</v>
       </c>
       <c r="L9" s="15" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M9" s="15" t="n">
-        <v>76.66</v>
+        <v>73.2</v>
       </c>
       <c r="N9" s="15" t="inlineStr">
         <is>
@@ -1549,7 +1540,7 @@
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1559,223 +1550,223 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>330</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-0.0573248422045384</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.0436044762683809</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.2641250888371863</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>311.0828020725023</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>344.3894771685657</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>417.1612793162715</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>311.0828020725023</v>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>305</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>-0.0124320687288295</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0.1047501547505572</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.1307692746289981</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>301.208219037707</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>336.9487971989199</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>344.8846287618445</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>197</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.0031018113855404</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0.025967427052516</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>0.0466708728798923</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>196.3889431570485</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>202.1155831293457</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>206.1941619573388</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>187.15</v>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
-        <v>270.75</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>-0.1075471744334234</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>-0.0035848577601887</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.0851215718148548</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>241.6316025221506</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>269.7793997614289</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>293.796665568872</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>241.6316025221506</v>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="D13" s="16" t="n">
+        <v>112.1999969482422</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.0615866518007279</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>-0.0157858315348814</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.0139753607082788</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>105.2899748041481</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>110.428826698203</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>113.7680323770617</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>105.2899748041481</v>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="N10" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="18" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>295</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.0081607762661732</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>0.1111299294937776</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>0.1437538499105514</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>297.4074289985211</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>327.7833292006644</v>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>337.4073857236127</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>280.1065641480558</v>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="N11" s="15" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="15" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>191.1000061035156</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>-0.0031017381985415</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>0.025967427052516</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>0.0466707608184535</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>190.5072639148428</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>196.0623815717441</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>200.0187887807778</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>181.5450057983398</v>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="M13" s="15" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O12" s="21" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>110.1999969482422</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>-0.0615866518007279</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>-0.0157857473464384</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.0100401434839101</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>103.4131481077495</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>108.4604076388389</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>111.306420729529</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>103.4131481077495</v>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="18" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
@@ -1787,54 +1778,54 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>348.5</v>
+        <v>44.06000137329102</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-0.0161982288834289</v>
+        <v>-0.0609999645366716</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.07687214851712661</v>
+        <v>-0.0254998112759489</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.2234482270298656</v>
+        <v>0.08211277661873199</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>342.854917234125</v>
+        <v>41.37234285203456</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>375.2899437582186</v>
+        <v>42.93647965345404</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>426.3717071199082</v>
+        <v>47.67789042387708</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>325.983211872735</v>
+        <v>41.37234285203456</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M14" s="15" t="n">
-        <v>76.66</v>
+        <v>73.2</v>
       </c>
       <c r="N14" s="15" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O14" s="15" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1844,230 +1835,287 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>-0.0197860443083401</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0.07687214851712661</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0.1760203790290668</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>345.5254193813101</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>379.5974323522872</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>414.5471836077461</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>329.6993168810639</v>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
-        <v>41.88000106811523</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>-0.0609999645366716</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>-0.0254997257062651</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>0.08211272221694969</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>39.32532248816444</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>40.81207252830021</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>45.31888196226694</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>39.32532248816444</v>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="D16" s="16" t="n">
+        <v>20.6200008392334</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.0789866180022725</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>-0.00990099449846</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.0584958172872285</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>18.99129670973833</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>20.41584232436591</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>21.82618464078769</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>18.99129670973833</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="N15" s="18" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="M16" s="15" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="15" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>-0.0338140537472411</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>0.0333833966972141</v>
+      </c>
+      <c r="G17" s="20" t="n">
+        <v>0.1048109348623858</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>43.47836758137415</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>46.50225285137464</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>49.71649206880736</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>42.69473037002698</v>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
-        <v>19.60000038146973</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>-0.0633746386509592</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>